--- a/docs/oc-mensuales/suministro-de-combustibles/feb-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/feb-2026.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2436.14</v>
+        <v>2427.47</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>37122.11</v>
+        <v>36989.94</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>44082.5</v>
+        <v>43925.56</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>22513.14</v>
+        <v>22432.98</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>23201.32</v>
+        <v>23118.71</v>
       </c>
     </row>
     <row r="7">
@@ -874,7 +874,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9247.49</v>
       </c>
     </row>
     <row r="8">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>5800.33</v>
+        <v>5779.68</v>
       </c>
     </row>
     <row r="9">
@@ -996,7 +996,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>32481.84</v>
+        <v>32366.2</v>
       </c>
     </row>
     <row r="10">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>11600.66</v>
+        <v>11559.36</v>
       </c>
     </row>
     <row r="11">
@@ -1118,7 +1118,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>11600.66</v>
+        <v>11559.36</v>
       </c>
     </row>
     <row r="12">
@@ -1179,7 +1179,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>23201.32</v>
+        <v>23118.71</v>
       </c>
     </row>
     <row r="13">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>5227.81</v>
+        <v>5209.2</v>
       </c>
     </row>
     <row r="14">
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>16240.92</v>
+        <v>16183.1</v>
       </c>
     </row>
     <row r="15">
@@ -1362,7 +1362,7 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>12285.1</v>
+        <v>12241.36</v>
       </c>
     </row>
     <row r="16">
@@ -1423,7 +1423,7 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>44082.5</v>
+        <v>43925.56</v>
       </c>
     </row>
     <row r="17">
@@ -1484,7 +1484,7 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>3888.8</v>
+        <v>3874.96</v>
       </c>
     </row>
     <row r="18">
@@ -1545,7 +1545,7 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>2668.15</v>
+        <v>2658.65</v>
       </c>
     </row>
     <row r="19">
@@ -1606,7 +1606,7 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4640.26</v>
+        <v>4623.74</v>
       </c>
     </row>
     <row r="20">
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>27758.06</v>
+        <v>27659.23</v>
       </c>
     </row>
     <row r="21">
@@ -1728,7 +1728,7 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>34384.35</v>
+        <v>34561.97</v>
       </c>
     </row>
     <row r="22">
@@ -1789,7 +1789,7 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>29117.65</v>
+        <v>29268.07</v>
       </c>
     </row>
     <row r="23">
@@ -1850,7 +1850,7 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>10211.9</v>
+        <v>10264.66</v>
       </c>
     </row>
     <row r="24">
@@ -1911,7 +1911,7 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>8816.5</v>
+        <v>8862.040000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1972,7 +1972,7 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>8352.469999999999</v>
+        <v>8395.620000000001</v>
       </c>
     </row>
     <row r="26">
@@ -2033,7 +2033,7 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2436.14</v>
+        <v>2448.72</v>
       </c>
     </row>
     <row r="27">
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>78884.48</v>
+        <v>79291.97</v>
       </c>
     </row>
     <row r="28">
@@ -2155,7 +2155,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>23201.32</v>
+        <v>23321.17</v>
       </c>
     </row>
     <row r="29">
@@ -2216,7 +2216,7 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2436.14</v>
+        <v>2448.72</v>
       </c>
     </row>
     <row r="30">
@@ -2277,7 +2277,7 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>2900.16</v>
+        <v>2915.15</v>
       </c>
     </row>
     <row r="31">
@@ -2338,7 +2338,7 @@
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>28744.11</v>
+        <v>28892.59</v>
       </c>
     </row>
     <row r="32">
@@ -2399,7 +2399,7 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3480.2</v>
+        <v>3498.18</v>
       </c>
     </row>
     <row r="33">
@@ -2460,7 +2460,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6631</v>
+        <v>6665.25</v>
       </c>
     </row>
     <row r="34">
@@ -2521,7 +2521,7 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>6960.4</v>
+        <v>6996.35</v>
       </c>
     </row>
     <row r="35">
@@ -2582,7 +2582,7 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>8120.46</v>
+        <v>8162.41</v>
       </c>
     </row>
     <row r="36">
@@ -2643,7 +2643,7 @@
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2552.14</v>
+        <v>2565.33</v>
       </c>
     </row>
     <row r="37">
@@ -2704,7 +2704,7 @@
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>8120.46</v>
+        <v>8162.41</v>
       </c>
     </row>
     <row r="38">
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9328.469999999999</v>
       </c>
     </row>
     <row r="39">
@@ -2826,7 +2826,7 @@
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>3480.2</v>
+        <v>3498.18</v>
       </c>
     </row>
     <row r="40">
@@ -2887,7 +2887,7 @@
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>4060.23</v>
+        <v>4081.2</v>
       </c>
     </row>
     <row r="41">
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>3480.2</v>
+        <v>3498.18</v>
       </c>
     </row>
     <row r="42">
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>18561.05</v>
+        <v>18656.93</v>
       </c>
     </row>
     <row r="43">
@@ -3070,7 +3070,7 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>11600.66</v>
+        <v>11660.58</v>
       </c>
     </row>
     <row r="44">
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>8120.46</v>
+        <v>8162.41</v>
       </c>
     </row>
     <row r="45">
@@ -3192,7 +3192,7 @@
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>4408.92</v>
+        <v>4431.7</v>
       </c>
     </row>
     <row r="46">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>5800.33</v>
+        <v>5830.29</v>
       </c>
     </row>
     <row r="47">
@@ -3314,7 +3314,7 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>8120.46</v>
+        <v>8162.41</v>
       </c>
     </row>
     <row r="48">
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>3480.2</v>
+        <v>3498.18</v>
       </c>
     </row>
     <row r="49">
@@ -3436,7 +3436,7 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2436.14</v>
+        <v>2448.72</v>
       </c>
     </row>
     <row r="50">
@@ -3497,7 +3497,7 @@
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2422.6</v>
+        <v>2435.11</v>
       </c>
     </row>
     <row r="51">
@@ -3558,7 +3558,7 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>34801.98</v>
+        <v>34981.75</v>
       </c>
     </row>
     <row r="52">
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>11600.66</v>
+        <v>11660.58</v>
       </c>
     </row>
     <row r="53">
@@ -3680,7 +3680,7 @@
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>2436.14</v>
+        <v>2448.72</v>
       </c>
     </row>
     <row r="54">
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4640.26</v>
+        <v>4664.23</v>
       </c>
     </row>
     <row r="55">
@@ -3802,7 +3802,7 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>23394.66</v>
+        <v>23515.51</v>
       </c>
     </row>
     <row r="56">
@@ -3863,7 +3863,7 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>34801.98</v>
+        <v>34981.75</v>
       </c>
     </row>
     <row r="57">
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>11554.26</v>
+        <v>11613.94</v>
       </c>
     </row>
     <row r="58">
@@ -3985,7 +3985,7 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>8120.46</v>
+        <v>8086.22</v>
       </c>
     </row>
     <row r="59">
@@ -4046,7 +4046,7 @@
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>3480.2</v>
+        <v>3465.52</v>
       </c>
     </row>
     <row r="60">
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>23201.32</v>
+        <v>23103.49</v>
       </c>
     </row>
     <row r="61">
@@ -4168,7 +4168,7 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>34801.98</v>
+        <v>34655.24</v>
       </c>
     </row>
     <row r="62">
@@ -4229,7 +4229,7 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>2552.14</v>
+        <v>2541.38</v>
       </c>
     </row>
     <row r="63">
@@ -4290,7 +4290,7 @@
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>5800.33</v>
+        <v>5775.87</v>
       </c>
     </row>
     <row r="64">
@@ -4351,7 +4351,7 @@
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>11600.66</v>
+        <v>11551.75</v>
       </c>
     </row>
     <row r="65">
@@ -4412,7 +4412,7 @@
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>2436.14</v>
+        <v>2425.87</v>
       </c>
     </row>
     <row r="66">
@@ -4473,7 +4473,7 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>4037.92</v>
+        <v>4020.89</v>
       </c>
     </row>
     <row r="67">
@@ -4534,7 +4534,7 @@
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>11600.66</v>
+        <v>11551.75</v>
       </c>
     </row>
     <row r="68">
@@ -4595,7 +4595,7 @@
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3480.2</v>
+        <v>3465.52</v>
       </c>
     </row>
     <row r="69">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>4640.26</v>
+        <v>4620.7</v>
       </c>
     </row>
     <row r="70">
@@ -4717,7 +4717,7 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>8120.46</v>
+        <v>8086.22</v>
       </c>
     </row>
     <row r="71">
@@ -4778,7 +4778,7 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>29001.65</v>
+        <v>28879.37</v>
       </c>
     </row>
     <row r="72">
@@ -4839,7 +4839,7 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9241.4</v>
       </c>
     </row>
     <row r="73">
@@ -4900,7 +4900,7 @@
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>3855.34</v>
+        <v>3839.08</v>
       </c>
     </row>
     <row r="74">
@@ -4961,7 +4961,7 @@
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>12542.03</v>
+        <v>12489.15</v>
       </c>
     </row>
     <row r="75">
@@ -5022,7 +5022,7 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>2422.6</v>
+        <v>2412.39</v>
       </c>
     </row>
     <row r="76">
@@ -5083,7 +5083,7 @@
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>2422.6</v>
+        <v>2412.39</v>
       </c>
     </row>
     <row r="77">
@@ -5144,7 +5144,7 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>15080.86</v>
+        <v>15017.27</v>
       </c>
     </row>
     <row r="78">
@@ -5205,7 +5205,7 @@
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>17400.99</v>
+        <v>17327.62</v>
       </c>
     </row>
     <row r="79">
@@ -5266,7 +5266,7 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>8120.46</v>
+        <v>8086.22</v>
       </c>
     </row>
     <row r="80">
@@ -5327,7 +5327,7 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>3480.2</v>
+        <v>3465.52</v>
       </c>
     </row>
     <row r="81">
@@ -5388,7 +5388,7 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>13920.79</v>
+        <v>13862.1</v>
       </c>
     </row>
     <row r="82">
@@ -5449,7 +5449,7 @@
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>29001.65</v>
+        <v>28879.37</v>
       </c>
     </row>
     <row r="83">
@@ -5510,7 +5510,7 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>2552.14</v>
+        <v>2541.38</v>
       </c>
     </row>
     <row r="84">
@@ -5571,7 +5571,7 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>23201.32</v>
+        <v>23103.49</v>
       </c>
     </row>
     <row r="85">
@@ -5632,7 +5632,7 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>10440.59</v>
+        <v>10396.57</v>
       </c>
     </row>
     <row r="86">
@@ -5693,7 +5693,7 @@
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>17400.99</v>
+        <v>17327.62</v>
       </c>
     </row>
     <row r="87">
@@ -5754,7 +5754,7 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>5800.33</v>
+        <v>5775.87</v>
       </c>
     </row>
     <row r="88">
@@ -5815,7 +5815,7 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>23201.32</v>
+        <v>23103.49</v>
       </c>
     </row>
     <row r="89">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>15080.86</v>
+        <v>15017.27</v>
       </c>
     </row>
     <row r="90">
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>8700.49</v>
+        <v>8663.809999999999</v>
       </c>
     </row>
     <row r="91">
@@ -5998,7 +5998,7 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>11600.66</v>
+        <v>11551.75</v>
       </c>
     </row>
     <row r="92">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>8120.46</v>
+        <v>8086.22</v>
       </c>
     </row>
     <row r="93">
@@ -6120,7 +6120,7 @@
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>11136.63</v>
+        <v>11089.68</v>
       </c>
     </row>
     <row r="94">
@@ -6181,7 +6181,7 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>11600.66</v>
+        <v>11551.75</v>
       </c>
     </row>
     <row r="95">
@@ -6242,7 +6242,7 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>45242.57</v>
+        <v>45051.81</v>
       </c>
     </row>
     <row r="96">
@@ -6303,7 +6303,7 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>8120.46</v>
+        <v>8086.22</v>
       </c>
     </row>
     <row r="97">
@@ -6364,7 +6364,7 @@
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>11600.66</v>
+        <v>11551.75</v>
       </c>
     </row>
     <row r="98">
@@ -6425,7 +6425,7 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>4480.02</v>
+        <v>4461.13</v>
       </c>
     </row>
     <row r="99">
@@ -6486,7 +6486,7 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2436.14</v>
+        <v>2425.87</v>
       </c>
     </row>
     <row r="100">
@@ -6547,7 +6547,7 @@
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>8004.45</v>
+        <v>7970.7</v>
       </c>
     </row>
     <row r="101">
@@ -6608,7 +6608,7 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>4524.26</v>
+        <v>4505.18</v>
       </c>
     </row>
     <row r="102">
@@ -6669,7 +6669,7 @@
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>8120.46</v>
+        <v>8086.22</v>
       </c>
     </row>
     <row r="103">
@@ -6730,7 +6730,7 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
-        <v>58003.29</v>
+        <v>57758.73</v>
       </c>
     </row>
     <row r="104">
@@ -6791,7 +6791,7 @@
         </is>
       </c>
       <c r="M104" s="2" t="n">
-        <v>11600.66</v>
+        <v>11551.75</v>
       </c>
     </row>
     <row r="105">
@@ -6852,7 +6852,7 @@
         </is>
       </c>
       <c r="M105" s="2" t="n">
-        <v>4060.23</v>
+        <v>4043.11</v>
       </c>
     </row>
     <row r="106">
@@ -6913,7 +6913,7 @@
         </is>
       </c>
       <c r="M106" s="2" t="n">
-        <v>18561.05</v>
+        <v>18482.79</v>
       </c>
     </row>
     <row r="107">
@@ -6974,7 +6974,7 @@
         </is>
       </c>
       <c r="M107" s="2" t="n">
-        <v>74244.22</v>
+        <v>73931.17</v>
       </c>
     </row>
     <row r="108">
@@ -7035,7 +7035,7 @@
         </is>
       </c>
       <c r="M108" s="2" t="n">
-        <v>2900.16</v>
+        <v>2887.94</v>
       </c>
     </row>
     <row r="109">
@@ -7096,7 +7096,7 @@
         </is>
       </c>
       <c r="M109" s="2" t="n">
-        <v>5800.33</v>
+        <v>5775.87</v>
       </c>
     </row>
     <row r="110">
@@ -7157,7 +7157,7 @@
         </is>
       </c>
       <c r="M110" s="2" t="n">
-        <v>8120.46</v>
+        <v>8086.22</v>
       </c>
     </row>
     <row r="111">
@@ -7218,7 +7218,7 @@
         </is>
       </c>
       <c r="M111" s="2" t="n">
-        <v>20881.19</v>
+        <v>20793.14</v>
       </c>
     </row>
     <row r="112">
@@ -7279,7 +7279,7 @@
         </is>
       </c>
       <c r="M112" s="2" t="n">
-        <v>20881.19</v>
+        <v>20793.14</v>
       </c>
     </row>
     <row r="113">
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="M113" s="2" t="n">
-        <v>8120.46</v>
+        <v>8086.22</v>
       </c>
     </row>
     <row r="114">
@@ -7401,7 +7401,7 @@
         </is>
       </c>
       <c r="M114" s="2" t="n">
-        <v>2465.84</v>
+        <v>2472.61</v>
       </c>
     </row>
     <row r="115">
@@ -7462,7 +7462,7 @@
         </is>
       </c>
       <c r="M115" s="2" t="n">
-        <v>34801.98</v>
+        <v>34897.52</v>
       </c>
     </row>
     <row r="116">
@@ -7523,7 +7523,7 @@
         </is>
       </c>
       <c r="M116" s="2" t="n">
-        <v>2436.14</v>
+        <v>2442.83</v>
       </c>
     </row>
     <row r="117">
@@ -7584,7 +7584,7 @@
         </is>
       </c>
       <c r="M117" s="2" t="n">
-        <v>11600.66</v>
+        <v>11632.51</v>
       </c>
     </row>
     <row r="118">
@@ -7645,7 +7645,7 @@
         </is>
       </c>
       <c r="M118" s="2" t="n">
-        <v>5800.33</v>
+        <v>5816.25</v>
       </c>
     </row>
     <row r="119">
@@ -7706,7 +7706,7 @@
         </is>
       </c>
       <c r="M119" s="2" t="n">
-        <v>45242.57</v>
+        <v>45366.77</v>
       </c>
     </row>
     <row r="120">
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="M120" s="2" t="n">
-        <v>6960.4</v>
+        <v>6979.5</v>
       </c>
     </row>
     <row r="121">
@@ -7828,7 +7828,7 @@
         </is>
       </c>
       <c r="M121" s="2" t="n">
-        <v>5106.61</v>
+        <v>5120.63</v>
       </c>
     </row>
     <row r="122">
@@ -7889,7 +7889,7 @@
         </is>
       </c>
       <c r="M122" s="2" t="n">
-        <v>3480.2</v>
+        <v>3489.75</v>
       </c>
     </row>
     <row r="123">
@@ -7950,7 +7950,7 @@
         </is>
       </c>
       <c r="M123" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9306</v>
       </c>
     </row>
     <row r="124">
@@ -8011,7 +8011,7 @@
         </is>
       </c>
       <c r="M124" s="2" t="n">
-        <v>3480.2</v>
+        <v>3489.75</v>
       </c>
     </row>
     <row r="125">
@@ -8072,7 +8072,7 @@
         </is>
       </c>
       <c r="M125" s="2" t="n">
-        <v>7888.45</v>
+        <v>7910.1</v>
       </c>
     </row>
     <row r="126">
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="M126" s="2" t="n">
-        <v>2436.14</v>
+        <v>2442.83</v>
       </c>
     </row>
     <row r="127">
@@ -8194,7 +8194,7 @@
         </is>
       </c>
       <c r="M127" s="2" t="n">
-        <v>2422.6</v>
+        <v>2429.25</v>
       </c>
     </row>
     <row r="128">
@@ -8255,7 +8255,7 @@
         </is>
       </c>
       <c r="M128" s="2" t="n">
-        <v>2424.54</v>
+        <v>2431.19</v>
       </c>
     </row>
     <row r="129">
@@ -8316,7 +8316,7 @@
         </is>
       </c>
       <c r="M129" s="2" t="n">
-        <v>46402.64</v>
+        <v>46530.02</v>
       </c>
     </row>
     <row r="130">
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="M130" s="2" t="n">
-        <v>6960.4</v>
+        <v>6979.5</v>
       </c>
     </row>
     <row r="131">
@@ -8438,7 +8438,7 @@
         </is>
       </c>
       <c r="M131" s="2" t="n">
-        <v>6960.4</v>
+        <v>6979.5</v>
       </c>
     </row>
     <row r="132">
@@ -8499,7 +8499,7 @@
         </is>
       </c>
       <c r="M132" s="2" t="n">
-        <v>2900.16</v>
+        <v>2908.13</v>
       </c>
     </row>
     <row r="133">
@@ -8560,7 +8560,7 @@
         </is>
       </c>
       <c r="M133" s="2" t="n">
-        <v>8120.46</v>
+        <v>8142.75</v>
       </c>
     </row>
     <row r="134">
@@ -8621,7 +8621,7 @@
         </is>
       </c>
       <c r="M134" s="2" t="n">
-        <v>5800.33</v>
+        <v>5816.25</v>
       </c>
     </row>
     <row r="135">
@@ -8682,7 +8682,7 @@
         </is>
       </c>
       <c r="M135" s="2" t="n">
-        <v>3480.2</v>
+        <v>3489.75</v>
       </c>
     </row>
     <row r="136">
@@ -8743,7 +8743,7 @@
         </is>
       </c>
       <c r="M136" s="2" t="n">
-        <v>5800.33</v>
+        <v>5816.25</v>
       </c>
     </row>
     <row r="137">
@@ -8804,7 +8804,7 @@
         </is>
       </c>
       <c r="M137" s="2" t="n">
-        <v>9267.059999999999</v>
+        <v>9292.5</v>
       </c>
     </row>
     <row r="138">
@@ -8865,7 +8865,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>2552.14</v>
+        <v>2559.15</v>
       </c>
     </row>
     <row r="139">
@@ -8926,7 +8926,7 @@
         </is>
       </c>
       <c r="M139" s="2" t="n">
-        <v>2900.16</v>
+        <v>2908.13</v>
       </c>
     </row>
     <row r="140">
@@ -8987,7 +8987,7 @@
         </is>
       </c>
       <c r="M140" s="2" t="n">
-        <v>4176.24</v>
+        <v>4187.7</v>
       </c>
     </row>
     <row r="141">
@@ -9048,7 +9048,7 @@
         </is>
       </c>
       <c r="M141" s="2" t="n">
-        <v>16240.92</v>
+        <v>16285.51</v>
       </c>
     </row>
     <row r="142">
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="M142" s="2" t="n">
-        <v>3016.17</v>
+        <v>3024.45</v>
       </c>
     </row>
     <row r="143">
@@ -9170,7 +9170,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9306</v>
       </c>
     </row>
     <row r="144">
@@ -9231,7 +9231,7 @@
         </is>
       </c>
       <c r="M144" s="2" t="n">
-        <v>4060.23</v>
+        <v>4071.38</v>
       </c>
     </row>
     <row r="145">
@@ -9292,7 +9292,7 @@
         </is>
       </c>
       <c r="M145" s="2" t="n">
-        <v>5800.33</v>
+        <v>5816.25</v>
       </c>
     </row>
     <row r="146">
@@ -9353,7 +9353,7 @@
         </is>
       </c>
       <c r="M146" s="2" t="n">
-        <v>13920.79</v>
+        <v>13959.01</v>
       </c>
     </row>
     <row r="147">
@@ -9414,7 +9414,7 @@
         </is>
       </c>
       <c r="M147" s="2" t="n">
-        <v>2436.14</v>
+        <v>2442.83</v>
       </c>
     </row>
     <row r="148">
@@ -9475,7 +9475,7 @@
         </is>
       </c>
       <c r="M148" s="2" t="n">
-        <v>2900.16</v>
+        <v>2908.13</v>
       </c>
     </row>
     <row r="149">
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="M149" s="2" t="n">
-        <v>19373.1</v>
+        <v>19549.31</v>
       </c>
     </row>
     <row r="150">
@@ -9597,7 +9597,7 @@
         </is>
       </c>
       <c r="M150" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.85</v>
       </c>
     </row>
     <row r="151">
@@ -9658,7 +9658,7 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>4176.24</v>
+        <v>4214.22</v>
       </c>
     </row>
     <row r="152">
@@ -9719,7 +9719,7 @@
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>5800.33</v>
+        <v>5853.09</v>
       </c>
     </row>
     <row r="153">
@@ -9780,7 +9780,7 @@
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>6496.37</v>
+        <v>6555.46</v>
       </c>
     </row>
     <row r="154">
@@ -9841,7 +9841,7 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>40602.31</v>
+        <v>40971.61</v>
       </c>
     </row>
     <row r="155">
@@ -9902,7 +9902,7 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.85</v>
       </c>
     </row>
     <row r="156">
@@ -9963,7 +9963,7 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>34801.98</v>
+        <v>35118.53</v>
       </c>
     </row>
     <row r="157">
@@ -10024,7 +10024,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>4640.26</v>
+        <v>4682.47</v>
       </c>
     </row>
     <row r="158">
@@ -10085,7 +10085,7 @@
         </is>
       </c>
       <c r="M158" s="2" t="n">
-        <v>2436.14</v>
+        <v>2458.3</v>
       </c>
     </row>
     <row r="159">
@@ -10146,7 +10146,7 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>6960.4</v>
+        <v>7023.71</v>
       </c>
     </row>
     <row r="160">
@@ -10207,7 +10207,7 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>5759.15</v>
+        <v>5811.53</v>
       </c>
     </row>
     <row r="161">
@@ -10268,7 +10268,7 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>16240.92</v>
+        <v>16388.65</v>
       </c>
     </row>
     <row r="162">
@@ -10329,7 +10329,7 @@
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>4060.23</v>
+        <v>4097.16</v>
       </c>
     </row>
     <row r="163">
@@ -10390,7 +10390,7 @@
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>11600.66</v>
+        <v>11706.18</v>
       </c>
     </row>
     <row r="164">
@@ -10451,7 +10451,7 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>4640.26</v>
+        <v>4682.47</v>
       </c>
     </row>
     <row r="165">
@@ -10512,7 +10512,7 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.85</v>
       </c>
     </row>
     <row r="166">
@@ -10573,7 +10573,7 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>2436.14</v>
+        <v>2458.3</v>
       </c>
     </row>
     <row r="167">
@@ -10634,7 +10634,7 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>2900.16</v>
+        <v>2926.54</v>
       </c>
     </row>
     <row r="168">
@@ -10695,7 +10695,7 @@
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>2668.15</v>
+        <v>2692.42</v>
       </c>
     </row>
     <row r="169">
@@ -10756,7 +10756,7 @@
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.85</v>
       </c>
     </row>
     <row r="170">
@@ -10817,7 +10817,7 @@
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>2552.14</v>
+        <v>2575.36</v>
       </c>
     </row>
     <row r="171">
@@ -10878,7 +10878,7 @@
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>11600.66</v>
+        <v>11706.18</v>
       </c>
     </row>
     <row r="172">
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>11600.66</v>
+        <v>11706.18</v>
       </c>
     </row>
     <row r="173">
@@ -11000,7 +11000,7 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>34801.98</v>
+        <v>35118.53</v>
       </c>
     </row>
     <row r="174">
@@ -11061,7 +11061,7 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>11600.66</v>
+        <v>11706.18</v>
       </c>
     </row>
     <row r="175">
@@ -11122,7 +11122,7 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>2482.94</v>
+        <v>2505.53</v>
       </c>
     </row>
     <row r="176">
@@ -11183,7 +11183,7 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.85</v>
       </c>
     </row>
     <row r="177">
@@ -11244,7 +11244,7 @@
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>6960.4</v>
+        <v>7023.71</v>
       </c>
     </row>
     <row r="178">
@@ -11305,7 +11305,7 @@
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>2900.16</v>
+        <v>2926.54</v>
       </c>
     </row>
     <row r="179">
@@ -11366,7 +11366,7 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>17400.99</v>
+        <v>17559.26</v>
       </c>
     </row>
     <row r="180">
@@ -11427,7 +11427,7 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>34801.98</v>
+        <v>35118.53</v>
       </c>
     </row>
     <row r="181">
@@ -11488,7 +11488,7 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>5800.33</v>
+        <v>5853.09</v>
       </c>
     </row>
     <row r="182">
@@ -11549,7 +11549,7 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>9628.549999999999</v>
+        <v>9716.129999999999</v>
       </c>
     </row>
     <row r="183">
@@ -11610,7 +11610,7 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>2436.14</v>
+        <v>2458.3</v>
       </c>
     </row>
     <row r="184">
@@ -11671,7 +11671,7 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>2436.14</v>
+        <v>2458.3</v>
       </c>
     </row>
     <row r="185">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>3016.17</v>
+        <v>3043.61</v>
       </c>
     </row>
     <row r="186">
@@ -11793,7 +11793,7 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>6664.15</v>
+        <v>6724.77</v>
       </c>
     </row>
     <row r="187">
@@ -11854,7 +11854,7 @@
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>33641.91</v>
+        <v>33947.91</v>
       </c>
     </row>
     <row r="188">
@@ -11915,7 +11915,7 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>2436.14</v>
+        <v>2453.1</v>
       </c>
     </row>
     <row r="189">
@@ -11976,7 +11976,7 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>8839.209999999999</v>
+        <v>8900.75</v>
       </c>
     </row>
     <row r="190">
@@ -12037,7 +12037,7 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>2436.14</v>
+        <v>2453.1</v>
       </c>
     </row>
     <row r="191">
@@ -12098,7 +12098,7 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>3480.2</v>
+        <v>3504.43</v>
       </c>
     </row>
     <row r="192">
@@ -12159,7 +12159,7 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>2784.16</v>
+        <v>2803.54</v>
       </c>
     </row>
     <row r="193">
@@ -12220,7 +12220,7 @@
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>23201.32</v>
+        <v>23362.85</v>
       </c>
     </row>
     <row r="194">
@@ -12281,7 +12281,7 @@
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>5800.33</v>
+        <v>5840.71</v>
       </c>
     </row>
     <row r="195">
@@ -12342,7 +12342,7 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>22389.27</v>
+        <v>22545.15</v>
       </c>
     </row>
     <row r="196">
@@ -12403,7 +12403,7 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>13920.79</v>
+        <v>14017.71</v>
       </c>
     </row>
     <row r="197">
@@ -12464,7 +12464,7 @@
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9345.139999999999</v>
       </c>
     </row>
     <row r="198">
@@ -12525,7 +12525,7 @@
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>11600.66</v>
+        <v>11681.42</v>
       </c>
     </row>
     <row r="199">
@@ -12586,7 +12586,7 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>5800.33</v>
+        <v>5840.71</v>
       </c>
     </row>
     <row r="200">
@@ -12647,7 +12647,7 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>2552.14</v>
+        <v>2569.91</v>
       </c>
     </row>
     <row r="201">
@@ -12708,7 +12708,7 @@
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>11600.66</v>
+        <v>11681.42</v>
       </c>
     </row>
     <row r="202">
@@ -12769,7 +12769,7 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>2423.38</v>
+        <v>2440.25</v>
       </c>
     </row>
     <row r="203">
@@ -12830,7 +12830,7 @@
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>2900.16</v>
+        <v>2920.36</v>
       </c>
     </row>
     <row r="204">
@@ -12891,7 +12891,7 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>3480.2</v>
+        <v>3504.43</v>
       </c>
     </row>
     <row r="205">
@@ -12952,7 +12952,7 @@
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9345.139999999999</v>
       </c>
     </row>
     <row r="206">
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>14712.07</v>
+        <v>14814.5</v>
       </c>
     </row>
     <row r="207">
@@ -13074,7 +13074,7 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>24361.38</v>
+        <v>24530.99</v>
       </c>
     </row>
     <row r="208">
@@ -13135,7 +13135,7 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>5684.32</v>
+        <v>5723.9</v>
       </c>
     </row>
     <row r="209">
@@ -13196,7 +13196,7 @@
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>4640.26</v>
+        <v>4672.57</v>
       </c>
     </row>
     <row r="210">
@@ -13257,7 +13257,7 @@
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>4640.26</v>
+        <v>4672.57</v>
       </c>
     </row>
     <row r="211">
@@ -13318,7 +13318,7 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>15080.86</v>
+        <v>15185.85</v>
       </c>
     </row>
     <row r="212">
@@ -13379,7 +13379,7 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>8075.33</v>
+        <v>8131.56</v>
       </c>
     </row>
     <row r="213">
@@ -13440,7 +13440,7 @@
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>7030</v>
+        <v>7078.94</v>
       </c>
     </row>
     <row r="214">
@@ -13501,7 +13501,7 @@
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>11600.66</v>
+        <v>11681.42</v>
       </c>
     </row>
     <row r="215">
@@ -13562,7 +13562,7 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>5220.3</v>
+        <v>5256.64</v>
       </c>
     </row>
     <row r="216">
@@ -13623,7 +13623,7 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>2422.6</v>
+        <v>2439.47</v>
       </c>
     </row>
     <row r="217">
@@ -13684,7 +13684,7 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>2436.14</v>
+        <v>2453.1</v>
       </c>
     </row>
     <row r="218">
@@ -13745,7 +13745,7 @@
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>12522.51</v>
+        <v>12609.69</v>
       </c>
     </row>
     <row r="219">
@@ -13806,7 +13806,7 @@
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>3480.2</v>
+        <v>3504.43</v>
       </c>
     </row>
     <row r="220">
@@ -13867,7 +13867,7 @@
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>3480.2</v>
+        <v>3504.43</v>
       </c>
     </row>
     <row r="221">
@@ -13928,7 +13928,7 @@
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>5238.86</v>
+        <v>5275.33</v>
       </c>
     </row>
     <row r="222">
@@ -13989,7 +13989,7 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>4060.23</v>
+        <v>4086.97</v>
       </c>
     </row>
     <row r="223">
@@ -14050,7 +14050,7 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>2552.14</v>
+        <v>2568.95</v>
       </c>
     </row>
     <row r="224">
@@ -14111,7 +14111,7 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>10629.68</v>
+        <v>10699.69</v>
       </c>
     </row>
     <row r="225">
@@ -14172,7 +14172,7 @@
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>18560.39</v>
+        <v>18682.62</v>
       </c>
     </row>
     <row r="226">
@@ -14233,7 +14233,7 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>16240.92</v>
+        <v>16347.88</v>
       </c>
     </row>
     <row r="227">
@@ -14294,7 +14294,7 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>8932.51</v>
+        <v>8991.34</v>
       </c>
     </row>
     <row r="228">
@@ -14355,7 +14355,7 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>7192.41</v>
+        <v>7239.78</v>
       </c>
     </row>
     <row r="229">
@@ -14416,7 +14416,7 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>2436.14</v>
+        <v>2452.18</v>
       </c>
     </row>
     <row r="230">
@@ -14477,7 +14477,7 @@
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>8120.46</v>
+        <v>8173.94</v>
       </c>
     </row>
     <row r="231">
@@ -14538,7 +14538,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>15080.86</v>
+        <v>15180.18</v>
       </c>
     </row>
     <row r="232">
@@ -14599,7 +14599,7 @@
         </is>
       </c>
       <c r="M232" s="2" t="n">
-        <v>30879.11</v>
+        <v>31082.48</v>
       </c>
     </row>
     <row r="233">
@@ -14660,7 +14660,7 @@
         </is>
       </c>
       <c r="M233" s="2" t="n">
-        <v>2436.14</v>
+        <v>2452.18</v>
       </c>
     </row>
     <row r="234">
@@ -14721,7 +14721,7 @@
         </is>
       </c>
       <c r="M234" s="2" t="n">
-        <v>17400.99</v>
+        <v>17515.59</v>
       </c>
     </row>
     <row r="235">
@@ -14782,7 +14782,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>11600.66</v>
+        <v>11677.06</v>
       </c>
     </row>
     <row r="236">
@@ -14843,7 +14843,7 @@
         </is>
       </c>
       <c r="M236" s="2" t="n">
-        <v>3712.21</v>
+        <v>3736.66</v>
       </c>
     </row>
     <row r="237">
@@ -14904,7 +14904,7 @@
         </is>
       </c>
       <c r="M237" s="2" t="n">
-        <v>5800.33</v>
+        <v>5838.53</v>
       </c>
     </row>
     <row r="238">
@@ -14965,7 +14965,7 @@
         </is>
       </c>
       <c r="M238" s="2" t="n">
-        <v>11600.66</v>
+        <v>11677.06</v>
       </c>
     </row>
     <row r="239">
@@ -15026,7 +15026,7 @@
         </is>
       </c>
       <c r="M239" s="2" t="n">
-        <v>11819.23</v>
+        <v>11897.07</v>
       </c>
     </row>
     <row r="240">
@@ -15087,7 +15087,7 @@
         </is>
       </c>
       <c r="M240" s="2" t="n">
-        <v>29001.65</v>
+        <v>29192.65</v>
       </c>
     </row>
     <row r="241">
@@ -15148,7 +15148,7 @@
         </is>
       </c>
       <c r="M241" s="2" t="n">
-        <v>19334.43</v>
+        <v>19461.76</v>
       </c>
     </row>
     <row r="242">
@@ -15209,7 +15209,7 @@
         </is>
       </c>
       <c r="M242" s="2" t="n">
-        <v>2552.14</v>
+        <v>2568.95</v>
       </c>
     </row>
     <row r="243">
@@ -15270,7 +15270,7 @@
         </is>
       </c>
       <c r="M243" s="2" t="n">
-        <v>2424.54</v>
+        <v>2446.13</v>
       </c>
     </row>
     <row r="244">
@@ -15331,7 +15331,7 @@
         </is>
       </c>
       <c r="M244" s="2" t="n">
-        <v>17400.99</v>
+        <v>17555.97</v>
       </c>
     </row>
     <row r="245">
@@ -15392,7 +15392,7 @@
         </is>
       </c>
       <c r="M245" s="2" t="n">
-        <v>55683.16</v>
+        <v>56179.12</v>
       </c>
     </row>
     <row r="246">
@@ -15453,7 +15453,7 @@
         </is>
       </c>
       <c r="M246" s="2" t="n">
-        <v>7424.42</v>
+        <v>7490.55</v>
       </c>
     </row>
     <row r="247">
@@ -15514,7 +15514,7 @@
         </is>
       </c>
       <c r="M247" s="2" t="n">
-        <v>4561.38</v>
+        <v>4602.01</v>
       </c>
     </row>
     <row r="248">
@@ -15575,7 +15575,7 @@
         </is>
       </c>
       <c r="M248" s="2" t="n">
-        <v>18561.05</v>
+        <v>18726.37</v>
       </c>
     </row>
     <row r="249">
@@ -15636,7 +15636,7 @@
         </is>
       </c>
       <c r="M249" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.19</v>
       </c>
     </row>
     <row r="250">
@@ -15697,7 +15697,7 @@
         </is>
       </c>
       <c r="M250" s="2" t="n">
-        <v>37702.14</v>
+        <v>38037.94</v>
       </c>
     </row>
     <row r="251">
@@ -15758,7 +15758,7 @@
         </is>
       </c>
       <c r="M251" s="2" t="n">
-        <v>11600.66</v>
+        <v>11703.98</v>
       </c>
     </row>
     <row r="252">
@@ -15819,7 +15819,7 @@
         </is>
       </c>
       <c r="M252" s="2" t="n">
-        <v>11600.66</v>
+        <v>11703.98</v>
       </c>
     </row>
     <row r="253">
@@ -15880,7 +15880,7 @@
         </is>
       </c>
       <c r="M253" s="2" t="n">
-        <v>3132.18</v>
+        <v>3160.08</v>
       </c>
     </row>
     <row r="254">
@@ -15941,7 +15941,7 @@
         </is>
       </c>
       <c r="M254" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.19</v>
       </c>
     </row>
     <row r="255">
@@ -16002,7 +16002,7 @@
         </is>
       </c>
       <c r="M255" s="2" t="n">
-        <v>34801.86</v>
+        <v>35111.83</v>
       </c>
     </row>
     <row r="256">
@@ -16063,7 +16063,7 @@
         </is>
       </c>
       <c r="M256" s="2" t="n">
-        <v>2900.16</v>
+        <v>2926</v>
       </c>
     </row>
     <row r="257">
@@ -16124,7 +16124,7 @@
         </is>
       </c>
       <c r="M257" s="2" t="n">
-        <v>25521.45</v>
+        <v>25748.76</v>
       </c>
     </row>
     <row r="258">
@@ -16185,7 +16185,7 @@
         </is>
       </c>
       <c r="M258" s="2" t="n">
-        <v>3480.2</v>
+        <v>3511.19</v>
       </c>
     </row>
     <row r="259">
@@ -16246,7 +16246,7 @@
         </is>
       </c>
       <c r="M259" s="2" t="n">
-        <v>23201.32</v>
+        <v>23407.97</v>
       </c>
     </row>
     <row r="260">
@@ -16307,7 +16307,7 @@
         </is>
       </c>
       <c r="M260" s="2" t="n">
-        <v>4609.27</v>
+        <v>4650.32</v>
       </c>
     </row>
     <row r="261">
@@ -16368,7 +16368,7 @@
         </is>
       </c>
       <c r="M261" s="2" t="n">
-        <v>10491.64</v>
+        <v>10585.08</v>
       </c>
     </row>
     <row r="262">
@@ -16429,7 +16429,7 @@
         </is>
       </c>
       <c r="M262" s="2" t="n">
-        <v>23201.32</v>
+        <v>23407.97</v>
       </c>
     </row>
     <row r="263">
@@ -16490,7 +16490,7 @@
         </is>
       </c>
       <c r="M263" s="2" t="n">
-        <v>10440.59</v>
+        <v>10533.58</v>
       </c>
     </row>
     <row r="264">
@@ -16551,7 +16551,7 @@
         </is>
       </c>
       <c r="M264" s="2" t="n">
-        <v>34801.98</v>
+        <v>35111.95</v>
       </c>
     </row>
     <row r="265">
@@ -16612,7 +16612,7 @@
         </is>
       </c>
       <c r="M265" s="2" t="n">
-        <v>8136.7</v>
+        <v>8209.17</v>
       </c>
     </row>
     <row r="266">
@@ -16673,7 +16673,7 @@
         </is>
       </c>
       <c r="M266" s="2" t="n">
-        <v>6960.4</v>
+        <v>7022.39</v>
       </c>
     </row>
     <row r="267">
@@ -16734,7 +16734,7 @@
         </is>
       </c>
       <c r="M267" s="2" t="n">
-        <v>24832.37</v>
+        <v>25053.55</v>
       </c>
     </row>
     <row r="268">
@@ -16795,7 +16795,7 @@
         </is>
       </c>
       <c r="M268" s="2" t="n">
-        <v>4640.26</v>
+        <v>4681.59</v>
       </c>
     </row>
     <row r="269">
@@ -16856,7 +16856,7 @@
         </is>
       </c>
       <c r="M269" s="2" t="n">
-        <v>11600.66</v>
+        <v>11580.78</v>
       </c>
     </row>
     <row r="270">
@@ -16917,7 +16917,7 @@
         </is>
       </c>
       <c r="M270" s="2" t="n">
-        <v>6960.4</v>
+        <v>6948.47</v>
       </c>
     </row>
     <row r="271">
@@ -16978,7 +16978,7 @@
         </is>
       </c>
       <c r="M271" s="2" t="n">
-        <v>2668.15</v>
+        <v>2663.58</v>
       </c>
     </row>
     <row r="272">
@@ -17039,7 +17039,7 @@
         </is>
       </c>
       <c r="M272" s="2" t="n">
-        <v>16240.92</v>
+        <v>16213.09</v>
       </c>
     </row>
     <row r="273">
@@ -17100,7 +17100,7 @@
         </is>
       </c>
       <c r="M273" s="2" t="n">
-        <v>13920.79</v>
+        <v>13896.93</v>
       </c>
     </row>
     <row r="274">
@@ -17161,7 +17161,7 @@
         </is>
       </c>
       <c r="M274" s="2" t="n">
-        <v>23201.32</v>
+        <v>23161.55</v>
       </c>
     </row>
     <row r="275">
@@ -17222,7 +17222,7 @@
         </is>
       </c>
       <c r="M275" s="2" t="n">
-        <v>23201.32</v>
+        <v>23161.55</v>
       </c>
     </row>
     <row r="276">
@@ -17283,7 +17283,7 @@
         </is>
       </c>
       <c r="M276" s="2" t="n">
-        <v>14848.84</v>
+        <v>14823.39</v>
       </c>
     </row>
     <row r="277">
@@ -17344,7 +17344,7 @@
         </is>
       </c>
       <c r="M277" s="2" t="n">
-        <v>6960.4</v>
+        <v>6948.47</v>
       </c>
     </row>
     <row r="278">
@@ -17405,7 +17405,7 @@
         </is>
       </c>
       <c r="M278" s="2" t="n">
-        <v>2436.14</v>
+        <v>2431.96</v>
       </c>
     </row>
     <row r="279">
@@ -17466,7 +17466,7 @@
         </is>
       </c>
       <c r="M279" s="2" t="n">
-        <v>3480.2</v>
+        <v>3474.23</v>
       </c>
     </row>
     <row r="280">
@@ -17527,7 +17527,7 @@
         </is>
       </c>
       <c r="M280" s="2" t="n">
-        <v>5707.52</v>
+        <v>5697.74</v>
       </c>
     </row>
     <row r="281">
@@ -17588,7 +17588,7 @@
         </is>
       </c>
       <c r="M281" s="2" t="n">
-        <v>11600.66</v>
+        <v>11580.78</v>
       </c>
     </row>
     <row r="282">
@@ -17649,7 +17649,7 @@
         </is>
       </c>
       <c r="M282" s="2" t="n">
-        <v>58003.29</v>
+        <v>57903.88</v>
       </c>
     </row>
     <row r="283">
@@ -17710,7 +17710,7 @@
         </is>
       </c>
       <c r="M283" s="2" t="n">
-        <v>24361.38</v>
+        <v>24319.63</v>
       </c>
     </row>
     <row r="284">
@@ -17771,7 +17771,7 @@
         </is>
       </c>
       <c r="M284" s="2" t="n">
-        <v>58003.29</v>
+        <v>57903.88</v>
       </c>
     </row>
     <row r="285">
@@ -17832,7 +17832,7 @@
         </is>
       </c>
       <c r="M285" s="2" t="n">
-        <v>10440.59</v>
+        <v>10422.7</v>
       </c>
     </row>
     <row r="286">
@@ -17893,7 +17893,7 @@
         </is>
       </c>
       <c r="M286" s="2" t="n">
-        <v>26681.52</v>
+        <v>26635.78</v>
       </c>
     </row>
     <row r="287">
@@ -17954,7 +17954,7 @@
         </is>
       </c>
       <c r="M287" s="2" t="n">
-        <v>31321.78</v>
+        <v>31268.09</v>
       </c>
     </row>
     <row r="288">
@@ -18015,7 +18015,7 @@
         </is>
       </c>
       <c r="M288" s="2" t="n">
-        <v>3402.95</v>
+        <v>3397.11</v>
       </c>
     </row>
     <row r="289">
@@ -18076,7 +18076,7 @@
         </is>
       </c>
       <c r="M289" s="2" t="n">
-        <v>2422.6</v>
+        <v>2418.45</v>
       </c>
     </row>
     <row r="290">
@@ -18137,7 +18137,7 @@
         </is>
       </c>
       <c r="M290" s="2" t="n">
-        <v>2436.14</v>
+        <v>2431.96</v>
       </c>
     </row>
     <row r="291">
@@ -18198,7 +18198,7 @@
         </is>
       </c>
       <c r="M291" s="2" t="n">
-        <v>23201.32</v>
+        <v>23161.55</v>
       </c>
     </row>
     <row r="292">
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="M292" s="2" t="n">
-        <v>5800.33</v>
+        <v>5790.39</v>
       </c>
     </row>
     <row r="293">
@@ -18320,7 +18320,7 @@
         </is>
       </c>
       <c r="M293" s="2" t="n">
-        <v>29269.24</v>
+        <v>29219.08</v>
       </c>
     </row>
     <row r="294">
@@ -18381,7 +18381,7 @@
         </is>
       </c>
       <c r="M294" s="2" t="n">
-        <v>5220.3</v>
+        <v>5211.35</v>
       </c>
     </row>
     <row r="295">
@@ -18442,7 +18442,7 @@
         </is>
       </c>
       <c r="M295" s="2" t="n">
-        <v>5628.7</v>
+        <v>5619.05</v>
       </c>
     </row>
     <row r="296">
@@ -18503,7 +18503,7 @@
         </is>
       </c>
       <c r="M296" s="2" t="n">
-        <v>2552.14</v>
+        <v>2547.77</v>
       </c>
     </row>
     <row r="297">
@@ -18564,7 +18564,7 @@
         </is>
       </c>
       <c r="M297" s="2" t="n">
-        <v>23201.32</v>
+        <v>23161.55</v>
       </c>
     </row>
     <row r="298">
@@ -18625,7 +18625,7 @@
         </is>
       </c>
       <c r="M298" s="2" t="n">
-        <v>3480.2</v>
+        <v>3474.23</v>
       </c>
     </row>
     <row r="299">
@@ -18686,7 +18686,7 @@
         </is>
       </c>
       <c r="M299" s="2" t="n">
-        <v>5800.33</v>
+        <v>5790.39</v>
       </c>
     </row>
     <row r="300">
@@ -18747,7 +18747,7 @@
         </is>
       </c>
       <c r="M300" s="2" t="n">
-        <v>11600.66</v>
+        <v>11588.69</v>
       </c>
     </row>
     <row r="301">
@@ -18808,7 +18808,7 @@
         </is>
       </c>
       <c r="M301" s="2" t="n">
-        <v>2579.78</v>
+        <v>2577.12</v>
       </c>
     </row>
     <row r="302">
@@ -18869,7 +18869,7 @@
         </is>
       </c>
       <c r="M302" s="2" t="n">
-        <v>6960.4</v>
+        <v>6953.22</v>
       </c>
     </row>
     <row r="303">
@@ -18930,7 +18930,7 @@
         </is>
       </c>
       <c r="M303" s="2" t="n">
-        <v>2900.16</v>
+        <v>2897.17</v>
       </c>
     </row>
     <row r="304">
@@ -18991,7 +18991,7 @@
         </is>
       </c>
       <c r="M304" s="2" t="n">
-        <v>23201.32</v>
+        <v>23177.39</v>
       </c>
     </row>
     <row r="305">
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="M305" s="2" t="n">
-        <v>11600.66</v>
+        <v>11588.69</v>
       </c>
     </row>
     <row r="306">
@@ -19113,7 +19113,7 @@
         </is>
       </c>
       <c r="M306" s="2" t="n">
-        <v>4640.26</v>
+        <v>4635.48</v>
       </c>
     </row>
     <row r="307">
@@ -19174,7 +19174,7 @@
         </is>
       </c>
       <c r="M307" s="2" t="n">
-        <v>2436.14</v>
+        <v>2433.63</v>
       </c>
     </row>
     <row r="308">
@@ -19235,7 +19235,7 @@
         </is>
       </c>
       <c r="M308" s="2" t="n">
-        <v>2436.14</v>
+        <v>2433.63</v>
       </c>
     </row>
     <row r="309">
@@ -19296,7 +19296,7 @@
         </is>
       </c>
       <c r="M309" s="2" t="n">
-        <v>4640.03</v>
+        <v>4635.25</v>
       </c>
     </row>
     <row r="310">
@@ -19357,7 +19357,7 @@
         </is>
       </c>
       <c r="M310" s="2" t="n">
-        <v>2900.16</v>
+        <v>2897.17</v>
       </c>
     </row>
     <row r="311">
@@ -19418,7 +19418,7 @@
         </is>
       </c>
       <c r="M311" s="2" t="n">
-        <v>2552.14</v>
+        <v>2549.51</v>
       </c>
     </row>
     <row r="312">
@@ -19479,7 +19479,7 @@
         </is>
       </c>
       <c r="M312" s="2" t="n">
-        <v>11600.66</v>
+        <v>11588.69</v>
       </c>
     </row>
     <row r="313">
@@ -19540,7 +19540,7 @@
         </is>
       </c>
       <c r="M313" s="2" t="n">
-        <v>6960.4</v>
+        <v>6953.22</v>
       </c>
     </row>
     <row r="314">
@@ -19601,7 +19601,7 @@
         </is>
       </c>
       <c r="M314" s="2" t="n">
-        <v>5800.33</v>
+        <v>5794.35</v>
       </c>
     </row>
     <row r="315">
@@ -19662,7 +19662,7 @@
         </is>
       </c>
       <c r="M315" s="2" t="n">
-        <v>2668.15</v>
+        <v>2665.4</v>
       </c>
     </row>
     <row r="316">
@@ -19723,7 +19723,7 @@
         </is>
       </c>
       <c r="M316" s="2" t="n">
-        <v>10440.59</v>
+        <v>10429.82</v>
       </c>
     </row>
     <row r="317">
@@ -19784,7 +19784,7 @@
         </is>
       </c>
       <c r="M317" s="2" t="n">
-        <v>2922.63</v>
+        <v>2919.62</v>
       </c>
     </row>
     <row r="318">
@@ -19845,7 +19845,7 @@
         </is>
       </c>
       <c r="M318" s="2" t="n">
-        <v>2900.16</v>
+        <v>2897.17</v>
       </c>
     </row>
     <row r="319">
@@ -19906,7 +19906,7 @@
         </is>
       </c>
       <c r="M319" s="2" t="n">
-        <v>39442.24</v>
+        <v>39401.56</v>
       </c>
     </row>
     <row r="320">
@@ -19967,7 +19967,7 @@
         </is>
       </c>
       <c r="M320" s="2" t="n">
-        <v>13920.79</v>
+        <v>13906.43</v>
       </c>
     </row>
     <row r="321">
@@ -20028,7 +20028,7 @@
         </is>
       </c>
       <c r="M321" s="2" t="n">
-        <v>3016.17</v>
+        <v>3013.06</v>
       </c>
     </row>
     <row r="322">
@@ -20089,7 +20089,7 @@
         </is>
       </c>
       <c r="M322" s="2" t="n">
-        <v>2784.08</v>
+        <v>2781.21</v>
       </c>
     </row>
     <row r="323">
@@ -20150,7 +20150,7 @@
         </is>
       </c>
       <c r="M323" s="2" t="n">
-        <v>5799.23</v>
+        <v>5793.25</v>
       </c>
     </row>
     <row r="324">
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="M324" s="2" t="n">
-        <v>15080.86</v>
+        <v>15065.3</v>
       </c>
     </row>
     <row r="325">
@@ -20272,7 +20272,7 @@
         </is>
       </c>
       <c r="M325" s="2" t="n">
-        <v>4640.26</v>
+        <v>4607.02</v>
       </c>
     </row>
     <row r="326">
@@ -20333,7 +20333,7 @@
         </is>
       </c>
       <c r="M326" s="2" t="n">
-        <v>5800.33</v>
+        <v>5758.78</v>
       </c>
     </row>
     <row r="327">
@@ -20394,7 +20394,7 @@
         </is>
       </c>
       <c r="M327" s="2" t="n">
-        <v>4640.26</v>
+        <v>4607.02</v>
       </c>
     </row>
     <row r="328">
@@ -20455,7 +20455,7 @@
         </is>
       </c>
       <c r="M328" s="2" t="n">
-        <v>3480.2</v>
+        <v>3455.27</v>
       </c>
     </row>
     <row r="329">
@@ -20516,7 +20516,7 @@
         </is>
       </c>
       <c r="M329" s="2" t="n">
-        <v>13920.79</v>
+        <v>13821.06</v>
       </c>
     </row>
     <row r="330">
@@ -20577,7 +20577,7 @@
         </is>
       </c>
       <c r="M330" s="2" t="n">
-        <v>10672.61</v>
+        <v>10596.15</v>
       </c>
     </row>
     <row r="331">
@@ -20638,7 +20638,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>2668.15</v>
+        <v>2649.04</v>
       </c>
     </row>
     <row r="332">
@@ -20699,7 +20699,7 @@
         </is>
       </c>
       <c r="M332" s="2" t="n">
-        <v>4141.44</v>
+        <v>4111.77</v>
       </c>
     </row>
     <row r="333">
@@ -20760,7 +20760,7 @@
         </is>
       </c>
       <c r="M333" s="2" t="n">
-        <v>2900.16</v>
+        <v>2879.39</v>
       </c>
     </row>
     <row r="334">
@@ -20821,7 +20821,7 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>9497.58</v>
+        <v>9429.540000000001</v>
       </c>
     </row>
     <row r="335">
@@ -20882,7 +20882,7 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>4640.26</v>
+        <v>4607.02</v>
       </c>
     </row>
     <row r="336">
@@ -20943,7 +20943,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>3480.2</v>
+        <v>3455.27</v>
       </c>
     </row>
     <row r="337">
@@ -21004,7 +21004,7 @@
         </is>
       </c>
       <c r="M337" s="2" t="n">
-        <v>41414.35</v>
+        <v>41117.66</v>
       </c>
     </row>
     <row r="338">
@@ -21065,7 +21065,7 @@
         </is>
       </c>
       <c r="M338" s="2" t="n">
-        <v>3596.2</v>
+        <v>3570.44</v>
       </c>
     </row>
     <row r="339">
@@ -21126,7 +21126,7 @@
         </is>
       </c>
       <c r="M339" s="2" t="n">
-        <v>2423.38</v>
+        <v>2406.02</v>
       </c>
     </row>
     <row r="340">
@@ -21187,7 +21187,7 @@
         </is>
       </c>
       <c r="M340" s="2" t="n">
-        <v>2422.6</v>
+        <v>2405.25</v>
       </c>
     </row>
     <row r="341">
@@ -21248,7 +21248,7 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3596.2</v>
+        <v>3570.44</v>
       </c>
     </row>
     <row r="342">
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>6960.4</v>
+        <v>6910.53</v>
       </c>
     </row>
     <row r="343">
@@ -21370,7 +21370,7 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>26919.33</v>
+        <v>26726.48</v>
       </c>
     </row>
     <row r="344">
@@ -21431,7 +21431,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>5568.32</v>
+        <v>5528.43</v>
       </c>
     </row>
     <row r="345">
@@ -21492,7 +21492,7 @@
         </is>
       </c>
       <c r="M345" s="2" t="n">
-        <v>8004.45</v>
+        <v>7947.11</v>
       </c>
     </row>
     <row r="346">
@@ -21553,7 +21553,7 @@
         </is>
       </c>
       <c r="M346" s="2" t="n">
-        <v>2436.14</v>
+        <v>2418.69</v>
       </c>
     </row>
     <row r="347">
@@ -21614,7 +21614,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>12644.72</v>
+        <v>12554.13</v>
       </c>
     </row>
     <row r="348">
@@ -21675,7 +21675,7 @@
         </is>
       </c>
       <c r="M348" s="2" t="n">
-        <v>2436.14</v>
+        <v>2418.69</v>
       </c>
     </row>
     <row r="349">
@@ -21736,7 +21736,7 @@
         </is>
       </c>
       <c r="M349" s="2" t="n">
-        <v>4060.23</v>
+        <v>4031.14</v>
       </c>
     </row>
     <row r="350">
@@ -21797,7 +21797,7 @@
         </is>
       </c>
       <c r="M350" s="2" t="n">
-        <v>11600.66</v>
+        <v>11517.55</v>
       </c>
     </row>
     <row r="351">
@@ -21858,7 +21858,7 @@
         </is>
       </c>
       <c r="M351" s="2" t="n">
-        <v>11553.38</v>
+        <v>11470.61</v>
       </c>
     </row>
     <row r="352">
@@ -21919,7 +21919,7 @@
         </is>
       </c>
       <c r="M352" s="2" t="n">
-        <v>13398.76</v>
+        <v>13302.77</v>
       </c>
     </row>
     <row r="353">
@@ -21980,7 +21980,7 @@
         </is>
       </c>
       <c r="M353" s="2" t="n">
-        <v>17203.76</v>
+        <v>17080.51</v>
       </c>
     </row>
     <row r="354">
@@ -22041,7 +22041,7 @@
         </is>
       </c>
       <c r="M354" s="2" t="n">
-        <v>6960.4</v>
+        <v>6910.53</v>
       </c>
     </row>
     <row r="355">
@@ -22102,7 +22102,7 @@
         </is>
       </c>
       <c r="M355" s="2" t="n">
-        <v>3480.2</v>
+        <v>3475.08</v>
       </c>
     </row>
     <row r="356">
@@ -22163,7 +22163,7 @@
         </is>
       </c>
       <c r="M356" s="2" t="n">
-        <v>11600.66</v>
+        <v>11583.59</v>
       </c>
     </row>
     <row r="357">
@@ -22224,7 +22224,7 @@
         </is>
       </c>
       <c r="M357" s="2" t="n">
-        <v>80044.55</v>
+        <v>79926.78999999999</v>
       </c>
     </row>
     <row r="358">
@@ -22285,7 +22285,7 @@
         </is>
       </c>
       <c r="M358" s="2" t="n">
-        <v>8136.7</v>
+        <v>8124.73</v>
       </c>
     </row>
     <row r="359">
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="M359" s="2" t="n">
-        <v>2587.24</v>
+        <v>2583.43</v>
       </c>
     </row>
     <row r="360">
@@ -22407,7 +22407,7 @@
         </is>
       </c>
       <c r="M360" s="2" t="n">
-        <v>5510.31</v>
+        <v>5502.21</v>
       </c>
     </row>
     <row r="361">
@@ -22468,7 +22468,7 @@
         </is>
       </c>
       <c r="M361" s="2" t="n">
-        <v>5728.87</v>
+        <v>5720.44</v>
       </c>
     </row>
     <row r="362">
@@ -22529,7 +22529,7 @@
         </is>
       </c>
       <c r="M362" s="2" t="n">
-        <v>3248.18</v>
+        <v>3243.41</v>
       </c>
     </row>
     <row r="363">
@@ -22590,7 +22590,7 @@
         </is>
       </c>
       <c r="M363" s="2" t="n">
-        <v>2436.14</v>
+        <v>2432.55</v>
       </c>
     </row>
     <row r="364">
@@ -22651,7 +22651,7 @@
         </is>
       </c>
       <c r="M364" s="2" t="n">
-        <v>4640.26</v>
+        <v>4633.44</v>
       </c>
     </row>
     <row r="365">
@@ -22712,7 +22712,7 @@
         </is>
       </c>
       <c r="M365" s="2" t="n">
-        <v>19721.12</v>
+        <v>19692.11</v>
       </c>
     </row>
     <row r="366">
@@ -22773,7 +22773,7 @@
         </is>
       </c>
       <c r="M366" s="2" t="n">
-        <v>2900.16</v>
+        <v>2895.9</v>
       </c>
     </row>
     <row r="367">
@@ -22834,7 +22834,7 @@
         </is>
       </c>
       <c r="M367" s="2" t="n">
-        <v>11600.66</v>
+        <v>11583.59</v>
       </c>
     </row>
     <row r="368">
@@ -22895,7 +22895,7 @@
         </is>
       </c>
       <c r="M368" s="2" t="n">
-        <v>11600.66</v>
+        <v>11583.59</v>
       </c>
     </row>
     <row r="369">
@@ -22956,7 +22956,7 @@
         </is>
       </c>
       <c r="M369" s="2" t="n">
-        <v>6960.4</v>
+        <v>6950.16</v>
       </c>
     </row>
     <row r="370">
@@ -23017,7 +23017,7 @@
         </is>
       </c>
       <c r="M370" s="2" t="n">
-        <v>5800.33</v>
+        <v>5791.8</v>
       </c>
     </row>
     <row r="371">
@@ -23078,7 +23078,7 @@
         </is>
       </c>
       <c r="M371" s="2" t="n">
-        <v>2451.86</v>
+        <v>2448.25</v>
       </c>
     </row>
     <row r="372">
@@ -23139,7 +23139,7 @@
         </is>
       </c>
       <c r="M372" s="2" t="n">
-        <v>37122.11</v>
+        <v>37067.5</v>
       </c>
     </row>
     <row r="373">
@@ -23200,7 +23200,7 @@
         </is>
       </c>
       <c r="M373" s="2" t="n">
-        <v>3248.18</v>
+        <v>3243.41</v>
       </c>
     </row>
     <row r="374">
@@ -23261,7 +23261,7 @@
         </is>
       </c>
       <c r="M374" s="2" t="n">
-        <v>3480.2</v>
+        <v>3475.08</v>
       </c>
     </row>
     <row r="375">
@@ -23322,7 +23322,7 @@
         </is>
       </c>
       <c r="M375" s="2" t="n">
-        <v>5800.33</v>
+        <v>5791.8</v>
       </c>
     </row>
     <row r="376">
@@ -23383,7 +23383,7 @@
         </is>
       </c>
       <c r="M376" s="2" t="n">
-        <v>80352.37</v>
+        <v>80234.16</v>
       </c>
     </row>
     <row r="377">
@@ -23444,7 +23444,7 @@
         </is>
       </c>
       <c r="M377" s="2" t="n">
-        <v>3248.18</v>
+        <v>3243.41</v>
       </c>
     </row>
     <row r="378">
@@ -23505,7 +23505,7 @@
         </is>
       </c>
       <c r="M378" s="2" t="n">
-        <v>5800.33</v>
+        <v>5768.74</v>
       </c>
     </row>
     <row r="379">
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="M379" s="2" t="n">
-        <v>9233.9</v>
+        <v>9183.610000000001</v>
       </c>
     </row>
     <row r="380">
@@ -23627,7 +23627,7 @@
         </is>
       </c>
       <c r="M380" s="2" t="n">
-        <v>2784.16</v>
+        <v>2769</v>
       </c>
     </row>
     <row r="381">
@@ -23688,7 +23688,7 @@
         </is>
       </c>
       <c r="M381" s="2" t="n">
-        <v>2436.14</v>
+        <v>2422.87</v>
       </c>
     </row>
     <row r="382">
@@ -23749,7 +23749,7 @@
         </is>
       </c>
       <c r="M382" s="2" t="n">
-        <v>13340.76</v>
+        <v>13268.11</v>
       </c>
     </row>
     <row r="383">
@@ -23810,7 +23810,7 @@
         </is>
       </c>
       <c r="M383" s="2" t="n">
-        <v>2900.16</v>
+        <v>2884.37</v>
       </c>
     </row>
     <row r="384">
@@ -23871,7 +23871,7 @@
         </is>
       </c>
       <c r="M384" s="2" t="n">
-        <v>4640.26</v>
+        <v>4614.99</v>
       </c>
     </row>
     <row r="385">
@@ -23932,7 +23932,7 @@
         </is>
       </c>
       <c r="M385" s="2" t="n">
-        <v>19503.59</v>
+        <v>19397.38</v>
       </c>
     </row>
     <row r="386">
@@ -23993,7 +23993,7 @@
         </is>
       </c>
       <c r="M386" s="2" t="n">
-        <v>17576.41</v>
+        <v>17480.69</v>
       </c>
     </row>
     <row r="387">
@@ -24054,7 +24054,7 @@
         </is>
       </c>
       <c r="M387" s="2" t="n">
-        <v>32638.45</v>
+        <v>32460.71</v>
       </c>
     </row>
     <row r="388">
@@ -24115,7 +24115,7 @@
         </is>
       </c>
       <c r="M388" s="2" t="n">
-        <v>2436.14</v>
+        <v>2422.87</v>
       </c>
     </row>
     <row r="389">
@@ -24176,7 +24176,7 @@
         </is>
       </c>
       <c r="M389" s="2" t="n">
-        <v>17400.99</v>
+        <v>17306.23</v>
       </c>
     </row>
     <row r="390">
@@ -24237,7 +24237,7 @@
         </is>
       </c>
       <c r="M390" s="2" t="n">
-        <v>2552.14</v>
+        <v>2538.25</v>
       </c>
     </row>
     <row r="391">
@@ -24298,7 +24298,7 @@
         </is>
       </c>
       <c r="M391" s="2" t="n">
-        <v>5800.33</v>
+        <v>5768.74</v>
       </c>
     </row>
     <row r="392">
@@ -24359,7 +24359,7 @@
         </is>
       </c>
       <c r="M392" s="2" t="n">
-        <v>5800.33</v>
+        <v>5768.74</v>
       </c>
     </row>
     <row r="393">
@@ -24420,7 +24420,7 @@
         </is>
       </c>
       <c r="M393" s="2" t="n">
-        <v>3480.2</v>
+        <v>3461.25</v>
       </c>
     </row>
     <row r="394">
@@ -24481,7 +24481,7 @@
         </is>
       </c>
       <c r="M394" s="2" t="n">
-        <v>6960.4</v>
+        <v>6922.49</v>
       </c>
     </row>
     <row r="395">
@@ -24542,7 +24542,7 @@
         </is>
       </c>
       <c r="M395" s="2" t="n">
-        <v>2961.22</v>
+        <v>2945.1</v>
       </c>
     </row>
     <row r="396">
@@ -24603,7 +24603,7 @@
         </is>
       </c>
       <c r="M396" s="2" t="n">
-        <v>2734.23</v>
+        <v>2719.34</v>
       </c>
     </row>
     <row r="397">
@@ -24664,7 +24664,7 @@
         </is>
       </c>
       <c r="M397" s="2" t="n">
-        <v>2436.14</v>
+        <v>2422.87</v>
       </c>
     </row>
     <row r="398">
@@ -24725,7 +24725,7 @@
         </is>
       </c>
       <c r="M398" s="2" t="n">
-        <v>2436.14</v>
+        <v>2422.87</v>
       </c>
     </row>
     <row r="399">
@@ -24786,7 +24786,7 @@
         </is>
       </c>
       <c r="M399" s="2" t="n">
-        <v>20881.19</v>
+        <v>20767.47</v>
       </c>
     </row>
     <row r="400">
@@ -24847,7 +24847,7 @@
         </is>
       </c>
       <c r="M400" s="2" t="n">
-        <v>6960.4</v>
+        <v>6922.49</v>
       </c>
     </row>
     <row r="401">
@@ -24908,7 +24908,7 @@
         </is>
       </c>
       <c r="M401" s="2" t="n">
-        <v>3480.2</v>
+        <v>3461.25</v>
       </c>
     </row>
     <row r="402">
@@ -24969,7 +24969,7 @@
         </is>
       </c>
       <c r="M402" s="2" t="n">
-        <v>25521.45</v>
+        <v>25382.47</v>
       </c>
     </row>
     <row r="403">
@@ -25030,7 +25030,7 @@
         </is>
       </c>
       <c r="M403" s="2" t="n">
-        <v>3480.2</v>
+        <v>3461.25</v>
       </c>
     </row>
     <row r="404">
@@ -25091,7 +25091,7 @@
         </is>
       </c>
       <c r="M404" s="2" t="n">
-        <v>51042.9</v>
+        <v>50742.1</v>
       </c>
     </row>
     <row r="405">
@@ -25152,7 +25152,7 @@
         </is>
       </c>
       <c r="M405" s="2" t="n">
-        <v>58003.29</v>
+        <v>57661.48</v>
       </c>
     </row>
     <row r="406">
@@ -25213,7 +25213,7 @@
         </is>
       </c>
       <c r="M406" s="2" t="n">
-        <v>5800.33</v>
+        <v>5766.15</v>
       </c>
     </row>
     <row r="407">
@@ -25274,7 +25274,7 @@
         </is>
       </c>
       <c r="M407" s="2" t="n">
-        <v>5800.33</v>
+        <v>5766.15</v>
       </c>
     </row>
     <row r="408">
@@ -25335,7 +25335,7 @@
         </is>
       </c>
       <c r="M408" s="2" t="n">
-        <v>69603.95</v>
+        <v>69193.78</v>
       </c>
     </row>
     <row r="409">
@@ -25396,7 +25396,7 @@
         </is>
       </c>
       <c r="M409" s="2" t="n">
-        <v>23201.32</v>
+        <v>23064.59</v>
       </c>
     </row>
     <row r="410">
@@ -25457,7 +25457,7 @@
         </is>
       </c>
       <c r="M410" s="2" t="n">
-        <v>11600.66</v>
+        <v>11532.3</v>
       </c>
     </row>
     <row r="411">
@@ -25518,7 +25518,7 @@
         </is>
       </c>
       <c r="M411" s="2" t="n">
-        <v>8120.46</v>
+        <v>8072.61</v>
       </c>
     </row>
     <row r="412">
@@ -25579,7 +25579,7 @@
         </is>
       </c>
       <c r="M412" s="2" t="n">
-        <v>4640.26</v>
+        <v>4612.92</v>
       </c>
     </row>
     <row r="413">
@@ -25640,7 +25640,7 @@
         </is>
       </c>
       <c r="M413" s="2" t="n">
-        <v>8120.46</v>
+        <v>8072.61</v>
       </c>
     </row>
     <row r="414">
@@ -25701,7 +25701,7 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>10317.63</v>
+        <v>10256.82</v>
       </c>
     </row>
     <row r="415">
@@ -25762,7 +25762,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>4820.07</v>
+        <v>4791.67</v>
       </c>
     </row>
     <row r="416">
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="M416" s="2" t="n">
-        <v>6960.4</v>
+        <v>6919.38</v>
       </c>
     </row>
     <row r="417">
@@ -25884,7 +25884,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>19721.12</v>
+        <v>19604.9</v>
       </c>
     </row>
     <row r="418">
@@ -25945,7 +25945,7 @@
         </is>
       </c>
       <c r="M418" s="2" t="n">
-        <v>4640.26</v>
+        <v>4612.92</v>
       </c>
     </row>
     <row r="419">
@@ -26006,7 +26006,7 @@
         </is>
       </c>
       <c r="M419" s="2" t="n">
-        <v>2436.14</v>
+        <v>2421.78</v>
       </c>
     </row>
     <row r="420">
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="M420" s="2" t="n">
-        <v>34801.98</v>
+        <v>34596.89</v>
       </c>
     </row>
     <row r="421">
@@ -26128,7 +26128,7 @@
         </is>
       </c>
       <c r="M421" s="2" t="n">
-        <v>5800.33</v>
+        <v>5766.15</v>
       </c>
     </row>
     <row r="422">
@@ -26189,7 +26189,7 @@
         </is>
       </c>
       <c r="M422" s="2" t="n">
-        <v>4988.28</v>
+        <v>4958.89</v>
       </c>
     </row>
     <row r="423">
@@ -26250,7 +26250,7 @@
         </is>
       </c>
       <c r="M423" s="2" t="n">
-        <v>2436.14</v>
+        <v>2421.78</v>
       </c>
     </row>
     <row r="424">
@@ -26311,7 +26311,7 @@
         </is>
       </c>
       <c r="M424" s="2" t="n">
-        <v>13920.79</v>
+        <v>13838.76</v>
       </c>
     </row>
     <row r="425">
@@ -26372,7 +26372,7 @@
         </is>
       </c>
       <c r="M425" s="2" t="n">
-        <v>2422.6</v>
+        <v>2408.32</v>
       </c>
     </row>
     <row r="426">
@@ -26433,7 +26433,7 @@
         </is>
       </c>
       <c r="M426" s="2" t="n">
-        <v>2427.47</v>
+        <v>2413.17</v>
       </c>
     </row>
     <row r="427">
@@ -26494,7 +26494,7 @@
         </is>
       </c>
       <c r="M427" s="2" t="n">
-        <v>38282.17</v>
+        <v>38056.58</v>
       </c>
     </row>
     <row r="428">
@@ -26555,7 +26555,7 @@
         </is>
       </c>
       <c r="M428" s="2" t="n">
-        <v>5104.29</v>
+        <v>5074.21</v>
       </c>
     </row>
     <row r="429">
@@ -26616,7 +26616,7 @@
         </is>
       </c>
       <c r="M429" s="2" t="n">
-        <v>5800.33</v>
+        <v>5766.15</v>
       </c>
     </row>
     <row r="430">
@@ -26677,7 +26677,7 @@
         </is>
       </c>
       <c r="M430" s="2" t="n">
-        <v>3480.2</v>
+        <v>3459.69</v>
       </c>
     </row>
     <row r="431">
@@ -26738,7 +26738,7 @@
         </is>
       </c>
       <c r="M431" s="2" t="n">
-        <v>3480.2</v>
+        <v>3459.05</v>
       </c>
     </row>
     <row r="432">
@@ -26799,7 +26799,7 @@
         </is>
       </c>
       <c r="M432" s="2" t="n">
-        <v>2552.14</v>
+        <v>2536.64</v>
       </c>
     </row>
     <row r="433">
@@ -26860,7 +26860,7 @@
         </is>
       </c>
       <c r="M433" s="2" t="n">
-        <v>2552.14</v>
+        <v>2536.64</v>
       </c>
     </row>
     <row r="434">
@@ -26921,7 +26921,7 @@
         </is>
       </c>
       <c r="M434" s="2" t="n">
-        <v>2900.16</v>
+        <v>2882.54</v>
       </c>
     </row>
     <row r="435">
@@ -26982,7 +26982,7 @@
         </is>
       </c>
       <c r="M435" s="2" t="n">
-        <v>3480.2</v>
+        <v>3459.05</v>
       </c>
     </row>
     <row r="436">
@@ -27043,7 +27043,7 @@
         </is>
       </c>
       <c r="M436" s="2" t="n">
-        <v>8120.46</v>
+        <v>8071.12</v>
       </c>
     </row>
     <row r="437">
@@ -27104,7 +27104,7 @@
         </is>
       </c>
       <c r="M437" s="2" t="n">
-        <v>3480.2</v>
+        <v>3459.05</v>
       </c>
     </row>
     <row r="438">
@@ -27165,7 +27165,7 @@
         </is>
       </c>
       <c r="M438" s="2" t="n">
-        <v>3480.2</v>
+        <v>3459.05</v>
       </c>
     </row>
     <row r="439">
@@ -27226,7 +27226,7 @@
         </is>
       </c>
       <c r="M439" s="2" t="n">
-        <v>2436.14</v>
+        <v>2421.34</v>
       </c>
     </row>
     <row r="440">
@@ -27287,7 +27287,7 @@
         </is>
       </c>
       <c r="M440" s="2" t="n">
-        <v>2424.54</v>
+        <v>2409.81</v>
       </c>
     </row>
     <row r="441">
@@ -27348,7 +27348,7 @@
         </is>
       </c>
       <c r="M441" s="2" t="n">
-        <v>3480.2</v>
+        <v>3459.05</v>
       </c>
     </row>
     <row r="442">
@@ -27409,7 +27409,7 @@
         </is>
       </c>
       <c r="M442" s="2" t="n">
-        <v>5800.33</v>
+        <v>5765.08</v>
       </c>
     </row>
     <row r="443">
@@ -27470,7 +27470,7 @@
         </is>
       </c>
       <c r="M443" s="2" t="n">
-        <v>2422.6</v>
+        <v>2407.88</v>
       </c>
     </row>
     <row r="444">
@@ -27531,7 +27531,7 @@
         </is>
       </c>
       <c r="M444" s="2" t="n">
-        <v>25521.45</v>
+        <v>25366.37</v>
       </c>
     </row>
     <row r="445">
@@ -27592,7 +27592,7 @@
         </is>
       </c>
       <c r="M445" s="2" t="n">
-        <v>4640.26</v>
+        <v>4612.07</v>
       </c>
     </row>
     <row r="446">
@@ -27653,7 +27653,7 @@
         </is>
       </c>
       <c r="M446" s="2" t="n">
-        <v>3248.18</v>
+        <v>3228.45</v>
       </c>
     </row>
     <row r="447">
@@ -27714,7 +27714,7 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>2900.16</v>
+        <v>2882.54</v>
       </c>
     </row>
     <row r="448">
@@ -27775,7 +27775,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>4060.23</v>
+        <v>4035.56</v>
       </c>
     </row>
     <row r="449">
@@ -27836,7 +27836,7 @@
         </is>
       </c>
       <c r="M449" s="2" t="n">
-        <v>37122.11</v>
+        <v>36896.54</v>
       </c>
     </row>
     <row r="450">
@@ -27897,7 +27897,7 @@
         </is>
       </c>
       <c r="M450" s="2" t="n">
-        <v>13920.79</v>
+        <v>13836.2</v>
       </c>
     </row>
     <row r="451">
@@ -27958,7 +27958,7 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>11600.66</v>
+        <v>11530.17</v>
       </c>
     </row>
     <row r="452">
@@ -28019,7 +28019,7 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>23201.32</v>
+        <v>23060.34</v>
       </c>
     </row>
     <row r="453">
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="M453" s="2" t="n">
-        <v>2900.16</v>
+        <v>2882.54</v>
       </c>
     </row>
     <row r="454">
@@ -28141,7 +28141,7 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>5800.33</v>
+        <v>5765.08</v>
       </c>
     </row>
     <row r="455">
@@ -28202,7 +28202,7 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2900.16</v>
+        <v>2882.54</v>
       </c>
     </row>
     <row r="456">
@@ -28263,7 +28263,7 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>7888.45</v>
+        <v>7840.51</v>
       </c>
     </row>
     <row r="457">
@@ -28324,7 +28324,7 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>4640.26</v>
+        <v>4612.07</v>
       </c>
     </row>
     <row r="458">
@@ -28385,7 +28385,7 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>2436.14</v>
+        <v>2421.34</v>
       </c>
     </row>
     <row r="459">
@@ -28446,7 +28446,7 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>2552.14</v>
+        <v>2536.64</v>
       </c>
     </row>
     <row r="460">
@@ -28507,7 +28507,7 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>11600.66</v>
+        <v>11530.17</v>
       </c>
     </row>
     <row r="461">
@@ -28568,7 +28568,7 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>2679.75</v>
+        <v>2663.47</v>
       </c>
     </row>
     <row r="462">
@@ -28629,7 +28629,7 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>5800.33</v>
+        <v>5777.94</v>
       </c>
     </row>
     <row r="463">
@@ -28690,7 +28690,7 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>31321.78</v>
+        <v>31200.89</v>
       </c>
     </row>
     <row r="464">
@@ -28751,7 +28751,7 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>2436.14</v>
+        <v>2426.74</v>
       </c>
     </row>
     <row r="465">
@@ -28812,7 +28812,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>11600.66</v>
+        <v>11555.88</v>
       </c>
     </row>
     <row r="466">
@@ -28873,7 +28873,7 @@
         </is>
       </c>
       <c r="M466" s="2" t="n">
-        <v>13920.79</v>
+        <v>13867.06</v>
       </c>
     </row>
     <row r="467">
@@ -28934,7 +28934,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>4111.92</v>
+        <v>4096.05</v>
       </c>
     </row>
     <row r="468">
@@ -28995,7 +28995,7 @@
         </is>
       </c>
       <c r="M468" s="2" t="n">
-        <v>3480.2</v>
+        <v>3466.77</v>
       </c>
     </row>
     <row r="469">
@@ -29056,7 +29056,7 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>23201.32</v>
+        <v>23111.77</v>
       </c>
     </row>
     <row r="470">
@@ -29117,7 +29117,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>4640.26</v>
+        <v>4622.35</v>
       </c>
     </row>
     <row r="471">
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="M471" s="2" t="n">
-        <v>6059.6</v>
+        <v>6036.22</v>
       </c>
     </row>
     <row r="472">
@@ -29239,7 +29239,7 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>34801.98</v>
+        <v>34667.65</v>
       </c>
     </row>
     <row r="473">
@@ -29300,7 +29300,7 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>12405.26</v>
+        <v>12357.37</v>
       </c>
     </row>
     <row r="474">
@@ -29361,7 +29361,7 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>13920.79</v>
+        <v>13867.06</v>
       </c>
     </row>
     <row r="475">
@@ -29422,7 +29422,7 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>11600.66</v>
+        <v>11555.88</v>
       </c>
     </row>
     <row r="476">
@@ -29483,7 +29483,7 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>30161.71</v>
+        <v>30045.3</v>
       </c>
     </row>
     <row r="477">
@@ -29544,7 +29544,7 @@
         </is>
       </c>
       <c r="M477" s="2" t="n">
-        <v>4640.26</v>
+        <v>4622.35</v>
       </c>
     </row>
     <row r="478">
@@ -29605,7 +29605,7 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>6960.4</v>
+        <v>6933.53</v>
       </c>
     </row>
     <row r="479">
@@ -29666,7 +29666,7 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>4060.23</v>
+        <v>4044.56</v>
       </c>
     </row>
     <row r="480">
@@ -29727,7 +29727,7 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9244.709999999999</v>
       </c>
     </row>
     <row r="481">
@@ -29788,7 +29788,7 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>51158.91</v>
+        <v>50961.45</v>
       </c>
     </row>
     <row r="482">
@@ -29849,7 +29849,7 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>80044.55</v>
+        <v>79735.60000000001</v>
       </c>
     </row>
     <row r="483">
@@ -29910,7 +29910,7 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>4640.26</v>
+        <v>4622.35</v>
       </c>
     </row>
     <row r="484">
@@ -29971,7 +29971,7 @@
         </is>
       </c>
       <c r="M484" s="2" t="n">
-        <v>4640.26</v>
+        <v>4622.35</v>
       </c>
     </row>
     <row r="485">
@@ -30032,7 +30032,7 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>3317.79</v>
+        <v>3304.98</v>
       </c>
     </row>
     <row r="486">
@@ -30093,7 +30093,7 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>27261.55</v>
+        <v>27156.33</v>
       </c>
     </row>
     <row r="487">
@@ -30154,7 +30154,7 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>5278.3</v>
+        <v>5257.93</v>
       </c>
     </row>
     <row r="488">
@@ -30215,7 +30215,7 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>5800.33</v>
+        <v>5777.94</v>
       </c>
     </row>
     <row r="489">
@@ -30276,7 +30276,7 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>8120.46</v>
+        <v>8089.12</v>
       </c>
     </row>
     <row r="490">
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>2900.16</v>
+        <v>2888.97</v>
       </c>
     </row>
     <row r="491">
@@ -30398,7 +30398,7 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>3248.18</v>
+        <v>3235.65</v>
       </c>
     </row>
     <row r="492">
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>39442.24</v>
+        <v>39290.01</v>
       </c>
     </row>
     <row r="493">
@@ -30520,7 +30520,7 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>23201.32</v>
+        <v>23111.77</v>
       </c>
     </row>
     <row r="494">
@@ -30581,7 +30581,7 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>2424.54</v>
+        <v>2415.18</v>
       </c>
     </row>
     <row r="495">
@@ -30642,7 +30642,7 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>4640.26</v>
+        <v>4622.35</v>
       </c>
     </row>
     <row r="496">
@@ -30703,7 +30703,7 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>23201.32</v>
+        <v>23321.44</v>
       </c>
     </row>
     <row r="497">
@@ -30764,7 +30764,7 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>8120.46</v>
+        <v>8162.5</v>
       </c>
     </row>
     <row r="498">
@@ -30825,7 +30825,7 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>23201.32</v>
+        <v>23321.44</v>
       </c>
     </row>
     <row r="499">
@@ -30886,7 +30886,7 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>2424.54</v>
+        <v>2437.09</v>
       </c>
     </row>
     <row r="500">
@@ -30947,7 +30947,7 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>2436.14</v>
+        <v>2448.75</v>
       </c>
     </row>
     <row r="501">
@@ -31008,7 +31008,7 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>10440.59</v>
+        <v>10494.65</v>
       </c>
     </row>
     <row r="502">
@@ -31069,7 +31069,7 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>4665.73</v>
+        <v>4689.89</v>
       </c>
     </row>
     <row r="503">
@@ -31130,7 +31130,7 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>4163.85</v>
+        <v>4185.41</v>
       </c>
     </row>
     <row r="504">
@@ -31191,7 +31191,7 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>5678.52</v>
+        <v>5707.92</v>
       </c>
     </row>
     <row r="505">
@@ -31252,7 +31252,7 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>2552.14</v>
+        <v>2565.36</v>
       </c>
     </row>
     <row r="506">
@@ -31313,7 +31313,7 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>2436.14</v>
+        <v>2448.75</v>
       </c>
     </row>
     <row r="507">
@@ -31374,7 +31374,7 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>4317.35</v>
+        <v>4339.7</v>
       </c>
     </row>
     <row r="508">
@@ -31435,7 +31435,7 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>3364.19</v>
+        <v>3381.61</v>
       </c>
     </row>
     <row r="509">
@@ -31496,7 +31496,7 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>17400.99</v>
+        <v>17491.08</v>
       </c>
     </row>
     <row r="510">
@@ -31557,7 +31557,7 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>3248.18</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="511">
@@ -31618,7 +31618,7 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>2900.16</v>
+        <v>2915.18</v>
       </c>
     </row>
     <row r="512">
@@ -31679,7 +31679,7 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>2422.6</v>
+        <v>2435.14</v>
       </c>
     </row>
     <row r="513">
@@ -31740,7 +31740,7 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>2436.14</v>
+        <v>2448.75</v>
       </c>
     </row>
     <row r="514">
@@ -31801,7 +31801,7 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>5336.3</v>
+        <v>5363.93</v>
       </c>
     </row>
     <row r="515">
@@ -31862,7 +31862,7 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>3480.2</v>
+        <v>3498.22</v>
       </c>
     </row>
     <row r="516">
@@ -31923,7 +31923,7 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>24361.38</v>
+        <v>24487.51</v>
       </c>
     </row>
     <row r="517">
@@ -31984,7 +31984,7 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>15080.86</v>
+        <v>15158.94</v>
       </c>
     </row>
     <row r="518">
@@ -32045,7 +32045,7 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>2436.14</v>
+        <v>2448.75</v>
       </c>
     </row>
     <row r="519">
@@ -32106,7 +32106,7 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>3132.18</v>
+        <v>3148.39</v>
       </c>
     </row>
     <row r="520">
@@ -32167,7 +32167,7 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>12760.72</v>
+        <v>12826.79</v>
       </c>
     </row>
     <row r="521">
@@ -32228,7 +32228,7 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>2422.6</v>
+        <v>2435.14</v>
       </c>
     </row>
     <row r="522">
@@ -32289,7 +32289,7 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>2610.15</v>
+        <v>2623.66</v>
       </c>
     </row>
     <row r="523">
@@ -32350,7 +32350,7 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>11600.66</v>
+        <v>11660.72</v>
       </c>
     </row>
     <row r="524">
@@ -32411,7 +32411,7 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>49302.8</v>
+        <v>49558.06</v>
       </c>
     </row>
     <row r="525">
@@ -32472,7 +32472,7 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>5800.33</v>
+        <v>5830.36</v>
       </c>
     </row>
     <row r="526">
@@ -32533,7 +32533,7 @@
         </is>
       </c>
       <c r="M526" s="2" t="n">
-        <v>5800.33</v>
+        <v>5830.36</v>
       </c>
     </row>
     <row r="527">
@@ -32594,7 +32594,7 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>5605.12</v>
+        <v>5634.14</v>
       </c>
     </row>
     <row r="528">
@@ -32655,7 +32655,7 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>80624.58</v>
+        <v>81042</v>
       </c>
     </row>
     <row r="529">
@@ -32716,7 +32716,7 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>2842.16</v>
+        <v>2856.88</v>
       </c>
     </row>
     <row r="530">
@@ -32777,7 +32777,7 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>2422.6</v>
+        <v>2435.14</v>
       </c>
     </row>
     <row r="531">
@@ -32838,7 +32838,7 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>3480.2</v>
+        <v>3498.22</v>
       </c>
     </row>
     <row r="532">
@@ -32899,7 +32899,7 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>29001.65</v>
+        <v>29151.8</v>
       </c>
     </row>
     <row r="533">
@@ -32960,7 +32960,7 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>3480.2</v>
+        <v>3498.22</v>
       </c>
     </row>
     <row r="534">
@@ -33021,7 +33021,7 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>23201.32</v>
+        <v>23223.68</v>
       </c>
     </row>
     <row r="535">
@@ -33082,7 +33082,7 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>3480.2</v>
+        <v>3483.55</v>
       </c>
     </row>
     <row r="536">
@@ -33143,7 +33143,7 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>23201.32</v>
+        <v>23223.68</v>
       </c>
     </row>
     <row r="537">
@@ -33204,7 +33204,7 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>15080.86</v>
+        <v>15095.39</v>
       </c>
     </row>
     <row r="538">
@@ -33265,7 +33265,7 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>6960.4</v>
+        <v>6967.1</v>
       </c>
     </row>
     <row r="539">
@@ -33326,7 +33326,7 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>5800.33</v>
+        <v>5805.92</v>
       </c>
     </row>
     <row r="540">
@@ -33387,7 +33387,7 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>6902.39</v>
+        <v>6909.04</v>
       </c>
     </row>
     <row r="541">
@@ -33448,7 +33448,7 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>8120.46</v>
+        <v>8128.29</v>
       </c>
     </row>
     <row r="542">
@@ -33509,7 +33509,7 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>11600.66</v>
+        <v>11611.84</v>
       </c>
     </row>
     <row r="543">
@@ -33570,7 +33570,7 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>5176.21</v>
+        <v>5181.2</v>
       </c>
     </row>
     <row r="544">
@@ -33631,7 +33631,7 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>10672.61</v>
+        <v>10682.89</v>
       </c>
     </row>
     <row r="545">
@@ -33692,7 +33692,7 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>3161.65</v>
+        <v>3164.7</v>
       </c>
     </row>
     <row r="546">
@@ -33753,7 +33753,7 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>9280.530000000001</v>
+        <v>9289.469999999999</v>
       </c>
     </row>
     <row r="547">
@@ -33814,7 +33814,7 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>2552.14</v>
+        <v>2554.6</v>
       </c>
     </row>
     <row r="548">
@@ -33875,7 +33875,7 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>4060.23</v>
+        <v>4064.14</v>
       </c>
     </row>
     <row r="549">
@@ -33936,7 +33936,7 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>34801.98</v>
+        <v>34835.52</v>
       </c>
     </row>
     <row r="550">
@@ -33997,7 +33997,7 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>23201.32</v>
+        <v>23223.68</v>
       </c>
     </row>
     <row r="551">
@@ -34058,7 +34058,7 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>40091.85</v>
+        <v>40130.49</v>
       </c>
     </row>
     <row r="552">
@@ -34119,7 +34119,7 @@
         </is>
       </c>
       <c r="M552" s="2" t="n">
-        <v>3480.2</v>
+        <v>3483.55</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-mensuales/suministro-de-combustibles/feb-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/feb-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC feb-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -7991,7 +7991,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -8235,7 +8235,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8662,7 +8662,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8967,7 +8967,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9028,7 +9028,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9577,7 +9577,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9821,7 +9821,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -10492,7 +10492,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
@@ -10614,7 +10614,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11285,7 +11285,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11773,7 +11773,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12322,7 +12322,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -14762,7 +14762,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
@@ -15006,7 +15006,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15128,7 +15128,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15189,7 +15189,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15311,7 +15311,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15799,7 +15799,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -16287,7 +16287,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16531,7 +16531,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -18666,7 +18666,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -19337,7 +19337,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19581,7 +19581,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -20374,7 +20374,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">
@@ -20435,7 +20435,7 @@
       </c>
       <c r="H328" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I328" t="inlineStr">
@@ -21106,7 +21106,7 @@
       </c>
       <c r="H339" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I339" t="inlineStr">
@@ -21777,7 +21777,7 @@
       </c>
       <c r="H350" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I350" t="inlineStr">
@@ -21838,7 +21838,7 @@
       </c>
       <c r="H351" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I351" t="inlineStr">
@@ -22021,7 +22021,7 @@
       </c>
       <c r="H354" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I354" t="inlineStr">
@@ -22326,7 +22326,7 @@
       </c>
       <c r="H359" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I359" t="inlineStr">
@@ -22448,7 +22448,7 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I361" t="inlineStr">
@@ -22570,7 +22570,7 @@
       </c>
       <c r="H363" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I363" t="inlineStr">
@@ -23180,7 +23180,7 @@
       </c>
       <c r="H373" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I373" t="inlineStr">
@@ -23241,7 +23241,7 @@
       </c>
       <c r="H374" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I374" t="inlineStr">
@@ -24461,7 +24461,7 @@
       </c>
       <c r="H394" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I394" t="inlineStr">
@@ -24644,7 +24644,7 @@
       </c>
       <c r="H397" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I397" t="inlineStr">
@@ -25071,7 +25071,7 @@
       </c>
       <c r="H404" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I404" t="inlineStr">
@@ -25620,7 +25620,7 @@
       </c>
       <c r="H413" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I413" t="inlineStr">
@@ -25864,7 +25864,7 @@
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -26352,7 +26352,7 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I425" t="inlineStr">
@@ -26596,7 +26596,7 @@
       </c>
       <c r="H429" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I429" t="inlineStr">
@@ -26840,7 +26840,7 @@
       </c>
       <c r="H433" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I433" t="inlineStr">
@@ -27572,7 +27572,7 @@
       </c>
       <c r="H445" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I445" t="inlineStr">
@@ -27938,7 +27938,7 @@
       </c>
       <c r="H451" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I451" t="inlineStr">
@@ -28121,7 +28121,7 @@
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -28426,7 +28426,7 @@
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -28975,7 +28975,7 @@
       </c>
       <c r="H468" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I468" t="inlineStr">
@@ -29341,7 +29341,7 @@
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -30256,7 +30256,7 @@
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
@@ -30927,7 +30927,7 @@
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
@@ -31049,7 +31049,7 @@
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
@@ -31110,7 +31110,7 @@
       </c>
       <c r="H503" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I503" t="inlineStr">
@@ -31354,7 +31354,7 @@
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
@@ -31842,7 +31842,7 @@
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -32147,7 +32147,7 @@
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
@@ -32696,7 +32696,7 @@
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -32757,7 +32757,7 @@
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Magallanes y Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -32818,7 +32818,7 @@
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -33306,7 +33306,7 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -33428,7 +33428,7 @@
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Bío-Bío</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -33794,7 +33794,7 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -33977,7 +33977,7 @@
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>Lib. Gral. Bdo. O'Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">

--- a/docs/oc-mensuales/suministro-de-combustibles/feb-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/feb-2026.xlsx
@@ -1093,7 +1093,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TRAIGUEN</t>
+          <t>MUNICIPALIDAD DE TRAIGUEN</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2252,7 +2252,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>I.MUNICIPALIDAD DE LOTA - SALUD</t>
+          <t>I MUNICIPALIDAD DE LOTA</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3289,7 +3289,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE</t>
+          <t>Hospital de Constitución</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -4448,7 +4448,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE SALUD- CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5180,7 +5180,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5607,7 +5607,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -5729,7 +5729,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -6217,7 +6217,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>INSTITUTO DE INVESTIGACIONES Y CONTROL</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -6583,7 +6583,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>CCorporación Municipal de Desarrollo Social de Cal</t>
+          <t>Corporación Municipal de Desarrollo Social de Calama</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Región Metropolitana" - B Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -7620,7 +7620,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo Hospital de Ovalle</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Instituto de Prevision Social</t>
+          <t>INSTITUTO DE PREVISION SOCIAL</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -8108,7 +8108,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -8169,7 +8169,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>I.Municipalidad de El Carmen</t>
+          <t>Ilustre Municipalidad de El Carmen</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -8230,12 +8230,12 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Instituto de Seguridad Laboral</t>
+          <t>INSTITUTO DE SEGURIDAD LABORAL</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8596,7 +8596,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>I. MUNICIPALIDAD DE SAN NICOLAS - DEPTO. DE SALUD</t>
+          <t>I MUNICIPALIDAD DE SAN NICOLAS</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -8840,7 +8840,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>GOBERNACION MARITIMA DE CASTRO</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIRECCION COMUNAL DE EDUCACION - CORP MARIA PINTO </t>
+          <t>CORPORACION MUNICIPAL DE MARÍA PINTO</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -9450,7 +9450,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hospital Comunitario de Salud Familiar de Bulnes</t>
+          <t>HOSPITAL COMUNITARIO DE SALUD FAMILIAR DE BULNES</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Subsecretaria de las Culturas y las Artes Región de Valparaiso</t>
+          <t>SUBSECRETARÍA DE LAS CULTURAS Y LAS ARTES</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -9999,7 +9999,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Proyecto La Cisterna</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -10365,7 +10365,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10426,7 +10426,7 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Proyecto La Cisterna</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>EMDN-RMA</t>
+          <t>ESTADO MAYOR CONJUNTO</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -10548,7 +10548,7 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Departamento de Salud</t>
+          <t>I MUNICIPALIDAD DE NINHUE</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -10853,7 +10853,7 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Yumbel - Depto. Salud</t>
+          <t>I MUNICIPALIDAD DE YUMBEL</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERPLAC VI Región</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -11463,7 +11463,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>JEFATURA DE BIENESTAR (I.P)</t>
+          <t>POLICIA DE INVESTIGACIONES DE CHILE</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -12073,7 +12073,7 @@
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Zona Bienestar "Valparaíso" Bienestar Social</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>CORPORACION SOCIAL Y CULTURAL DE CONCEPCION- SEMCO</t>
+          <t>CORPORACION SOCIAL Y CULTURA DE CONCEPCION - SEMCO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -12195,7 +12195,7 @@
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Gobierno Regional de Antofagasta</t>
+          <t>GOBIERNO REGIONAL DE ANTOFAGASTA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hospital de Peñaflor</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE P</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -12378,7 +12378,7 @@
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
@@ -12439,7 +12439,7 @@
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>CORSABER</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION Y SALUD DE SAN BERNARDO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
@@ -12561,7 +12561,7 @@
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LUMACO</t>
+          <t>Ilustre Municipalidad de Lumaco</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
@@ -12683,7 +12683,7 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -12927,7 +12927,7 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Iquique</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL XIV REGION DE LOS RIOS</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
@@ -14269,7 +14269,7 @@
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TREHUACO DEPARTAMENTO</t>
+          <t>I MUNICIPALIDAD DE TREHUACO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -14818,7 +14818,7 @@
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>IMunicipalidad de Molina</t>
+          <t xml:space="preserve">ILUSTRE MUNICIPALIDAD DE MOLINA </t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GORBEA</t>
+          <t>Municipalidad de Gorbea</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>CORP DE EDUCACION Y SALUD DE LAS CONDES</t>
+          <t>Corporación de Educación y Salud de Las Condes</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -15611,7 +15611,7 @@
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE GENDARMERIA DE CHILE, REGION</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -16038,12 +16038,12 @@
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Dirección de Bienestar</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16343,7 +16343,7 @@
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Longaví Depto. de Salud</t>
+          <t>I MUNICIPALIDAD DE LONGAVI</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -16470,7 +16470,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -17197,7 +17197,7 @@
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>DEPARTAMENTO SALUD MUNICIPALIDAD DE QUILLON</t>
+          <t>ILUSTRE MUNICIPALIDAD DE QUILLON</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -17319,7 +17319,7 @@
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Departamento de Educación</t>
+          <t>I MUNICIPALIDAD DE CALBUCO</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -17746,7 +17746,7 @@
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Adulto Mayor</t>
+          <t>SERVICIO NACIONAL DEL ADULTO MAYOR</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -18905,7 +18905,7 @@
       </c>
       <c r="G303" t="inlineStr">
         <is>
-          <t>Servicio Nacional del Patrimonio Cultural</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H303" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="G305" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NIQUEN</t>
+          <t>Ilustre Municipalidad de Ñiquen</t>
         </is>
       </c>
       <c r="H305" t="inlineStr">
@@ -19088,7 +19088,7 @@
       </c>
       <c r="G306" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H306" t="inlineStr">
@@ -19149,7 +19149,7 @@
       </c>
       <c r="G307" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H307" t="inlineStr">
@@ -19200,7 +19200,7 @@
       </c>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F308" t="inlineStr">
@@ -19210,7 +19210,7 @@
       </c>
       <c r="G308" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Reinserción Social Juvenil</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H308" t="inlineStr">
@@ -19332,7 +19332,7 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo - Salud</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -19454,7 +19454,7 @@
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Hospital de Castro</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -20308,7 +20308,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TORTEL</t>
+          <t>Ilustre Municipalidad de Tortel</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -20369,7 +20369,7 @@
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de San Rosendo - Educación</t>
+          <t>I MUNICIPALIDAD DE SAN ROSENDO</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -20491,7 +20491,7 @@
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -20735,7 +20735,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>SERPLAC IV REGION</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -20918,7 +20918,7 @@
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
@@ -21162,7 +21162,7 @@
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t xml:space="preserve">SERPLAC VII REGION								</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -21528,7 +21528,7 @@
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Proyecto San Joaquín</t>
+          <t>ASOCIACIÓN DE MUNICIPIOS PARA LA SEGURIDAD COMUNITARIA</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>Servicio de Salud Coquimbo</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -22016,7 +22016,7 @@
       </c>
       <c r="G354" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Santa Barbara - Salud</t>
+          <t>I MUNICIPALIDAD DE SANTA BARBARA</t>
         </is>
       </c>
       <c r="H354" t="inlineStr">
@@ -22565,7 +22565,7 @@
       </c>
       <c r="G363" t="inlineStr">
         <is>
-          <t>Departamento Comunal de Salud</t>
+          <t>I MUNICIPALIDAD DE TUCAPEL</t>
         </is>
       </c>
       <c r="H363" t="inlineStr">
@@ -23053,7 +23053,7 @@
       </c>
       <c r="G371" t="inlineStr">
         <is>
-          <t>DIRECCION REGIONAL DE VALPARAISO DEL SNPC</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H371" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENAFLOR</t>
+          <t>MUNICIPALIDAD DE PEÑAFLOR</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -23226,7 +23226,7 @@
       </c>
       <c r="E374" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F374" t="inlineStr">
@@ -23297,7 +23297,7 @@
       </c>
       <c r="G375" t="inlineStr">
         <is>
-          <t>Servicio de Registro Civil e Identificación</t>
+          <t>SERVICIO DE REGISTRO CIVIL E IDENTIFICACION</t>
         </is>
       </c>
       <c r="H375" t="inlineStr">
@@ -23485,7 +23485,7 @@
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I378" t="inlineStr">
@@ -24395,7 +24395,7 @@
       </c>
       <c r="G393" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H393" t="inlineStr">
@@ -24456,7 +24456,7 @@
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO DEPARTAMENTO DE SALUD</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -25798,7 +25798,7 @@
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Copiapo</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -25859,7 +25859,7 @@
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Concepcion</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
@@ -25920,7 +25920,7 @@
       </c>
       <c r="G418" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Retiro</t>
+          <t>ILUSTRE MUNICIPALIDAD DE RETIRO</t>
         </is>
       </c>
       <c r="H418" t="inlineStr">
@@ -26535,7 +26535,7 @@
       </c>
       <c r="H428" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I428" t="inlineStr">
@@ -27018,7 +27018,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>I. Municipalidad Sagrada Familia</t>
+          <t>ILUSTRE MUNICIPALIDAD  DE SAGRADA FAMILIA</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -27079,7 +27079,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>I.Municipalidad de San Pablo -Salud</t>
+          <t>I MUNICIPALIDAD DE SAN PABLO</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -27201,7 +27201,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>SECRETARIA REGIONAL MINISTERIAL DE EDUCACION V REGIÓN</t>
+          <t>SUBSECRETARIA DEL MINISTERIO DE EDUCACION PUBLICA</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -27262,7 +27262,7 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>Departamento Administrativo de Salud Municipal.</t>
+          <t>I MUNICIPALIDAD DE FRUTILLAR</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
@@ -27323,7 +27323,7 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
@@ -27445,7 +27445,7 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>SERVICIO DEL PATRIMONIO</t>
+          <t>SERVICIO NACIONAL DEL PATRIMONIO CULTURAL</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
@@ -27628,7 +27628,7 @@
       </c>
       <c r="G446" t="inlineStr">
         <is>
-          <t>Dirección Regional de Gendarmeria - Antofagasta</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H446" t="inlineStr">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CUREPTO</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
@@ -27872,7 +27872,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>Iluste Municipalidad de Huechuraba</t>
+          <t>Municipalidad de Huechuraba</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -28116,7 +28116,7 @@
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONTULMO</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL F</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
@@ -28726,7 +28726,7 @@
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
@@ -29458,7 +29458,7 @@
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>DIRECCION DE SALUD</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
@@ -30800,7 +30800,7 @@
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE GALVARINO</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -31227,7 +31227,7 @@
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Productivo y T</t>
+          <t>Corporación Municipal de Desarrollo Productivo y Turismo de Molina</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
@@ -31288,7 +31288,7 @@
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>Corporación del Deporte e Inclusión Social de la I</t>
+          <t>Corporación del Deporte e Inclusión Social de la Ilustre Municipalidad de Cerro Navia</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Cochamó - Salud</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
@@ -31837,7 +31837,7 @@
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
@@ -32752,7 +32752,7 @@
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
@@ -32940,7 +32940,7 @@
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -32996,7 +32996,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Putre</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -33057,7 +33057,7 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>Servicio de Salud del Reloncaví</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
@@ -33728,7 +33728,7 @@
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>HOSPITAL CLAUDIO VICUNA</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -33911,7 +33911,7 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>SERVICIO HIDROGRAFICO Y OCEANOGRAFICO DE LA ARMADA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
@@ -34033,7 +34033,7 @@
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA SERENA</t>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">

--- a/docs/oc-mensuales/suministro-de-combustibles/feb-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/feb-2026.xlsx
@@ -562,7 +562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1111,7 +1147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1277,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1342,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1355,7 +1407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1477,7 +1537,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1599,7 +1667,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1721,7 +1797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1843,7 +1927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1904,7 +1992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +2057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2026,7 +2122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2270,7 +2382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2331,7 +2447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2392,7 +2512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2577,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2514,7 +2642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2575,7 +2707,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2636,7 +2772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2880,7 +3032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2941,7 +3097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3002,7 +3162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3063,7 +3227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3185,7 +3357,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3246,7 +3422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3307,7 +3487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3368,7 +3552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3429,7 +3617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3490,7 +3682,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3551,7 +3747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3612,7 +3812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L52" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3673,7 +3877,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3734,7 +3942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L54" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3795,7 +4007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3856,7 +4072,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L56" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3917,7 +4137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr"/>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L57" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3978,7 +4202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L58" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4100,7 +4332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L60" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4161,7 +4397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4222,7 +4462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4283,7 +4527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4344,7 +4592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4466,7 +4722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L66" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4649,7 +4917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L69" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4710,7 +4982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L70" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4771,7 +5047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L71" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4832,7 +5112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L72" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +5177,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4954,7 +5242,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5015,7 +5307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L75" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5076,7 +5372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5137,7 +5437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L77" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5198,7 +5502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5259,7 +5567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L79" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5320,7 +5632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L80" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5381,7 +5697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5442,7 +5762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5503,7 +5827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L83" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5564,7 +5892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L84" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5625,7 +5957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L85" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +6022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5747,7 +6087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K87" t="inlineStr"/>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L87" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5808,7 +6152,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L88" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +6217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5930,7 +6282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L90" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5991,7 +6347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L91" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6542,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6235,7 +6607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L95" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6296,7 +6672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L96" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6357,7 +6737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6418,7 +6802,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L98" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6540,7 +6932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6601,7 +6997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L101" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6662,7 +7062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K102" t="inlineStr"/>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6723,7 +7127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K103" t="inlineStr"/>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L103" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6784,7 +7192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L104" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6845,7 +7257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K105" t="inlineStr"/>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L105" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6906,7 +7322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K106" t="inlineStr"/>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L106" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6967,7 +7387,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K107" t="inlineStr"/>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L107" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7028,7 +7452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L108" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7089,7 +7517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K109" t="inlineStr"/>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L109" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7150,7 +7582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K110" t="inlineStr"/>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L110" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7211,7 +7647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K111" t="inlineStr"/>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L111" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7272,7 +7712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L112" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7333,7 +7777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7394,7 +7842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7455,7 +7907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K115" t="inlineStr"/>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L115" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7516,7 +7972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K116" t="inlineStr"/>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L116" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7577,7 +8037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L117" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7638,7 +8102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K118" t="inlineStr"/>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L118" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7699,7 +8167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K119" t="inlineStr"/>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L119" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7760,7 +8232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K120" t="inlineStr"/>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L120" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7821,7 +8297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K121" t="inlineStr"/>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L121" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7882,7 +8362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K122" t="inlineStr"/>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L122" t="inlineStr">
         <is>
           <t>USD</t>
@@ -7943,7 +8427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K123" t="inlineStr"/>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L123" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8004,7 +8492,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K124" t="inlineStr"/>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L124" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8065,7 +8557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K125" t="inlineStr"/>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L125" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8126,7 +8622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K126" t="inlineStr"/>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L126" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8187,7 +8687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K127" t="inlineStr"/>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L127" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8248,7 +8752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K128" t="inlineStr"/>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L128" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8309,7 +8817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K129" t="inlineStr"/>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L129" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8370,7 +8882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8431,7 +8947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K131" t="inlineStr"/>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L131" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8492,7 +9012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K132" t="inlineStr"/>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L132" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8553,7 +9077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K133" t="inlineStr"/>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L133" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8614,7 +9142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L134" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8675,7 +9207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K135" t="inlineStr"/>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L135" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8736,7 +9272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8797,7 +9337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K137" t="inlineStr"/>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L137" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8858,7 +9402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L138" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8919,7 +9467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K139" t="inlineStr"/>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L139" t="inlineStr">
         <is>
           <t>USD</t>
@@ -8980,7 +9532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K140" t="inlineStr"/>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L140" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9041,7 +9597,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K141" t="inlineStr"/>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L141" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9102,7 +9662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L142" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9163,7 +9727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr"/>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L143" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9224,7 +9792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L144" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9285,7 +9857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K145" t="inlineStr"/>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L145" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9346,7 +9922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K146" t="inlineStr"/>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L146" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9407,7 +9987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L147" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9468,7 +10052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K148" t="inlineStr"/>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L148" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9529,7 +10117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K149" t="inlineStr"/>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L149" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9590,7 +10182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L150" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9651,7 +10247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L151" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9712,7 +10312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9773,7 +10377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K153" t="inlineStr"/>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9834,7 +10442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K154" t="inlineStr"/>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L154" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9895,7 +10507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L155" t="inlineStr">
         <is>
           <t>USD</t>
@@ -9956,7 +10572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K156" t="inlineStr"/>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L156" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10017,7 +10637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K157" t="inlineStr"/>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L157" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10078,7 +10702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10139,7 +10767,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L159" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10200,7 +10832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K160" t="inlineStr"/>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L160" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10261,7 +10897,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K161" t="inlineStr"/>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L161" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10322,7 +10962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K162" t="inlineStr"/>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10383,7 +11027,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10444,7 +11092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K164" t="inlineStr"/>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L164" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10505,7 +11157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K165" t="inlineStr"/>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L165" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10566,7 +11222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K166" t="inlineStr"/>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L166" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10627,7 +11287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K167" t="inlineStr"/>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L167" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10688,7 +11352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K168" t="inlineStr"/>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10749,7 +11417,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K169" t="inlineStr"/>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10810,7 +11482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K170" t="inlineStr"/>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10871,7 +11547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K171" t="inlineStr"/>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10932,7 +11612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K172" t="inlineStr"/>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L172" t="inlineStr">
         <is>
           <t>USD</t>
@@ -10993,7 +11677,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L173" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11054,7 +11742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K174" t="inlineStr"/>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L174" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11115,7 +11807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K175" t="inlineStr"/>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L175" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11176,7 +11872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K176" t="inlineStr"/>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L176" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11237,7 +11937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K177" t="inlineStr"/>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11298,7 +12002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K178" t="inlineStr"/>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11359,7 +12067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K179" t="inlineStr"/>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L179" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11420,7 +12132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L180" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11481,7 +12197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K181" t="inlineStr"/>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L181" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11542,7 +12262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K182" t="inlineStr"/>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L182" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11603,7 +12327,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K183" t="inlineStr"/>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L183" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11664,7 +12392,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L184" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11725,7 +12457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K185" t="inlineStr"/>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11786,7 +12522,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K186" t="inlineStr"/>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L186" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11847,7 +12587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11908,7 +12652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K188" t="inlineStr"/>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L188" t="inlineStr">
         <is>
           <t>USD</t>
@@ -11969,7 +12717,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K189" t="inlineStr"/>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L189" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12030,7 +12782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K190" t="inlineStr"/>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L190" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12091,7 +12847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K191" t="inlineStr"/>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L191" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12152,7 +12912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K192" t="inlineStr"/>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L192" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12213,7 +12977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr"/>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12274,7 +13042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K194" t="inlineStr"/>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12335,7 +13107,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K195" t="inlineStr"/>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L195" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12396,7 +13172,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K196" t="inlineStr"/>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L196" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12457,7 +13237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K197" t="inlineStr"/>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12518,7 +13302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K198" t="inlineStr"/>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12579,7 +13367,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr"/>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L199" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12640,7 +13432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K200" t="inlineStr"/>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L200" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12701,7 +13497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K201" t="inlineStr"/>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12762,7 +13562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K202" t="inlineStr"/>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L202" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12823,7 +13627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K203" t="inlineStr"/>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12884,7 +13692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K204" t="inlineStr"/>
+      <c r="K204" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L204" t="inlineStr">
         <is>
           <t>USD</t>
@@ -12945,7 +13757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K205" t="inlineStr"/>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13006,7 +13822,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K206" t="inlineStr"/>
+      <c r="K206" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13067,7 +13887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L207" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13128,7 +13952,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K208" t="inlineStr"/>
+      <c r="K208" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L208" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13189,7 +14017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13250,7 +14082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K210" t="inlineStr"/>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13311,7 +14147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K211" t="inlineStr"/>
+      <c r="K211" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L211" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13372,7 +14212,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K212" t="inlineStr"/>
+      <c r="K212" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L212" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13433,7 +14277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K213" t="inlineStr"/>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13494,7 +14342,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13555,7 +14407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K215" t="inlineStr"/>
+      <c r="K215" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L215" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13616,7 +14472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K216" t="inlineStr"/>
+      <c r="K216" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L216" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13677,7 +14537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K217" t="inlineStr"/>
+      <c r="K217" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L217" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13738,7 +14602,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K218" t="inlineStr"/>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13799,7 +14667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K219" t="inlineStr"/>
+      <c r="K219" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13860,7 +14732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K220" t="inlineStr"/>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13921,7 +14797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K221" t="inlineStr"/>
+      <c r="K221" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
@@ -13982,7 +14862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K222" t="inlineStr"/>
+      <c r="K222" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L222" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14043,7 +14927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K223" t="inlineStr"/>
+      <c r="K223" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L223" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14104,7 +14992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K224" t="inlineStr"/>
+      <c r="K224" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L224" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14165,7 +15057,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K225" t="inlineStr"/>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14226,7 +15122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K226" t="inlineStr"/>
+      <c r="K226" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L226" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14287,7 +15187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K227" t="inlineStr"/>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L227" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14348,7 +15252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K228" t="inlineStr"/>
+      <c r="K228" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L228" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14409,7 +15317,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K229" t="inlineStr"/>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L229" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14470,7 +15382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K230" t="inlineStr"/>
+      <c r="K230" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14531,7 +15447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K231" t="inlineStr"/>
+      <c r="K231" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L231" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14592,7 +15512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K232" t="inlineStr"/>
+      <c r="K232" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L232" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14653,7 +15577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K233" t="inlineStr"/>
+      <c r="K233" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L233" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14714,7 +15642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K234" t="inlineStr"/>
+      <c r="K234" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L234" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14775,7 +15707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K235" t="inlineStr"/>
+      <c r="K235" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L235" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14836,7 +15772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K236" t="inlineStr"/>
+      <c r="K236" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L236" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14897,7 +15837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K237" t="inlineStr"/>
+      <c r="K237" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L237" t="inlineStr">
         <is>
           <t>USD</t>
@@ -14958,7 +15902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K238" t="inlineStr"/>
+      <c r="K238" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L238" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15019,7 +15967,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K239" t="inlineStr"/>
+      <c r="K239" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L239" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15080,7 +16032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K240" t="inlineStr"/>
+      <c r="K240" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L240" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15141,7 +16097,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L241" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15202,7 +16162,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K242" t="inlineStr"/>
+      <c r="K242" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L242" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15263,7 +16227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K243" t="inlineStr"/>
+      <c r="K243" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L243" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15324,7 +16292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K244" t="inlineStr"/>
+      <c r="K244" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L244" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15385,7 +16357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K245" t="inlineStr"/>
+      <c r="K245" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L245" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15446,7 +16422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L246" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15507,7 +16487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K247" t="inlineStr"/>
+      <c r="K247" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L247" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15568,7 +16552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K248" t="inlineStr"/>
+      <c r="K248" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L248" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15629,7 +16617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K249" t="inlineStr"/>
+      <c r="K249" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L249" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15690,7 +16682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K250" t="inlineStr"/>
+      <c r="K250" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L250" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15751,7 +16747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K251" t="inlineStr"/>
+      <c r="K251" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L251" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15812,7 +16812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L252" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15873,7 +16877,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K253" t="inlineStr"/>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L253" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15934,7 +16942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K254" t="inlineStr"/>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L254" t="inlineStr">
         <is>
           <t>USD</t>
@@ -15995,7 +17007,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K255" t="inlineStr"/>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L255" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16056,7 +17072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K256" t="inlineStr"/>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L256" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16117,7 +17137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K257" t="inlineStr"/>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L257" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16178,7 +17202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K258" t="inlineStr"/>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L258" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16239,7 +17267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K259" t="inlineStr"/>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L259" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16300,7 +17332,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K260" t="inlineStr"/>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L260" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16361,7 +17397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K261" t="inlineStr"/>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L261" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16422,7 +17462,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K262" t="inlineStr"/>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L262" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16483,7 +17527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K263" t="inlineStr"/>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L263" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16544,7 +17592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K264" t="inlineStr"/>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L264" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16605,7 +17657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K265" t="inlineStr"/>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L265" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16666,7 +17722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K266" t="inlineStr"/>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L266" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16727,7 +17787,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K267" t="inlineStr"/>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L267" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16788,7 +17852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K268" t="inlineStr"/>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L268" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16849,7 +17917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr"/>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L269" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16910,7 +17982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K270" t="inlineStr"/>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L270" t="inlineStr">
         <is>
           <t>USD</t>
@@ -16971,7 +18047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K271" t="inlineStr"/>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L271" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17032,7 +18112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K272" t="inlineStr"/>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L272" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17093,7 +18177,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K273" t="inlineStr"/>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L273" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17154,7 +18242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K274" t="inlineStr"/>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L274" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17215,7 +18307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K275" t="inlineStr"/>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L275" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17276,7 +18372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K276" t="inlineStr"/>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L276" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17337,7 +18437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K277" t="inlineStr"/>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L277" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17398,7 +18502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr"/>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L278" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17459,7 +18567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K279" t="inlineStr"/>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L279" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17520,7 +18632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K280" t="inlineStr"/>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L280" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17581,7 +18697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K281" t="inlineStr"/>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L281" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17642,7 +18762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr"/>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L282" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17703,7 +18827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K283" t="inlineStr"/>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L283" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17764,7 +18892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K284" t="inlineStr"/>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L284" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17825,7 +18957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K285" t="inlineStr"/>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L285" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17886,7 +19022,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K286" t="inlineStr"/>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L286" t="inlineStr">
         <is>
           <t>USD</t>
@@ -17947,7 +19087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr"/>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L287" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18008,7 +19152,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K288" t="inlineStr"/>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L288" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18069,7 +19217,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K289" t="inlineStr"/>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L289" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18130,7 +19282,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K290" t="inlineStr"/>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L290" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18191,7 +19347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K291" t="inlineStr"/>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L291" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18252,7 +19412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K292" t="inlineStr"/>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L292" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18313,7 +19477,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K293" t="inlineStr"/>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L293" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18374,7 +19542,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K294" t="inlineStr"/>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L294" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18435,7 +19607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K295" t="inlineStr"/>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L295" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18496,7 +19672,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K296" t="inlineStr"/>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L296" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18557,7 +19737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K297" t="inlineStr"/>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L297" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18618,7 +19802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K298" t="inlineStr"/>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L298" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18679,7 +19867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K299" t="inlineStr"/>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L299" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18740,7 +19932,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K300" t="inlineStr"/>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L300" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18801,7 +19997,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K301" t="inlineStr"/>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L301" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18862,7 +20062,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K302" t="inlineStr"/>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L302" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18923,7 +20127,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K303" t="inlineStr"/>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L303" t="inlineStr">
         <is>
           <t>USD</t>
@@ -18984,7 +20192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K304" t="inlineStr"/>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L304" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19045,7 +20257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K305" t="inlineStr"/>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L305" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19106,7 +20322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K306" t="inlineStr"/>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L306" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19167,7 +20387,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K307" t="inlineStr"/>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L307" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19228,7 +20452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K308" t="inlineStr"/>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L308" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19289,7 +20517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K309" t="inlineStr"/>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L309" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19350,7 +20582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K310" t="inlineStr"/>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L310" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19411,7 +20647,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K311" t="inlineStr"/>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L311" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19472,7 +20712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K312" t="inlineStr"/>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L312" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19533,7 +20777,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K313" t="inlineStr"/>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L313" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19594,7 +20842,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K314" t="inlineStr"/>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L314" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19655,7 +20907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K315" t="inlineStr"/>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L315" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19716,7 +20972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K316" t="inlineStr"/>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L316" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19777,7 +21037,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K317" t="inlineStr"/>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L317" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19838,7 +21102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K318" t="inlineStr"/>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L318" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19899,7 +21167,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K319" t="inlineStr"/>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L319" t="inlineStr">
         <is>
           <t>USD</t>
@@ -19960,7 +21232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K320" t="inlineStr"/>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L320" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20021,7 +21297,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K321" t="inlineStr"/>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L321" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20082,7 +21362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K322" t="inlineStr"/>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L322" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20143,7 +21427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K323" t="inlineStr"/>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L323" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20204,7 +21492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K324" t="inlineStr"/>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L324" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20265,7 +21557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K325" t="inlineStr"/>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L325" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20326,7 +21622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K326" t="inlineStr"/>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L326" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20387,7 +21687,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K327" t="inlineStr"/>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L327" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20448,7 +21752,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K328" t="inlineStr"/>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L328" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20509,7 +21817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K329" t="inlineStr"/>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L329" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20570,7 +21882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K330" t="inlineStr"/>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L330" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20631,7 +21947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K331" t="inlineStr"/>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L331" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20692,7 +22012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K332" t="inlineStr"/>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L332" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20753,7 +22077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K333" t="inlineStr"/>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L333" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20814,7 +22142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K334" t="inlineStr"/>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L334" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20875,7 +22207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K335" t="inlineStr"/>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L335" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20936,7 +22272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K336" t="inlineStr"/>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L336" t="inlineStr">
         <is>
           <t>USD</t>
@@ -20997,7 +22337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K337" t="inlineStr"/>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L337" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21058,7 +22402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K338" t="inlineStr"/>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L338" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21119,7 +22467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K339" t="inlineStr"/>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L339" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21180,7 +22532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K340" t="inlineStr"/>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L340" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21241,7 +22597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K341" t="inlineStr"/>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L341" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21302,7 +22662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K342" t="inlineStr"/>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L342" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21363,7 +22727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K343" t="inlineStr"/>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L343" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21424,7 +22792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K344" t="inlineStr"/>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L344" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21485,7 +22857,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K345" t="inlineStr"/>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L345" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21546,7 +22922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K346" t="inlineStr"/>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L346" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21607,7 +22987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K347" t="inlineStr"/>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L347" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21668,7 +23052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K348" t="inlineStr"/>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L348" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21729,7 +23117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K349" t="inlineStr"/>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L349" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21790,7 +23182,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K350" t="inlineStr"/>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L350" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21851,7 +23247,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K351" t="inlineStr"/>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L351" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21912,7 +23312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K352" t="inlineStr"/>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L352" t="inlineStr">
         <is>
           <t>USD</t>
@@ -21973,7 +23377,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K353" t="inlineStr"/>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L353" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22034,7 +23442,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K354" t="inlineStr"/>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L354" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22095,7 +23507,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K355" t="inlineStr"/>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L355" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22156,7 +23572,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K356" t="inlineStr"/>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L356" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22217,7 +23637,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K357" t="inlineStr"/>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L357" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22278,7 +23702,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K358" t="inlineStr"/>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L358" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22339,7 +23767,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K359" t="inlineStr"/>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L359" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22400,7 +23832,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K360" t="inlineStr"/>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L360" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22461,7 +23897,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K361" t="inlineStr"/>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L361" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22522,7 +23962,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K362" t="inlineStr"/>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L362" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22583,7 +24027,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K363" t="inlineStr"/>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L363" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22644,7 +24092,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K364" t="inlineStr"/>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L364" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22705,7 +24157,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K365" t="inlineStr"/>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L365" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22766,7 +24222,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K366" t="inlineStr"/>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L366" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22827,7 +24287,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K367" t="inlineStr"/>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L367" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22888,7 +24352,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K368" t="inlineStr"/>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L368" t="inlineStr">
         <is>
           <t>USD</t>
@@ -22949,7 +24417,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K369" t="inlineStr"/>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L369" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23010,7 +24482,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K370" t="inlineStr"/>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L370" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23071,7 +24547,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K371" t="inlineStr"/>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L371" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23132,7 +24612,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K372" t="inlineStr"/>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L372" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23193,7 +24677,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K373" t="inlineStr"/>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L373" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23254,7 +24742,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K374" t="inlineStr"/>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L374" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23315,7 +24807,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K375" t="inlineStr"/>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L375" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23376,7 +24872,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K376" t="inlineStr"/>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L376" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23437,7 +24937,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K377" t="inlineStr"/>
+      <c r="K377" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L377" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23498,7 +25002,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K378" t="inlineStr"/>
+      <c r="K378" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L378" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23559,7 +25067,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K379" t="inlineStr"/>
+      <c r="K379" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L379" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23620,7 +25132,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K380" t="inlineStr"/>
+      <c r="K380" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L380" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23681,7 +25197,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K381" t="inlineStr"/>
+      <c r="K381" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L381" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23742,7 +25262,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K382" t="inlineStr"/>
+      <c r="K382" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L382" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23803,7 +25327,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K383" t="inlineStr"/>
+      <c r="K383" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L383" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23864,7 +25392,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K384" t="inlineStr"/>
+      <c r="K384" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L384" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23925,7 +25457,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K385" t="inlineStr"/>
+      <c r="K385" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L385" t="inlineStr">
         <is>
           <t>USD</t>
@@ -23986,7 +25522,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K386" t="inlineStr"/>
+      <c r="K386" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L386" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24047,7 +25587,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K387" t="inlineStr"/>
+      <c r="K387" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L387" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24108,7 +25652,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K388" t="inlineStr"/>
+      <c r="K388" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L388" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24169,7 +25717,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K389" t="inlineStr"/>
+      <c r="K389" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L389" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24230,7 +25782,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K390" t="inlineStr"/>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L390" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24291,7 +25847,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K391" t="inlineStr"/>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L391" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24352,7 +25912,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K392" t="inlineStr"/>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L392" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24413,7 +25977,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K393" t="inlineStr"/>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L393" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24474,7 +26042,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K394" t="inlineStr"/>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L394" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24535,7 +26107,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K395" t="inlineStr"/>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L395" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24596,7 +26172,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K396" t="inlineStr"/>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L396" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24657,7 +26237,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K397" t="inlineStr"/>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L397" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24718,7 +26302,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K398" t="inlineStr"/>
+      <c r="K398" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L398" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24779,7 +26367,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K399" t="inlineStr"/>
+      <c r="K399" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L399" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24840,7 +26432,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K400" t="inlineStr"/>
+      <c r="K400" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L400" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24901,7 +26497,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K401" t="inlineStr"/>
+      <c r="K401" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L401" t="inlineStr">
         <is>
           <t>USD</t>
@@ -24962,7 +26562,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K402" t="inlineStr"/>
+      <c r="K402" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L402" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25023,7 +26627,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K403" t="inlineStr"/>
+      <c r="K403" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L403" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25084,7 +26692,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K404" t="inlineStr"/>
+      <c r="K404" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L404" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25145,7 +26757,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K405" t="inlineStr"/>
+      <c r="K405" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L405" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25206,7 +26822,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K406" t="inlineStr"/>
+      <c r="K406" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L406" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25267,7 +26887,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K407" t="inlineStr"/>
+      <c r="K407" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L407" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25328,7 +26952,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K408" t="inlineStr"/>
+      <c r="K408" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L408" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25389,7 +27017,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K409" t="inlineStr"/>
+      <c r="K409" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L409" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25450,7 +27082,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K410" t="inlineStr"/>
+      <c r="K410" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L410" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25511,7 +27147,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K411" t="inlineStr"/>
+      <c r="K411" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L411" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25572,7 +27212,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K412" t="inlineStr"/>
+      <c r="K412" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L412" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25633,7 +27277,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K413" t="inlineStr"/>
+      <c r="K413" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L413" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25694,7 +27342,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K414" t="inlineStr"/>
+      <c r="K414" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L414" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25755,7 +27407,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K415" t="inlineStr"/>
+      <c r="K415" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L415" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25816,7 +27472,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K416" t="inlineStr"/>
+      <c r="K416" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L416" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25877,7 +27537,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K417" t="inlineStr"/>
+      <c r="K417" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L417" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25938,7 +27602,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K418" t="inlineStr"/>
+      <c r="K418" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L418" t="inlineStr">
         <is>
           <t>USD</t>
@@ -25999,7 +27667,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K419" t="inlineStr"/>
+      <c r="K419" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L419" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26060,7 +27732,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K420" t="inlineStr"/>
+      <c r="K420" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L420" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26121,7 +27797,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K421" t="inlineStr"/>
+      <c r="K421" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L421" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26182,7 +27862,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K422" t="inlineStr"/>
+      <c r="K422" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L422" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26243,7 +27927,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K423" t="inlineStr"/>
+      <c r="K423" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L423" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26304,7 +27992,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K424" t="inlineStr"/>
+      <c r="K424" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L424" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26365,7 +28057,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K425" t="inlineStr"/>
+      <c r="K425" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L425" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26426,7 +28122,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K426" t="inlineStr"/>
+      <c r="K426" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L426" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26487,7 +28187,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K427" t="inlineStr"/>
+      <c r="K427" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L427" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26548,7 +28252,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K428" t="inlineStr"/>
+      <c r="K428" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L428" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26609,7 +28317,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K429" t="inlineStr"/>
+      <c r="K429" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L429" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26670,7 +28382,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K430" t="inlineStr"/>
+      <c r="K430" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L430" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26731,7 +28447,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K431" t="inlineStr"/>
+      <c r="K431" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L431" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26792,7 +28512,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K432" t="inlineStr"/>
+      <c r="K432" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L432" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26853,7 +28577,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K433" t="inlineStr"/>
+      <c r="K433" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L433" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26914,7 +28642,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K434" t="inlineStr"/>
+      <c r="K434" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L434" t="inlineStr">
         <is>
           <t>USD</t>
@@ -26975,7 +28707,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K435" t="inlineStr"/>
+      <c r="K435" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L435" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27036,7 +28772,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K436" t="inlineStr"/>
+      <c r="K436" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L436" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27097,7 +28837,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K437" t="inlineStr"/>
+      <c r="K437" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L437" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27158,7 +28902,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K438" t="inlineStr"/>
+      <c r="K438" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L438" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27219,7 +28967,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K439" t="inlineStr"/>
+      <c r="K439" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L439" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27280,7 +29032,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K440" t="inlineStr"/>
+      <c r="K440" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L440" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27341,7 +29097,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K441" t="inlineStr"/>
+      <c r="K441" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L441" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27402,7 +29162,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K442" t="inlineStr"/>
+      <c r="K442" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L442" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27463,7 +29227,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K443" t="inlineStr"/>
+      <c r="K443" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L443" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27524,7 +29292,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K444" t="inlineStr"/>
+      <c r="K444" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L444" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27585,7 +29357,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K445" t="inlineStr"/>
+      <c r="K445" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L445" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27646,7 +29422,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K446" t="inlineStr"/>
+      <c r="K446" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L446" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27707,7 +29487,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K447" t="inlineStr"/>
+      <c r="K447" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L447" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27768,7 +29552,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K448" t="inlineStr"/>
+      <c r="K448" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L448" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27829,7 +29617,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K449" t="inlineStr"/>
+      <c r="K449" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L449" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27890,7 +29682,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K450" t="inlineStr"/>
+      <c r="K450" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L450" t="inlineStr">
         <is>
           <t>USD</t>
@@ -27951,7 +29747,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K451" t="inlineStr"/>
+      <c r="K451" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L451" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28012,7 +29812,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K452" t="inlineStr"/>
+      <c r="K452" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L452" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28073,7 +29877,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K453" t="inlineStr"/>
+      <c r="K453" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L453" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28134,7 +29942,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K454" t="inlineStr"/>
+      <c r="K454" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L454" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28195,7 +30007,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K455" t="inlineStr"/>
+      <c r="K455" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L455" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28256,7 +30072,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K456" t="inlineStr"/>
+      <c r="K456" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L456" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28317,7 +30137,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K457" t="inlineStr"/>
+      <c r="K457" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L457" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28378,7 +30202,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K458" t="inlineStr"/>
+      <c r="K458" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L458" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28439,7 +30267,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K459" t="inlineStr"/>
+      <c r="K459" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L459" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28500,7 +30332,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K460" t="inlineStr"/>
+      <c r="K460" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L460" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28561,7 +30397,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K461" t="inlineStr"/>
+      <c r="K461" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L461" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28622,7 +30462,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K462" t="inlineStr"/>
+      <c r="K462" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L462" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28683,7 +30527,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K463" t="inlineStr"/>
+      <c r="K463" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L463" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28744,7 +30592,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K464" t="inlineStr"/>
+      <c r="K464" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L464" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28805,7 +30657,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K465" t="inlineStr"/>
+      <c r="K465" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L465" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28866,7 +30722,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K466" t="inlineStr"/>
+      <c r="K466" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L466" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28927,7 +30787,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K467" t="inlineStr"/>
+      <c r="K467" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L467" t="inlineStr">
         <is>
           <t>USD</t>
@@ -28988,7 +30852,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K468" t="inlineStr"/>
+      <c r="K468" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L468" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29049,7 +30917,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K469" t="inlineStr"/>
+      <c r="K469" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L469" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29110,7 +30982,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K470" t="inlineStr"/>
+      <c r="K470" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L470" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29171,7 +31047,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K471" t="inlineStr"/>
+      <c r="K471" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L471" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29232,7 +31112,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K472" t="inlineStr"/>
+      <c r="K472" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L472" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29293,7 +31177,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K473" t="inlineStr"/>
+      <c r="K473" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L473" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29354,7 +31242,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K474" t="inlineStr"/>
+      <c r="K474" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L474" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29415,7 +31307,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K475" t="inlineStr"/>
+      <c r="K475" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L475" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29476,7 +31372,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K476" t="inlineStr"/>
+      <c r="K476" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L476" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29537,7 +31437,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K477" t="inlineStr"/>
+      <c r="K477" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L477" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29598,7 +31502,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K478" t="inlineStr"/>
+      <c r="K478" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L478" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29659,7 +31567,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K479" t="inlineStr"/>
+      <c r="K479" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L479" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29720,7 +31632,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K480" t="inlineStr"/>
+      <c r="K480" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L480" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29781,7 +31697,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K481" t="inlineStr"/>
+      <c r="K481" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L481" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29842,7 +31762,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K482" t="inlineStr"/>
+      <c r="K482" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L482" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29903,7 +31827,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K483" t="inlineStr"/>
+      <c r="K483" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L483" t="inlineStr">
         <is>
           <t>USD</t>
@@ -29964,7 +31892,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K484" t="inlineStr"/>
+      <c r="K484" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L484" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30025,7 +31957,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K485" t="inlineStr"/>
+      <c r="K485" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L485" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30086,7 +32022,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K486" t="inlineStr"/>
+      <c r="K486" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L486" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30147,7 +32087,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K487" t="inlineStr"/>
+      <c r="K487" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L487" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30208,7 +32152,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K488" t="inlineStr"/>
+      <c r="K488" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L488" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30269,7 +32217,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K489" t="inlineStr"/>
+      <c r="K489" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L489" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30330,7 +32282,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K490" t="inlineStr"/>
+      <c r="K490" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L490" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30391,7 +32347,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K491" t="inlineStr"/>
+      <c r="K491" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L491" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30452,7 +32412,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K492" t="inlineStr"/>
+      <c r="K492" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L492" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30513,7 +32477,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K493" t="inlineStr"/>
+      <c r="K493" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L493" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30574,7 +32542,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K494" t="inlineStr"/>
+      <c r="K494" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L494" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30635,7 +32607,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K495" t="inlineStr"/>
+      <c r="K495" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L495" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30696,7 +32672,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K496" t="inlineStr"/>
+      <c r="K496" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L496" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30757,7 +32737,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K497" t="inlineStr"/>
+      <c r="K497" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L497" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30818,7 +32802,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K498" t="inlineStr"/>
+      <c r="K498" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L498" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30879,7 +32867,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K499" t="inlineStr"/>
+      <c r="K499" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L499" t="inlineStr">
         <is>
           <t>USD</t>
@@ -30940,7 +32932,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K500" t="inlineStr"/>
+      <c r="K500" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L500" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31001,7 +32997,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K501" t="inlineStr"/>
+      <c r="K501" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L501" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31062,7 +33062,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K502" t="inlineStr"/>
+      <c r="K502" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L502" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31123,7 +33127,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K503" t="inlineStr"/>
+      <c r="K503" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L503" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31184,7 +33192,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K504" t="inlineStr"/>
+      <c r="K504" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L504" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31245,7 +33257,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K505" t="inlineStr"/>
+      <c r="K505" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L505" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31306,7 +33322,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K506" t="inlineStr"/>
+      <c r="K506" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L506" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31367,7 +33387,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K507" t="inlineStr"/>
+      <c r="K507" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L507" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31428,7 +33452,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K508" t="inlineStr"/>
+      <c r="K508" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L508" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31489,7 +33517,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K509" t="inlineStr"/>
+      <c r="K509" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L509" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31550,7 +33582,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K510" t="inlineStr"/>
+      <c r="K510" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L510" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31611,7 +33647,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K511" t="inlineStr"/>
+      <c r="K511" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L511" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31672,7 +33712,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K512" t="inlineStr"/>
+      <c r="K512" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L512" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31733,7 +33777,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K513" t="inlineStr"/>
+      <c r="K513" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L513" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31794,7 +33842,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K514" t="inlineStr"/>
+      <c r="K514" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L514" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31855,7 +33907,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K515" t="inlineStr"/>
+      <c r="K515" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L515" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31916,7 +33972,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K516" t="inlineStr"/>
+      <c r="K516" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L516" t="inlineStr">
         <is>
           <t>USD</t>
@@ -31977,7 +34037,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K517" t="inlineStr"/>
+      <c r="K517" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L517" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32038,7 +34102,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K518" t="inlineStr"/>
+      <c r="K518" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L518" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32099,7 +34167,11 @@
           <t>92.011.000-2</t>
         </is>
       </c>
-      <c r="K519" t="inlineStr"/>
+      <c r="K519" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L519" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32160,7 +34232,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K520" t="inlineStr"/>
+      <c r="K520" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L520" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32221,7 +34297,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K521" t="inlineStr"/>
+      <c r="K521" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L521" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32282,7 +34362,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K522" t="inlineStr"/>
+      <c r="K522" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L522" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32343,7 +34427,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K523" t="inlineStr"/>
+      <c r="K523" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L523" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32404,7 +34492,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K524" t="inlineStr"/>
+      <c r="K524" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L524" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32465,7 +34557,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K525" t="inlineStr"/>
+      <c r="K525" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L525" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32526,7 +34622,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K526" t="inlineStr"/>
+      <c r="K526" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L526" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32587,7 +34687,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K527" t="inlineStr"/>
+      <c r="K527" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L527" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32648,7 +34752,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K528" t="inlineStr"/>
+      <c r="K528" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L528" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32709,7 +34817,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K529" t="inlineStr"/>
+      <c r="K529" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L529" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32770,7 +34882,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K530" t="inlineStr"/>
+      <c r="K530" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L530" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32831,7 +34947,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K531" t="inlineStr"/>
+      <c r="K531" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L531" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32892,7 +35012,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K532" t="inlineStr"/>
+      <c r="K532" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L532" t="inlineStr">
         <is>
           <t>USD</t>
@@ -32953,7 +35077,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K533" t="inlineStr"/>
+      <c r="K533" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L533" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33014,7 +35142,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K534" t="inlineStr"/>
+      <c r="K534" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L534" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33075,7 +35207,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K535" t="inlineStr"/>
+      <c r="K535" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L535" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33136,7 +35272,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K536" t="inlineStr"/>
+      <c r="K536" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L536" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33197,7 +35337,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K537" t="inlineStr"/>
+      <c r="K537" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L537" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33258,7 +35402,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K538" t="inlineStr"/>
+      <c r="K538" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L538" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33319,7 +35467,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K539" t="inlineStr"/>
+      <c r="K539" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L539" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33380,7 +35532,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K540" t="inlineStr"/>
+      <c r="K540" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L540" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33441,7 +35597,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K541" t="inlineStr"/>
+      <c r="K541" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L541" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33502,7 +35662,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K542" t="inlineStr"/>
+      <c r="K542" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L542" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33563,7 +35727,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K543" t="inlineStr"/>
+      <c r="K543" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L543" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33624,7 +35792,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K544" t="inlineStr"/>
+      <c r="K544" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L544" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33685,7 +35857,11 @@
           <t>79.588.870-5</t>
         </is>
       </c>
-      <c r="K545" t="inlineStr"/>
+      <c r="K545" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
       <c r="L545" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33746,7 +35922,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K546" t="inlineStr"/>
+      <c r="K546" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L546" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33807,7 +35987,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K547" t="inlineStr"/>
+      <c r="K547" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L547" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33868,7 +36052,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K548" t="inlineStr"/>
+      <c r="K548" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L548" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33929,7 +36117,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K549" t="inlineStr"/>
+      <c r="K549" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L549" t="inlineStr">
         <is>
           <t>USD</t>
@@ -33990,7 +36182,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K550" t="inlineStr"/>
+      <c r="K550" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L550" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34051,7 +36247,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K551" t="inlineStr"/>
+      <c r="K551" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L551" t="inlineStr">
         <is>
           <t>USD</t>
@@ -34112,7 +36312,11 @@
           <t>99.520.000-7</t>
         </is>
       </c>
-      <c r="K552" t="inlineStr"/>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L552" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/suministro-de-combustibles/feb-2026.xlsx
+++ b/docs/oc-mensuales/suministro-de-combustibles/feb-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M552"/>
+  <dimension ref="A1:M553"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3654,7 +3654,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -7359,7 +7359,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
@@ -21899,7 +21899,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>3820-130-CM26</t>
+          <t>3708-72-CM26</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -21919,22 +21919,22 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>69.051.000-6</t>
+          <t>69.191.300-7</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
+          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I331" t="inlineStr">
@@ -21958,7 +21958,7 @@
         </is>
       </c>
       <c r="M331" s="2" t="n">
-        <v>2649.04</v>
+        <v>9429.540000000001</v>
       </c>
     </row>
     <row r="332">
@@ -22094,7 +22094,7 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>3708-72-CM26</t>
+          <t>2929-117-CM26</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -22119,17 +22119,17 @@
       </c>
       <c r="F334" t="inlineStr">
         <is>
-          <t>69.191.300-7</t>
+          <t>69.231.300-3</t>
         </is>
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PITRUFQUEN</t>
+          <t>I MUNICIPALIDAD DE PALENA</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I334" t="inlineStr">
@@ -22153,13 +22153,13 @@
         </is>
       </c>
       <c r="M334" s="2" t="n">
-        <v>9429.540000000001</v>
+        <v>4607.02</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>2929-117-CM26</t>
+          <t>1661-103-CM26</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -22179,17 +22179,17 @@
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F335" t="inlineStr">
         <is>
-          <t>69.231.300-3</t>
+          <t>61.602.268-7</t>
         </is>
       </c>
       <c r="G335" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PALENA</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H335" t="inlineStr">
@@ -22218,13 +22218,13 @@
         </is>
       </c>
       <c r="M335" s="2" t="n">
-        <v>4607.02</v>
+        <v>3455.27</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>1661-103-CM26</t>
+          <t>3820-130-CM26</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -22249,17 +22249,17 @@
       </c>
       <c r="F336" t="inlineStr">
         <is>
-          <t>61.602.268-7</t>
+          <t>69.051.000-6</t>
         </is>
       </c>
       <c r="G336" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>I MUNICIPALIDAD DE SANTA MARIA</t>
         </is>
       </c>
       <c r="H336" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I336" t="inlineStr">
@@ -22283,7 +22283,7 @@
         </is>
       </c>
       <c r="M336" s="2" t="n">
-        <v>3455.27</v>
+        <v>2649.04</v>
       </c>
     </row>
     <row r="337">
@@ -22549,7 +22549,7 @@
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>929-36-CM26</t>
+          <t>1211839-80-CM26</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -22569,17 +22569,17 @@
       </c>
       <c r="E341" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>70.856.400-1</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -22608,13 +22608,13 @@
         </is>
       </c>
       <c r="M341" s="2" t="n">
-        <v>3570.44</v>
+        <v>6910.53</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>1211839-80-CM26</t>
+          <t>1229788-40-CM26</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -22634,22 +22634,22 @@
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>70.856.400-1</t>
+          <t>61.606.400-2</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+          <t>SERVICIO DE SALUD COQUIMBO</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I342" t="inlineStr">
@@ -22673,13 +22673,13 @@
         </is>
       </c>
       <c r="M342" s="2" t="n">
-        <v>6910.53</v>
+        <v>12554.13</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>1395-61-CM26</t>
+          <t>1195-80-CM26</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -22704,17 +22704,17 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>61.606.400-2</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO</t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I343" t="inlineStr">
@@ -22738,13 +22738,13 @@
         </is>
       </c>
       <c r="M343" s="2" t="n">
-        <v>26726.48</v>
+        <v>5528.43</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>1195-80-CM26</t>
+          <t>929-36-CM26</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -22769,17 +22769,17 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>69.240.300-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I344" t="inlineStr">
@@ -22803,7 +22803,7 @@
         </is>
       </c>
       <c r="M344" s="2" t="n">
-        <v>5528.43</v>
+        <v>3570.44</v>
       </c>
     </row>
     <row r="345">
@@ -22939,7 +22939,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>1229788-40-CM26</t>
+          <t>1395-61-CM26</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -22998,7 +22998,7 @@
         </is>
       </c>
       <c r="M347" s="2" t="n">
-        <v>12554.13</v>
+        <v>26726.48</v>
       </c>
     </row>
     <row r="348">
@@ -27294,7 +27294,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>1158-6-CM26</t>
+          <t>3620-45-CM26</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -27319,17 +27319,17 @@
       </c>
       <c r="F414" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.072.300-k</t>
         </is>
       </c>
       <c r="G414" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE SAN JOSE DE MAIPO</t>
         </is>
       </c>
       <c r="H414" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I414" t="inlineStr">
@@ -27353,13 +27353,13 @@
         </is>
       </c>
       <c r="M414" s="2" t="n">
-        <v>10256.82</v>
+        <v>4791.67</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>3620-45-CM26</t>
+          <t>1969-136-CM26</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -27379,22 +27379,22 @@
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F415" t="inlineStr">
         <is>
-          <t>69.072.300-k</t>
+          <t>61.004.068-3</t>
         </is>
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN JOSE DE MAIPO</t>
+          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I415" t="inlineStr">
@@ -27418,7 +27418,7 @@
         </is>
       </c>
       <c r="M415" s="2" t="n">
-        <v>4791.67</v>
+        <v>19604.9</v>
       </c>
     </row>
     <row r="416">
@@ -27489,7 +27489,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>1969-136-CM26</t>
+          <t>1158-6-CM26</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -27509,22 +27509,22 @@
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F417" t="inlineStr">
         <is>
-          <t>61.004.068-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G417" t="inlineStr">
         <is>
-          <t>DIRECCION GENERAL DE GENDARMERIA DE CHIL</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H417" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I417" t="inlineStr">
@@ -27548,7 +27548,7 @@
         </is>
       </c>
       <c r="M417" s="2" t="n">
-        <v>19604.9</v>
+        <v>10256.82</v>
       </c>
     </row>
     <row r="418">
@@ -28029,7 +28029,7 @@
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F425" t="inlineStr">
@@ -29439,7 +29439,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>4316-7-CM26</t>
+          <t>2989-110-CM26</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -29459,22 +29459,22 @@
       </c>
       <c r="E447" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F447" t="inlineStr">
         <is>
-          <t>69.110.300-5</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G447" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Curepto</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H447" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I447" t="inlineStr">
@@ -29498,13 +29498,13 @@
         </is>
       </c>
       <c r="M447" s="2" t="n">
-        <v>2882.54</v>
+        <v>11530.17</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>1305527-8-CM26</t>
+          <t>2989-111-CM26</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -29529,17 +29529,17 @@
       </c>
       <c r="F448" t="inlineStr">
         <is>
-          <t>61.981.090-2</t>
+          <t>69.220.800-5</t>
         </is>
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL PINO</t>
+          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I448" t="inlineStr">
@@ -29563,7 +29563,7 @@
         </is>
       </c>
       <c r="M448" s="2" t="n">
-        <v>4035.56</v>
+        <v>2882.54</v>
       </c>
     </row>
     <row r="449">
@@ -29699,7 +29699,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>1233613-242-CM26</t>
+          <t>1233613-229-CM26</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -29719,7 +29719,7 @@
       </c>
       <c r="E451" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F451" t="inlineStr">
@@ -29758,13 +29758,13 @@
         </is>
       </c>
       <c r="M451" s="2" t="n">
-        <v>11530.17</v>
+        <v>10377.15</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>3807-81-CM26</t>
+          <t>1233613-242-CM26</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -29784,22 +29784,22 @@
       </c>
       <c r="E452" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F452" t="inlineStr">
         <is>
-          <t>69.120.200-3</t>
+          <t>61.980.960-2</t>
         </is>
       </c>
       <c r="G452" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
+          <t>Servicio Local de Educación Pública Magallanes</t>
         </is>
       </c>
       <c r="H452" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I452" t="inlineStr">
@@ -29823,13 +29823,13 @@
         </is>
       </c>
       <c r="M452" s="2" t="n">
-        <v>23060.34</v>
+        <v>11530.17</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>2989-111-CM26</t>
+          <t>4316-7-CM26</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -29849,22 +29849,22 @@
       </c>
       <c r="E453" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F453" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.110.300-5</t>
         </is>
       </c>
       <c r="G453" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>Ilustre Municipalidad de Curepto</t>
         </is>
       </c>
       <c r="H453" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I453" t="inlineStr">
@@ -29894,7 +29894,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>4474-161-CM26</t>
+          <t>3807-81-CM26</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -29919,17 +29919,17 @@
       </c>
       <c r="F454" t="inlineStr">
         <is>
-          <t>69.160.600-7</t>
+          <t>69.120.200-3</t>
         </is>
       </c>
       <c r="G454" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Contulmo</t>
+          <t>I MUNICIPALIDAD DE EMPEDRADO</t>
         </is>
       </c>
       <c r="H454" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I454" t="inlineStr">
@@ -29953,13 +29953,13 @@
         </is>
       </c>
       <c r="M454" s="2" t="n">
-        <v>5765.08</v>
+        <v>23060.34</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>4357-65-CM26</t>
+          <t>1305527-8-CM26</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -29979,22 +29979,22 @@
       </c>
       <c r="E455" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F455" t="inlineStr">
         <is>
-          <t>69.030.600-k</t>
+          <t>61.981.090-2</t>
         </is>
       </c>
       <c r="G455" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRINA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL PINO</t>
         </is>
       </c>
       <c r="H455" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I455" t="inlineStr">
@@ -30018,13 +30018,13 @@
         </is>
       </c>
       <c r="M455" s="2" t="n">
-        <v>2882.54</v>
+        <v>4035.56</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>1432-2-CM26</t>
+          <t>696750-9-CM26</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -30044,22 +30044,22 @@
       </c>
       <c r="E456" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F456" t="inlineStr">
         <is>
-          <t>61.702.000-9</t>
+          <t>61.935.400-1</t>
         </is>
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
+          <t>MINISTERIO PUBLICO</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I456" t="inlineStr">
@@ -30083,13 +30083,13 @@
         </is>
       </c>
       <c r="M456" s="2" t="n">
-        <v>7840.51</v>
+        <v>2663.47</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>1642-188-CM26</t>
+          <t>4357-65-CM26</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -30114,17 +30114,17 @@
       </c>
       <c r="F457" t="inlineStr">
         <is>
-          <t>61.602.125-7</t>
+          <t>69.030.600-k</t>
         </is>
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE HOSPITAL DE CURACAVI</t>
+          <t>I MUNICIPALIDAD DE FREIRINA</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I457" t="inlineStr">
@@ -30148,13 +30148,13 @@
         </is>
       </c>
       <c r="M457" s="2" t="n">
-        <v>4612.07</v>
+        <v>2882.54</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>501-48-CM26</t>
+          <t>1432-2-CM26</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -30174,22 +30174,22 @@
       </c>
       <c r="E458" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F458" t="inlineStr">
         <is>
-          <t>69.150.300-3</t>
+          <t>61.702.000-9</t>
         </is>
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Ranquil</t>
+          <t>SERVICIO NACIONAL DE GEOLOGIA Y MINERIA</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I458" t="inlineStr">
@@ -30213,13 +30213,13 @@
         </is>
       </c>
       <c r="M458" s="2" t="n">
-        <v>2421.34</v>
+        <v>7840.51</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>1536-42-CM26</t>
+          <t>1642-188-CM26</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -30239,22 +30239,22 @@
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>60.511.123-8</t>
+          <t>61.602.125-7</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
+          <t>SERVICIO DE SALUD METROPOLITANO OCCIDENTE HOSPITAL DE CURACAVI</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I459" t="inlineStr">
@@ -30278,13 +30278,13 @@
         </is>
       </c>
       <c r="M459" s="2" t="n">
-        <v>2536.64</v>
+        <v>4612.07</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>2989-110-CM26</t>
+          <t>501-48-CM26</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -30304,22 +30304,22 @@
       </c>
       <c r="E460" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F460" t="inlineStr">
         <is>
-          <t>69.220.800-5</t>
+          <t>69.150.300-3</t>
         </is>
       </c>
       <c r="G460" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS MUERMOS</t>
+          <t>Ilustre Municipalidad de Ranquil</t>
         </is>
       </c>
       <c r="H460" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I460" t="inlineStr">
@@ -30343,13 +30343,13 @@
         </is>
       </c>
       <c r="M460" s="2" t="n">
-        <v>11530.17</v>
+        <v>2421.34</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>696750-9-CM26</t>
+          <t>1536-42-CM26</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -30369,22 +30369,22 @@
       </c>
       <c r="E461" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F461" t="inlineStr">
         <is>
-          <t>61.935.400-1</t>
+          <t>60.511.123-8</t>
         </is>
       </c>
       <c r="G461" t="inlineStr">
         <is>
-          <t>MINISTERIO PUBLICO</t>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE TIERRA DEL FUEGO</t>
         </is>
       </c>
       <c r="H461" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I461" t="inlineStr">
@@ -30408,13 +30408,13 @@
         </is>
       </c>
       <c r="M461" s="2" t="n">
-        <v>2663.47</v>
+        <v>2536.64</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>1057472-6261-CM26</t>
+          <t>4474-161-CM26</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -30429,37 +30429,37 @@
       </c>
       <c r="D462" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E462" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F462" t="inlineStr">
         <is>
-          <t>61.980.320-5</t>
+          <t>69.160.600-7</t>
         </is>
       </c>
       <c r="G462" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO EL CARMEN DOCTOR LUIS VALENTIN FERRADA</t>
+          <t>Ilustre Municipalidad de Contulmo</t>
         </is>
       </c>
       <c r="H462" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I462" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J462" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K462" t="inlineStr">
@@ -30473,13 +30473,13 @@
         </is>
       </c>
       <c r="M462" s="2" t="n">
-        <v>5777.94</v>
+        <v>5765.08</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>4404-15-CM26</t>
+          <t>3841-27-CM26</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -30499,22 +30499,22 @@
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>69.110.500-8</t>
+          <t>69.141.600-3</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
+          <t>I MUNICIPALIDAD DE PEMUCO</t>
         </is>
       </c>
       <c r="H463" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I463" t="inlineStr">
@@ -30538,13 +30538,13 @@
         </is>
       </c>
       <c r="M463" s="2" t="n">
-        <v>31200.89</v>
+        <v>11555.88</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>4176-40-CM26</t>
+          <t>2297-203-CM26</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -30569,32 +30569,32 @@
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H464" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I464" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J464" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K464" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L464" t="inlineStr">
@@ -30603,13 +30603,13 @@
         </is>
       </c>
       <c r="M464" s="2" t="n">
-        <v>2426.74</v>
+        <v>4096.05</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>3841-27-CM26</t>
+          <t>4404-15-CM26</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -30629,22 +30629,22 @@
       </c>
       <c r="E465" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F465" t="inlineStr">
         <is>
-          <t>69.141.600-3</t>
+          <t>69.110.500-8</t>
         </is>
       </c>
       <c r="G465" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PEMUCO</t>
+          <t>I MUNICIPALIDAD DE SAN CLEMENTE</t>
         </is>
       </c>
       <c r="H465" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I465" t="inlineStr">
@@ -30668,7 +30668,7 @@
         </is>
       </c>
       <c r="M465" s="2" t="n">
-        <v>11555.88</v>
+        <v>31200.89</v>
       </c>
     </row>
     <row r="466">
@@ -30739,7 +30739,7 @@
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>2297-203-CM26</t>
+          <t>3811-51-CM26</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -30764,32 +30764,32 @@
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.071.900-2</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE ISLA DE MAIPO</t>
         </is>
       </c>
       <c r="H467" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I467" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J467" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K467" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L467" t="inlineStr">
@@ -30798,7 +30798,7 @@
         </is>
       </c>
       <c r="M467" s="2" t="n">
-        <v>4096.05</v>
+        <v>6933.53</v>
       </c>
     </row>
     <row r="468">
@@ -30869,7 +30869,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>2458-34-CM26</t>
+          <t>1298355-153-CM26</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -30894,12 +30894,12 @@
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>69.070.300-9</t>
+          <t>71.293.900-1</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
+          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -30928,13 +30928,13 @@
         </is>
       </c>
       <c r="M469" s="2" t="n">
-        <v>23111.77</v>
+        <v>30045.3</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>4484-17-CM26</t>
+          <t>3611-68-CM26</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -30959,17 +30959,17 @@
       </c>
       <c r="F470" t="inlineStr">
         <is>
-          <t>69.030.400-7</t>
+          <t>69.190.600-0</t>
         </is>
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
+          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I470" t="inlineStr">
@@ -30993,7 +30993,7 @@
         </is>
       </c>
       <c r="M470" s="2" t="n">
-        <v>4622.35</v>
+        <v>34667.65</v>
       </c>
     </row>
     <row r="471">
@@ -31064,7 +31064,7 @@
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>3611-68-CM26</t>
+          <t>2297-208-CM26</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -31089,32 +31089,32 @@
       </c>
       <c r="F472" t="inlineStr">
         <is>
-          <t>69.190.600-0</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G472" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAAVEDRA</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H472" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I472" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J472" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K472" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L472" t="inlineStr">
@@ -31123,13 +31123,13 @@
         </is>
       </c>
       <c r="M472" s="2" t="n">
-        <v>34667.65</v>
+        <v>12357.37</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>2297-208-CM26</t>
+          <t>4079-64-CM26</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -31154,32 +31154,32 @@
       </c>
       <c r="F473" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.151.000-k</t>
         </is>
       </c>
       <c r="G473" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE CABRERO</t>
         </is>
       </c>
       <c r="H473" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I473" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J473" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K473" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L473" t="inlineStr">
@@ -31188,13 +31188,13 @@
         </is>
       </c>
       <c r="M473" s="2" t="n">
-        <v>12357.37</v>
+        <v>13867.06</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>4079-64-CM26</t>
+          <t>2458-33-CM26</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -31214,22 +31214,22 @@
       </c>
       <c r="E474" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F474" t="inlineStr">
         <is>
-          <t>69.151.000-k</t>
+          <t>69.070.300-9</t>
         </is>
       </c>
       <c r="G474" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CABRERO</t>
+          <t>I MUNICIPALIDAD DE PROVIDENCIA</t>
         </is>
       </c>
       <c r="H474" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I474" t="inlineStr">
@@ -31253,13 +31253,13 @@
         </is>
       </c>
       <c r="M474" s="2" t="n">
-        <v>13867.06</v>
+        <v>11555.88</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>2458-33-CM26</t>
+          <t>2458-34-CM26</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -31318,13 +31318,13 @@
         </is>
       </c>
       <c r="M475" s="2" t="n">
-        <v>11555.88</v>
+        <v>23111.77</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>1298355-153-CM26</t>
+          <t>4176-40-CM26</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -31344,22 +31344,22 @@
       </c>
       <c r="E476" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F476" t="inlineStr">
         <is>
-          <t>71.293.900-1</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G476" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL MELIPILLA PARA LA ED SALUD</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H476" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I476" t="inlineStr">
@@ -31383,13 +31383,13 @@
         </is>
       </c>
       <c r="M476" s="2" t="n">
-        <v>30045.3</v>
+        <v>2426.74</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>1057429-483-CM26</t>
+          <t>4484-17-CM26</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -31409,22 +31409,22 @@
       </c>
       <c r="E477" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F477" t="inlineStr">
         <is>
-          <t>61.602.201-6</t>
+          <t>69.030.400-7</t>
         </is>
       </c>
       <c r="G477" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE CORONEL</t>
+          <t>I MUNICIPALIDAD DE TIERRA AMARILLA</t>
         </is>
       </c>
       <c r="H477" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I477" t="inlineStr">
@@ -31454,7 +31454,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>3811-51-CM26</t>
+          <t>1057429-483-CM26</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -31474,22 +31474,22 @@
       </c>
       <c r="E478" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F478" t="inlineStr">
         <is>
-          <t>69.071.900-2</t>
+          <t>61.602.201-6</t>
         </is>
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ISLA DE MAIPO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE CORONEL</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I478" t="inlineStr">
@@ -31513,13 +31513,13 @@
         </is>
       </c>
       <c r="M478" s="2" t="n">
-        <v>6933.53</v>
+        <v>4622.35</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>2145-178-CM26</t>
+          <t>1057472-6261-CM26</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -31544,27 +31544,27 @@
       </c>
       <c r="F479" t="inlineStr">
         <is>
-          <t>61.606.409-6</t>
+          <t>61.980.320-5</t>
         </is>
       </c>
       <c r="G479" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
+          <t>HOSPITAL CLINICO METROPOLITANO EL CARMEN DOCTOR LUIS VALENTIN FERRADA</t>
         </is>
       </c>
       <c r="H479" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I479" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J479" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K479" t="inlineStr">
@@ -31578,13 +31578,13 @@
         </is>
       </c>
       <c r="M479" s="2" t="n">
-        <v>4044.56</v>
+        <v>5777.94</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>2803-84-CM26</t>
+          <t>2145-178-CM26</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -31609,17 +31609,17 @@
       </c>
       <c r="F480" t="inlineStr">
         <is>
-          <t>69.051.100-2</t>
+          <t>61.606.409-6</t>
         </is>
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>MUNICIPALIDAD DE LOS ANDES</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE LOS VILOS</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I480" t="inlineStr">
@@ -31643,13 +31643,13 @@
         </is>
       </c>
       <c r="M480" s="2" t="n">
-        <v>9244.709999999999</v>
+        <v>4044.56</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>3935-23-CM26</t>
+          <t>2803-84-CM26</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -31669,22 +31669,22 @@
       </c>
       <c r="E481" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F481" t="inlineStr">
         <is>
-          <t>69.190.900-K</t>
+          <t>69.051.100-2</t>
         </is>
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FREIRE</t>
+          <t>MUNICIPALIDAD DE LOS ANDES</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I481" t="inlineStr">
@@ -31708,13 +31708,13 @@
         </is>
       </c>
       <c r="M481" s="2" t="n">
-        <v>50961.45</v>
+        <v>9244.709999999999</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>2595-75-CM26</t>
+          <t>3935-23-CM26</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -31734,22 +31734,22 @@
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>69.130.700-K</t>
+          <t>69.190.900-K</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PARRAL</t>
+          <t>I MUNICIPALIDAD DE FREIRE</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I482" t="inlineStr">
@@ -31773,13 +31773,13 @@
         </is>
       </c>
       <c r="M482" s="2" t="n">
-        <v>79735.60000000001</v>
+        <v>50961.45</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>720-36-CM26</t>
+          <t>2595-75-CM26</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -31804,17 +31804,17 @@
       </c>
       <c r="F483" t="inlineStr">
         <is>
-          <t>61.308.000-7</t>
+          <t>69.130.700-K</t>
         </is>
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>SERVICIO AGRICOLA Y GANADERO</t>
+          <t>I MUNICIPALIDAD DE PARRAL</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I483" t="inlineStr">
@@ -31838,13 +31838,13 @@
         </is>
       </c>
       <c r="M483" s="2" t="n">
-        <v>4622.35</v>
+        <v>79735.60000000001</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>3299-42-CM26</t>
+          <t>720-36-CM26</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -31864,22 +31864,22 @@
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H484" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I484" t="inlineStr">
@@ -31909,7 +31909,7 @@
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>929-62-CM26</t>
+          <t>3299-42-CM26</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -31929,22 +31929,22 @@
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>61.107.000-4</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
         <is>
-          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H485" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I485" t="inlineStr">
@@ -31968,13 +31968,13 @@
         </is>
       </c>
       <c r="M485" s="2" t="n">
-        <v>3304.98</v>
+        <v>4622.35</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>1057489-3793-CM26</t>
+          <t>929-62-CM26</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -31994,17 +31994,17 @@
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>61.608.406-2</t>
+          <t>61.107.000-4</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
+          <t>INSTITUTO NACIONAL DE DEPORTES DE CHILE</t>
         </is>
       </c>
       <c r="H486" t="inlineStr">
@@ -32014,12 +32014,12 @@
       </c>
       <c r="I486" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J486" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K486" t="inlineStr">
@@ -32033,13 +32033,13 @@
         </is>
       </c>
       <c r="M486" s="2" t="n">
-        <v>27156.33</v>
+        <v>3304.98</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>2445-1706-CM26</t>
+          <t>1057489-3793-CM26</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -32059,32 +32059,32 @@
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>69.100.100-8</t>
+          <t>61.608.406-2</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURICO</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL DEL SALVADOR</t>
         </is>
       </c>
       <c r="H487" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I487" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J487" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K487" t="inlineStr">
@@ -32098,13 +32098,13 @@
         </is>
       </c>
       <c r="M487" s="2" t="n">
-        <v>5257.93</v>
+        <v>27156.33</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>2548-109-CM26</t>
+          <t>2445-1706-CM26</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -32124,37 +32124,37 @@
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.100.100-8</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE CURICO</t>
         </is>
       </c>
       <c r="H488" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I488" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J488" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K488" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L488" t="inlineStr">
@@ -32163,13 +32163,13 @@
         </is>
       </c>
       <c r="M488" s="2" t="n">
-        <v>5777.94</v>
+        <v>5257.93</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>3796-114-CM26</t>
+          <t>2548-109-CM26</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -32189,37 +32189,37 @@
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>69.172.600-2</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILACO</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I489" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J489" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K489" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L489" t="inlineStr">
@@ -32228,13 +32228,13 @@
         </is>
       </c>
       <c r="M489" s="2" t="n">
-        <v>8089.12</v>
+        <v>5777.94</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>1016414-5-CM26</t>
+          <t>3796-114-CM26</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -32259,17 +32259,17 @@
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>60.909.000-6</t>
+          <t>69.172.600-2</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
         <is>
-          <t>CONSEJO NACIONAL DE TELEVISION</t>
+          <t>I MUNICIPALIDAD DE QUILACO</t>
         </is>
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I490" t="inlineStr">
@@ -32293,13 +32293,13 @@
         </is>
       </c>
       <c r="M490" s="2" t="n">
-        <v>2888.97</v>
+        <v>8089.12</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>3602-28-CM26</t>
+          <t>1016414-5-CM26</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -32319,22 +32319,22 @@
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>69.050.300-K</t>
+          <t>60.909.000-6</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PAPUDO</t>
+          <t>CONSEJO NACIONAL DE TELEVISION</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I491" t="inlineStr">
@@ -32358,13 +32358,13 @@
         </is>
       </c>
       <c r="M491" s="2" t="n">
-        <v>3235.65</v>
+        <v>2888.97</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>2345-81-CM26</t>
+          <t>3602-28-CM26</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -32384,22 +32384,22 @@
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>69.070.400-5</t>
+          <t>69.050.300-K</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAS CONDES</t>
+          <t>I MUNICIPALIDAD DE PAPUDO</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I492" t="inlineStr">
@@ -32423,13 +32423,13 @@
         </is>
       </c>
       <c r="M492" s="2" t="n">
-        <v>39290.01</v>
+        <v>3235.65</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>4037-104-CM26</t>
+          <t>2345-81-CM26</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -32449,22 +32449,22 @@
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>69.220.400-K</t>
+          <t>69.070.400-5</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE FRESIA</t>
+          <t>I MUNICIPALIDAD DE LAS CONDES</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I493" t="inlineStr">
@@ -32488,13 +32488,13 @@
         </is>
       </c>
       <c r="M493" s="2" t="n">
-        <v>23111.77</v>
+        <v>39290.01</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>1057494-823-CM26</t>
+          <t>4037-104-CM26</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -32514,32 +32514,32 @@
       </c>
       <c r="E494" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F494" t="inlineStr">
         <is>
-          <t>61.608.102-0</t>
+          <t>69.220.400-K</t>
         </is>
       </c>
       <c r="G494" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
+          <t>I MUNICIPALIDAD DE FRESIA</t>
         </is>
       </c>
       <c r="H494" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I494" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J494" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K494" t="inlineStr">
@@ -32553,13 +32553,13 @@
         </is>
       </c>
       <c r="M494" s="2" t="n">
-        <v>2415.18</v>
+        <v>23111.77</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>2170-178-CM26</t>
+          <t>1057494-823-CM26</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -32584,27 +32584,27 @@
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>61.606.606-4</t>
+          <t>61.608.102-0</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
+          <t>SERVICIO DE SALUD SUR HOSPITAL EXEQUIEL</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I495" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J495" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K495" t="inlineStr">
@@ -32618,13 +32618,13 @@
         </is>
       </c>
       <c r="M495" s="2" t="n">
-        <v>4622.35</v>
+        <v>2415.18</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>4090-40-CM26</t>
+          <t>2170-178-CM26</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -32639,7 +32639,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>2026-02-26</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -32649,17 +32649,17 @@
       </c>
       <c r="F496" t="inlineStr">
         <is>
-          <t>69.220.500-6</t>
+          <t>61.606.606-4</t>
         </is>
       </c>
       <c r="G496" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MAULLIN</t>
+          <t>HOSPITAL DE LA FAMILIA Y LA COMUNIDAD SANTO TOMAS DE LIMACHE</t>
         </is>
       </c>
       <c r="H496" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I496" t="inlineStr">
@@ -32683,13 +32683,13 @@
         </is>
       </c>
       <c r="M496" s="2" t="n">
-        <v>23321.44</v>
+        <v>4622.35</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>1274907-80-CM26</t>
+          <t>4090-40-CM26</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -32714,12 +32714,12 @@
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>71.299.000-7</t>
+          <t>69.220.500-6</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>CORPORACIÓN MUNICIPAL DE EDUCACIÓN, SALUD Y ATENCIÓN DE MENORES CHONCHI</t>
+          <t>I MUNICIPALIDAD DE MAULLIN</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -32748,13 +32748,13 @@
         </is>
       </c>
       <c r="M497" s="2" t="n">
-        <v>8162.5</v>
+        <v>23321.44</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>4170-61-CM26</t>
+          <t>1274907-80-CM26</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -32779,17 +32779,17 @@
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>69.190.200-5</t>
+          <t>71.299.000-7</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>Ilustre Municipalidad de Galvarino</t>
+          <t>CORPORACIÓN MUNICIPAL DE EDUCACIÓN, SALUD Y ATENCIÓN DE MENORES CHONCHI</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I498" t="inlineStr">
@@ -32813,13 +32813,13 @@
         </is>
       </c>
       <c r="M498" s="2" t="n">
-        <v>23321.44</v>
+        <v>8162.5</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>1346279-25-CM26</t>
+          <t>4170-61-CM26</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -32844,17 +32844,17 @@
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>62.000.970-9</t>
+          <t>69.190.200-5</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
+          <t>Ilustre Municipalidad de Galvarino</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I499" t="inlineStr">
@@ -32878,13 +32878,13 @@
         </is>
       </c>
       <c r="M499" s="2" t="n">
-        <v>2437.09</v>
+        <v>23321.44</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>1057420-140-CM26</t>
+          <t>1346279-25-CM26</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -32909,32 +32909,32 @@
       </c>
       <c r="F500" t="inlineStr">
         <is>
-          <t>61.607.305-2</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G500" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H500" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I500" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J500" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K500" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L500" t="inlineStr">
@@ -32943,13 +32943,13 @@
         </is>
       </c>
       <c r="M500" s="2" t="n">
-        <v>2448.75</v>
+        <v>2437.09</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>3705-82-CM26</t>
+          <t>1057420-140-CM26</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -32969,37 +32969,37 @@
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>69.180.300-7</t>
+          <t>61.607.305-2</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
+          <t>SERVICIO DE SALUD BIO BIO HOSPITAL DE HU</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I501" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J501" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K501" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L501" t="inlineStr">
@@ -33008,13 +33008,13 @@
         </is>
       </c>
       <c r="M501" s="2" t="n">
-        <v>10494.65</v>
+        <v>2448.75</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>3947-154-CM26</t>
+          <t>3705-82-CM26</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -33039,32 +33039,32 @@
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>69.151.400-5</t>
+          <t>69.180.300-7</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA JUANA</t>
+          <t>I MUNICIPALIDAD DE LOS SAUCES</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I502" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J502" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K502" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L502" t="inlineStr">
@@ -33073,13 +33073,13 @@
         </is>
       </c>
       <c r="M502" s="2" t="n">
-        <v>4689.89</v>
+        <v>10494.65</v>
       </c>
     </row>
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>3947-155-CM26</t>
+          <t>3947-154-CM26</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -33138,13 +33138,13 @@
         </is>
       </c>
       <c r="M503" s="2" t="n">
-        <v>4185.41</v>
+        <v>4689.89</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>3707-125-CM26</t>
+          <t>3947-155-CM26</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -33164,37 +33164,37 @@
       </c>
       <c r="E504" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F504" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>69.151.400-5</t>
         </is>
       </c>
       <c r="G504" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>I MUNICIPALIDAD DE SANTA JUANA</t>
         </is>
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I504" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J504" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K504" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L504" t="inlineStr">
@@ -33203,13 +33203,13 @@
         </is>
       </c>
       <c r="M504" s="2" t="n">
-        <v>5707.92</v>
+        <v>4185.41</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>1230872-44-CM26</t>
+          <t>3707-125-CM26</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -33234,17 +33234,17 @@
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>65.114.043-9</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Productivo y Turismo de Molina</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I505" t="inlineStr">
@@ -33268,13 +33268,13 @@
         </is>
       </c>
       <c r="M505" s="2" t="n">
-        <v>2565.36</v>
+        <v>5707.92</v>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>1233664-34-CM26</t>
+          <t>1230872-44-CM26</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -33299,17 +33299,17 @@
       </c>
       <c r="F506" t="inlineStr">
         <is>
-          <t>65.473.570-0</t>
+          <t>65.114.043-9</t>
         </is>
       </c>
       <c r="G506" t="inlineStr">
         <is>
-          <t>Corporación del Deporte e Inclusión Social de la Ilustre Municipalidad de Cerro Navia</t>
+          <t>Corporación Municipal de Desarrollo Productivo y Turismo de Molina</t>
         </is>
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I506" t="inlineStr">
@@ -33333,13 +33333,13 @@
         </is>
       </c>
       <c r="M506" s="2" t="n">
-        <v>2448.75</v>
+        <v>2565.36</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>3181-98-CM26</t>
+          <t>1233664-34-CM26</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -33364,32 +33364,32 @@
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>69.080.200-7</t>
+          <t>65.473.570-0</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
+          <t>Corporación del Deporte e Inclusión Social de la Ilustre Municipalidad de Cerro Navia</t>
         </is>
       </c>
       <c r="H507" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J507" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K507" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L507" t="inlineStr">
@@ -33398,13 +33398,13 @@
         </is>
       </c>
       <c r="M507" s="2" t="n">
-        <v>4339.7</v>
+        <v>2448.75</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>2737-109-CM26</t>
+          <t>3181-98-CM26</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -33429,32 +33429,32 @@
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>69.050.600-9</t>
+          <t>69.080.200-7</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE MACHALI</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J508" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K508" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L508" t="inlineStr">
@@ -33463,13 +33463,13 @@
         </is>
       </c>
       <c r="M508" s="2" t="n">
-        <v>3381.61</v>
+        <v>4339.7</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>5520-1268-CM26</t>
+          <t>2737-109-CM26</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -33494,17 +33494,17 @@
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.050.600-9</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE SAN FELIPE</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I509" t="inlineStr">
@@ -33528,13 +33528,13 @@
         </is>
       </c>
       <c r="M509" s="2" t="n">
-        <v>17491.08</v>
+        <v>3381.61</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>5350-693-CM26</t>
+          <t>5520-1268-CM26</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -33554,22 +33554,22 @@
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>69.030.500-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VALLENAR</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I510" t="inlineStr">
@@ -33593,13 +33593,13 @@
         </is>
       </c>
       <c r="M510" s="2" t="n">
-        <v>3265</v>
+        <v>17491.08</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="inlineStr">
         <is>
-          <t>1608-21-CM26</t>
+          <t>5350-693-CM26</t>
         </is>
       </c>
       <c r="B511" t="inlineStr">
@@ -33619,22 +33619,22 @@
       </c>
       <c r="E511" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F511" t="inlineStr">
         <is>
-          <t>60.511.110-6</t>
+          <t>69.030.500-3</t>
         </is>
       </c>
       <c r="G511" t="inlineStr">
         <is>
-          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
+          <t>I MUNICIPALIDAD DE VALLENAR</t>
         </is>
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I511" t="inlineStr">
@@ -33658,13 +33658,13 @@
         </is>
       </c>
       <c r="M511" s="2" t="n">
-        <v>2915.18</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
         <is>
-          <t>4834-55-CM26</t>
+          <t>1608-21-CM26</t>
         </is>
       </c>
       <c r="B512" t="inlineStr">
@@ -33689,17 +33689,17 @@
       </c>
       <c r="F512" t="inlineStr">
         <is>
-          <t>61.932.200-2</t>
+          <t>60.511.110-6</t>
         </is>
       </c>
       <c r="G512" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
         </is>
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I512" t="inlineStr">
@@ -33723,13 +33723,13 @@
         </is>
       </c>
       <c r="M512" s="2" t="n">
-        <v>2435.14</v>
+        <v>2915.18</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>3506-124-CM26</t>
+          <t>4834-55-CM26</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -33749,22 +33749,22 @@
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>69.020.100-3</t>
+          <t>61.932.200-2</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
+          <t>ILUSTRE MUNICIPALIDAD COCHAMO</t>
         </is>
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I513" t="inlineStr">
@@ -33788,13 +33788,13 @@
         </is>
       </c>
       <c r="M513" s="2" t="n">
-        <v>2448.75</v>
+        <v>2435.14</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>705291-6-CM26</t>
+          <t>3506-124-CM26</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -33814,22 +33814,22 @@
       </c>
       <c r="E514" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F514" t="inlineStr">
         <is>
-          <t>61.608.205-1</t>
+          <t>69.020.100-3</t>
         </is>
       </c>
       <c r="G514" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
+          <t>I MUNICIPALIDAD DE TOCOPILLA</t>
         </is>
       </c>
       <c r="H514" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I514" t="inlineStr">
@@ -33853,13 +33853,13 @@
         </is>
       </c>
       <c r="M514" s="2" t="n">
-        <v>5363.93</v>
+        <v>2448.75</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>1988-8-CM26</t>
+          <t>705291-6-CM26</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -33884,17 +33884,17 @@
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>60.701.003-K</t>
+          <t>61.608.205-1</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
         </is>
       </c>
       <c r="H515" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I515" t="inlineStr">
@@ -33918,13 +33918,13 @@
         </is>
       </c>
       <c r="M515" s="2" t="n">
-        <v>3498.22</v>
+        <v>5363.93</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>4686-149-CM26</t>
+          <t>1988-8-CM26</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -33944,22 +33944,22 @@
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>60.202.000-2</t>
+          <t>60.701.003-K</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
         <is>
-          <t>Cámara de Diputados de Chile</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H516" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I516" t="inlineStr">
@@ -33983,13 +33983,13 @@
         </is>
       </c>
       <c r="M516" s="2" t="n">
-        <v>24487.51</v>
+        <v>3498.22</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>2923-123-CM26</t>
+          <t>4686-149-CM26</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -34009,22 +34009,22 @@
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>69.030.100-8</t>
+          <t>60.202.000-2</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHANARAL</t>
+          <t>Cámara de Diputados de Chile</t>
         </is>
       </c>
       <c r="H517" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I517" t="inlineStr">
@@ -34048,13 +34048,13 @@
         </is>
       </c>
       <c r="M517" s="2" t="n">
-        <v>15158.94</v>
+        <v>24487.51</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>2546-131-CM26</t>
+          <t>2923-123-CM26</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -34074,22 +34074,22 @@
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>61.955.000-5</t>
+          <t>69.030.100-8</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
+          <t>I MUNICIPALIDAD DE CHANARAL</t>
         </is>
       </c>
       <c r="H518" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I518" t="inlineStr">
@@ -34113,13 +34113,13 @@
         </is>
       </c>
       <c r="M518" s="2" t="n">
-        <v>2448.75</v>
+        <v>15158.94</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="inlineStr">
         <is>
-          <t>2069-1686-CM26</t>
+          <t>2546-131-CM26</t>
         </is>
       </c>
       <c r="B519" t="inlineStr">
@@ -34139,32 +34139,32 @@
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>61.608.101-2</t>
+          <t>61.955.000-5</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
+          <t>I MUNICIPALIDAD DE PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H519" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I519" t="inlineStr">
         <is>
-          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J519" t="inlineStr">
         <is>
-          <t>92.011.000-2</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K519" t="inlineStr">
@@ -34178,13 +34178,13 @@
         </is>
       </c>
       <c r="M519" s="2" t="n">
-        <v>3148.39</v>
+        <v>2448.75</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>4769-14-CM26</t>
+          <t>2069-1686-CM26</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -34204,32 +34204,32 @@
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>69.091.400-K</t>
+          <t>61.608.101-2</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA ESTRELLA</t>
+          <t>SERVICIO DE SALUD METROPOLITANO SUR HOSP</t>
         </is>
       </c>
       <c r="H520" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I520" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>EMPRESA NACIONAL DE ENERGIA ENEX S.A.</t>
         </is>
       </c>
       <c r="J520" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>92.011.000-2</t>
         </is>
       </c>
       <c r="K520" t="inlineStr">
@@ -34243,13 +34243,13 @@
         </is>
       </c>
       <c r="M520" s="2" t="n">
-        <v>12826.79</v>
+        <v>3148.39</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>2306-33-CM26</t>
+          <t>4769-14-CM26</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -34274,32 +34274,32 @@
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>69.091.400-K</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>I MUNICIPALIDAD DE LA ESTRELLA</t>
         </is>
       </c>
       <c r="H521" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I521" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J521" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K521" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L521" t="inlineStr">
@@ -34308,13 +34308,13 @@
         </is>
       </c>
       <c r="M521" s="2" t="n">
-        <v>2435.14</v>
+        <v>12826.79</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>1350296-325-CM26</t>
+          <t>2306-33-CM26</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -34334,37 +34334,37 @@
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>65.228.694-1</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
         <is>
-          <t>HOSPITAL DE ALTO HOSPICIO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H522" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I522" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J522" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K522" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L522" t="inlineStr">
@@ -34373,13 +34373,13 @@
         </is>
       </c>
       <c r="M522" s="2" t="n">
-        <v>2623.66</v>
+        <v>2435.14</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>3497-90-CM26</t>
+          <t>1350296-325-CM26</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
@@ -34404,17 +34404,17 @@
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>69.140.400-5</t>
+          <t>65.228.694-1</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COBQUECURA</t>
+          <t>HOSPITAL DE ALTO HOSPICIO</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I523" t="inlineStr">
@@ -34438,13 +34438,13 @@
         </is>
       </c>
       <c r="M523" s="2" t="n">
-        <v>11660.72</v>
+        <v>2623.66</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>2026-163-CM26</t>
+          <t>3497-90-CM26</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -34469,17 +34469,17 @@
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>61.606.600-5</t>
+          <t>69.140.400-5</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
+          <t>I MUNICIPALIDAD DE COBQUECURA</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I524" t="inlineStr">
@@ -34503,13 +34503,13 @@
         </is>
       </c>
       <c r="M524" s="2" t="n">
-        <v>49558.06</v>
+        <v>11660.72</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>4452-182-CM26</t>
+          <t>2026-163-CM26</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -34529,22 +34529,22 @@
       </c>
       <c r="E525" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F525" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.606.600-5</t>
         </is>
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>SERVICIO SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I525" t="inlineStr">
@@ -34568,13 +34568,13 @@
         </is>
       </c>
       <c r="M525" s="2" t="n">
-        <v>5830.36</v>
+        <v>49558.06</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>3707-122-CM26</t>
+          <t>4452-182-CM26</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -34594,22 +34594,22 @@
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>69.040.200-9</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H526" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I526" t="inlineStr">
@@ -34639,7 +34639,7 @@
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>3334-32-CM26</t>
+          <t>3707-122-CM26</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -34659,37 +34659,37 @@
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>69.200.800-6</t>
+          <t>69.040.200-9</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA UNION</t>
+          <t>I MUNICIPALIDAD DE LA HIGUERA</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I527" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J527" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K527" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L527" t="inlineStr">
@@ -34698,13 +34698,13 @@
         </is>
       </c>
       <c r="M527" s="2" t="n">
-        <v>5634.14</v>
+        <v>5830.36</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>2200-78-CM26</t>
+          <t>3334-32-CM26</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -34724,37 +34724,37 @@
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>61.606.700-1</t>
+          <t>69.200.800-6</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ACONCAGUA</t>
+          <t>I MUNICIPALIDAD DE LA UNION</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I528" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J528" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K528" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L528" t="inlineStr">
@@ -34763,13 +34763,13 @@
         </is>
       </c>
       <c r="M528" s="2" t="n">
-        <v>81042</v>
+        <v>5634.14</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>3736-21-CM26</t>
+          <t>2200-78-CM26</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -34794,17 +34794,17 @@
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>69.170.300-2</t>
+          <t>61.606.700-1</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LAJA</t>
+          <t>SERVICIO DE SALUD ACONCAGUA</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I529" t="inlineStr">
@@ -34828,13 +34828,13 @@
         </is>
       </c>
       <c r="M529" s="2" t="n">
-        <v>2856.88</v>
+        <v>81042</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>1988-7-CM26</t>
+          <t>3736-21-CM26</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -34859,17 +34859,17 @@
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>60.701.003-K</t>
+          <t>69.170.300-2</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>I MUNICIPALIDAD DE LAJA</t>
         </is>
       </c>
       <c r="H530" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I530" t="inlineStr">
@@ -34893,13 +34893,13 @@
         </is>
       </c>
       <c r="M530" s="2" t="n">
-        <v>2435.14</v>
+        <v>2856.88</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>3953-49-CM26</t>
+          <t>1988-7-CM26</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -34919,22 +34919,22 @@
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>69.091.500-6</t>
+          <t>60.701.003-K</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PERALILLO</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I531" t="inlineStr">
@@ -34958,13 +34958,13 @@
         </is>
       </c>
       <c r="M531" s="2" t="n">
-        <v>3498.22</v>
+        <v>2435.14</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>924-47-CM26</t>
+          <t>3953-49-CM26</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -34984,22 +34984,22 @@
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>61.601.000-K</t>
+          <t>69.091.500-6</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
+          <t>I MUNICIPALIDAD DE PERALILLO</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I532" t="inlineStr">
@@ -35023,13 +35023,13 @@
         </is>
       </c>
       <c r="M532" s="2" t="n">
-        <v>29151.8</v>
+        <v>3498.22</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>437-10-CM26</t>
+          <t>924-47-CM26</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -35049,22 +35049,22 @@
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>70.816.700-2</t>
+          <t>61.601.000-K</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
+          <t>SUBSECRETARIA DE SALUD PUBLICA</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I533" t="inlineStr">
@@ -35088,13 +35088,13 @@
         </is>
       </c>
       <c r="M533" s="2" t="n">
-        <v>3498.22</v>
+        <v>29151.8</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>4022-95-CM26</t>
+          <t>437-10-CM26</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -35109,7 +35109,7 @@
       </c>
       <c r="D534" t="inlineStr">
         <is>
-          <t>2026-02-27</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="E534" t="inlineStr">
@@ -35119,17 +35119,17 @@
       </c>
       <c r="F534" t="inlineStr">
         <is>
-          <t>69.250.800-9</t>
+          <t>70.816.700-2</t>
         </is>
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
+          <t>CORPORACION DE ASISTENCIA JUDICIAL DE LA REGION DEL BIO BIO</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I534" t="inlineStr">
@@ -35153,13 +35153,13 @@
         </is>
       </c>
       <c r="M534" s="2" t="n">
-        <v>23223.68</v>
+        <v>3498.22</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>4906-55-CM26</t>
+          <t>4022-95-CM26</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -35179,22 +35179,22 @@
       </c>
       <c r="E535" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F535" t="inlineStr">
         <is>
-          <t>61.980.740-5</t>
+          <t>69.250.800-9</t>
         </is>
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD DEL RELONCAVI</t>
+          <t>ILUSTRE MUNICIPALIDAD DE PUTRE</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I535" t="inlineStr">
@@ -35218,13 +35218,13 @@
         </is>
       </c>
       <c r="M535" s="2" t="n">
-        <v>3483.55</v>
+        <v>23223.68</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>411-87-CM26</t>
+          <t>4906-55-CM26</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -35244,22 +35244,22 @@
       </c>
       <c r="E536" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F536" t="inlineStr">
         <is>
-          <t>69.251.900-0</t>
+          <t>61.980.740-5</t>
         </is>
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
+          <t>SERVICIO SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I536" t="inlineStr">
@@ -35283,13 +35283,13 @@
         </is>
       </c>
       <c r="M536" s="2" t="n">
-        <v>23223.68</v>
+        <v>3483.55</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>4168-269-CM26</t>
+          <t>411-87-CM26</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -35309,22 +35309,22 @@
       </c>
       <c r="E537" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F537" t="inlineStr">
         <is>
-          <t>69.130.500-7</t>
+          <t>69.251.900-0</t>
         </is>
       </c>
       <c r="G537" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
+          <t>ILUSTRE MUNICIPALIDAD DE ALTO DEL CARMEN</t>
         </is>
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I537" t="inlineStr">
@@ -35348,13 +35348,13 @@
         </is>
       </c>
       <c r="M537" s="2" t="n">
-        <v>15095.39</v>
+        <v>23223.68</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>557974-32-CM26</t>
+          <t>4168-269-CM26</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -35379,17 +35379,17 @@
       </c>
       <c r="F538" t="inlineStr">
         <is>
-          <t>70.878.900-3</t>
+          <t>69.130.500-7</t>
         </is>
       </c>
       <c r="G538" t="inlineStr">
         <is>
-          <t>CORPORACION MUNICIPAL DE EDUCACION,SALUD,CULTURA Y ATENCION AL MENOR,</t>
+          <t>ILUSTRE MUNICIPALIDAD DE COLBUN</t>
         </is>
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I538" t="inlineStr">
@@ -35413,13 +35413,13 @@
         </is>
       </c>
       <c r="M538" s="2" t="n">
-        <v>6967.1</v>
+        <v>15095.39</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>2207-177-CM26</t>
+          <t>557974-32-CM26</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -35439,22 +35439,22 @@
       </c>
       <c r="E539" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F539" t="inlineStr">
         <is>
-          <t>61.602.153-2</t>
+          <t>70.878.900-3</t>
         </is>
       </c>
       <c r="G539" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
+          <t>CORPORACION MUNICIPAL DE EDUCACION,SALUD,CULTURA Y ATENCION AL MENOR,</t>
         </is>
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I539" t="inlineStr">
@@ -35478,13 +35478,13 @@
         </is>
       </c>
       <c r="M539" s="2" t="n">
-        <v>5805.92</v>
+        <v>6967.1</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>2730-97-CM26</t>
+          <t>2207-177-CM26</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -35504,22 +35504,22 @@
       </c>
       <c r="E540" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F540" t="inlineStr">
         <is>
-          <t>69.230.400-4</t>
+          <t>61.602.153-2</t>
         </is>
       </c>
       <c r="G540" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASTRO</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE PICHILEMU</t>
         </is>
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I540" t="inlineStr">
@@ -35543,13 +35543,13 @@
         </is>
       </c>
       <c r="M540" s="2" t="n">
-        <v>6909.04</v>
+        <v>5805.92</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>2102-123-CM26</t>
+          <t>2730-97-CM26</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -35574,17 +35574,17 @@
       </c>
       <c r="F541" t="inlineStr">
         <is>
-          <t>61.602.212-1</t>
+          <t>69.230.400-4</t>
         </is>
       </c>
       <c r="G541" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
+          <t>I MUNICIPALIDAD DE CASTRO</t>
         </is>
       </c>
       <c r="H541" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I541" t="inlineStr">
@@ -35608,13 +35608,13 @@
         </is>
       </c>
       <c r="M541" s="2" t="n">
-        <v>8128.29</v>
+        <v>6909.04</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>3909-36-CM26</t>
+          <t>2102-123-CM26</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -35634,22 +35634,22 @@
       </c>
       <c r="E542" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F542" t="inlineStr">
         <is>
-          <t>69.180.400-3</t>
+          <t>61.602.212-1</t>
         </is>
       </c>
       <c r="G542" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE RENAICO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE LEBU</t>
         </is>
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I542" t="inlineStr">
@@ -35673,13 +35673,13 @@
         </is>
       </c>
       <c r="M542" s="2" t="n">
-        <v>11611.84</v>
+        <v>8128.29</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
         <is>
-          <t>3884-132-CM26</t>
+          <t>3909-36-CM26</t>
         </is>
       </c>
       <c r="B543" t="inlineStr">
@@ -35699,22 +35699,22 @@
       </c>
       <c r="E543" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F543" t="inlineStr">
         <is>
-          <t>69.040.600-4</t>
+          <t>69.180.400-3</t>
         </is>
       </c>
       <c r="G543" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD PAIHUANO</t>
+          <t>I MUNICIPALIDAD DE RENAICO</t>
         </is>
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I543" t="inlineStr">
@@ -35738,13 +35738,13 @@
         </is>
       </c>
       <c r="M543" s="2" t="n">
-        <v>5181.2</v>
+        <v>11611.84</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>1267885-181-CM26</t>
+          <t>3884-132-CM26</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -35769,17 +35769,17 @@
       </c>
       <c r="F544" t="inlineStr">
         <is>
-          <t>71.016.300-6</t>
+          <t>69.040.600-4</t>
         </is>
       </c>
       <c r="G544" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
+          <t>I MUNICIPALIDAD PAIHUANO</t>
         </is>
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I544" t="inlineStr">
@@ -35803,13 +35803,13 @@
         </is>
       </c>
       <c r="M544" s="2" t="n">
-        <v>10682.89</v>
+        <v>5181.2</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>2307-248-CM26</t>
+          <t>1267885-181-CM26</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -35829,37 +35829,37 @@
       </c>
       <c r="E545" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F545" t="inlineStr">
         <is>
-          <t>69.210.100-6</t>
+          <t>71.016.300-6</t>
         </is>
       </c>
       <c r="G545" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE OSORNO</t>
+          <t>CORP MUNICIPAL DE PANGUIPULLI</t>
         </is>
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>ESMAX DISTRIBUCION LIMITADA</t>
+          <t>COPEC S.A.</t>
         </is>
       </c>
       <c r="J545" t="inlineStr">
         <is>
-          <t>79.588.870-5</t>
+          <t>99.520.000-7</t>
         </is>
       </c>
       <c r="K545" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L545" t="inlineStr">
@@ -35868,13 +35868,13 @@
         </is>
       </c>
       <c r="M545" s="2" t="n">
-        <v>3164.7</v>
+        <v>10682.89</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>898-702-CM26</t>
+          <t>2307-248-CM26</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -35894,37 +35894,37 @@
       </c>
       <c r="E546" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F546" t="inlineStr">
         <is>
-          <t>61.602.126-5</t>
+          <t>69.210.100-6</t>
         </is>
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
+          <t>I MUNICIPALIDAD DE OSORNO</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>COPEC S.A.</t>
+          <t>ESMAX DISTRIBUCION LIMITADA</t>
         </is>
       </c>
       <c r="J546" t="inlineStr">
         <is>
-          <t>99.520.000-7</t>
+          <t>79.588.870-5</t>
         </is>
       </c>
       <c r="K546" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="L546" t="inlineStr">
@@ -35933,13 +35933,13 @@
         </is>
       </c>
       <c r="M546" s="2" t="n">
-        <v>9289.469999999999</v>
+        <v>3164.7</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>580075-22-CM26</t>
+          <t>898-702-CM26</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -35959,22 +35959,22 @@
       </c>
       <c r="E547" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F547" t="inlineStr">
         <is>
-          <t>69.091.100-0</t>
+          <t>61.602.126-5</t>
         </is>
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LITUECHE</t>
+          <t>SERVICIO DE SALUD VALPARAISO SAN ANTONIO</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I547" t="inlineStr">
@@ -35998,13 +35998,13 @@
         </is>
       </c>
       <c r="M547" s="2" t="n">
-        <v>2554.6</v>
+        <v>9289.469999999999</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>1057438-49-CM26</t>
+          <t>580075-22-CM26</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -36024,22 +36024,22 @@
       </c>
       <c r="E548" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F548" t="inlineStr">
         <is>
-          <t>61.606.401-0</t>
+          <t>69.091.100-0</t>
         </is>
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
+          <t>I MUNICIPALIDAD DE LITUECHE</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I548" t="inlineStr">
@@ -36063,13 +36063,13 @@
         </is>
       </c>
       <c r="M548" s="2" t="n">
-        <v>4064.14</v>
+        <v>2554.6</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>3073-78-CM26</t>
+          <t>1057438-49-CM26</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -36094,17 +36094,17 @@
       </c>
       <c r="F549" t="inlineStr">
         <is>
-          <t>61.102.015-5</t>
+          <t>61.606.401-0</t>
         </is>
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL VICUNA</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I549" t="inlineStr">
@@ -36128,13 +36128,13 @@
         </is>
       </c>
       <c r="M549" s="2" t="n">
-        <v>34835.52</v>
+        <v>4064.14</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>3863-60-CM26</t>
+          <t>3073-78-CM26</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -36159,17 +36159,17 @@
       </c>
       <c r="F550" t="inlineStr">
         <is>
-          <t>69.090.600-7</t>
+          <t>61.102.015-5</t>
         </is>
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I550" t="inlineStr">
@@ -36193,13 +36193,13 @@
         </is>
       </c>
       <c r="M550" s="2" t="n">
-        <v>23223.68</v>
+        <v>34835.52</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>2450-187-CM26</t>
+          <t>3863-60-CM26</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -36224,17 +36224,17 @@
       </c>
       <c r="F551" t="inlineStr">
         <is>
-          <t>69.040.100-2</t>
+          <t>69.090.600-7</t>
         </is>
       </c>
       <c r="G551" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H551" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I551" t="inlineStr">
@@ -36258,71 +36258,136 @@
         </is>
       </c>
       <c r="M551" s="2" t="n">
-        <v>40130.49</v>
+        <v>23223.68</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
+          <t>2450-187-CM26</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>2026-02-27</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>69.040.100-2</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>ILUSTRE MUNICIPALIDAD DE LA SERENA</t>
+        </is>
+      </c>
+      <c r="H552" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I552" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J552" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K552" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L552" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M552" s="2" t="n">
+        <v>40130.49</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
           <t>1057389-1307-CM26</t>
         </is>
       </c>
-      <c r="B552" t="inlineStr">
-        <is>
-          <t>2239-13-LR25</t>
-        </is>
-      </c>
-      <c r="C552" t="inlineStr">
-        <is>
-          <t>feb-2026</t>
-        </is>
-      </c>
-      <c r="D552" t="inlineStr">
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>2239-13-LR25</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
         <is>
           <t>2026-02-27</t>
         </is>
       </c>
-      <c r="E552" t="inlineStr">
+      <c r="E553" t="inlineStr">
         <is>
           <t>Recepcion Conforme</t>
         </is>
       </c>
-      <c r="F552" t="inlineStr">
+      <c r="F553" t="inlineStr">
         <is>
           <t>61.602.229-6</t>
         </is>
       </c>
-      <c r="G552" t="inlineStr">
+      <c r="G553" t="inlineStr">
         <is>
           <t>SERVICIO SALUD ARAUCANIA NORTE HOSPITAL VICTORIA</t>
         </is>
       </c>
-      <c r="H552" t="inlineStr">
+      <c r="H553" t="inlineStr">
         <is>
           <t>Araucanía</t>
         </is>
       </c>
-      <c r="I552" t="inlineStr">
-        <is>
-          <t>COPEC S.A.</t>
-        </is>
-      </c>
-      <c r="J552" t="inlineStr">
-        <is>
-          <t>99.520.000-7</t>
-        </is>
-      </c>
-      <c r="K552" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="L552" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M552" s="2" t="n">
+      <c r="I553" t="inlineStr">
+        <is>
+          <t>COPEC S.A.</t>
+        </is>
+      </c>
+      <c r="J553" t="inlineStr">
+        <is>
+          <t>99.520.000-7</t>
+        </is>
+      </c>
+      <c r="K553" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L553" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M553" s="2" t="n">
         <v>3483.55</v>
       </c>
     </row>
